--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -553,7 +553,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:50</v>
@@ -2260,7 +2260,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
@@ -2293,7 +2293,7 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="51">
@@ -3099,7 +3099,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>2:34</v>

--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -553,7 +553,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:50</v>
@@ -1009,7 +1009,7 @@
         <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:01</v>
@@ -1047,7 +1047,7 @@
         <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:16</v>
@@ -1085,7 +1085,7 @@
         <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:03</v>
@@ -1123,7 +1123,7 @@
         <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:41</v>
@@ -1161,7 +1161,7 @@
         <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:05</v>
@@ -1199,7 +1199,7 @@
         <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:46</v>
@@ -1237,7 +1237,7 @@
         <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:32</v>
@@ -1275,7 +1275,7 @@
         <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:42</v>
@@ -1313,7 +1313,7 @@
         <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:38</v>
@@ -1351,7 +1351,7 @@
         <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:10</v>
@@ -1389,7 +1389,7 @@
         <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:57</v>
@@ -1427,7 +1427,7 @@
         <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>2:19</v>
@@ -2415,7 +2415,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>4:37</v>
@@ -2453,7 +2453,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>4:06</v>
@@ -2491,7 +2491,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:54</v>
@@ -2529,7 +2529,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>4:10</v>
@@ -2567,7 +2567,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:26</v>
@@ -2643,7 +2643,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:56</v>
@@ -2681,7 +2681,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>4:01</v>
@@ -2719,7 +2719,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:05</v>
@@ -2757,7 +2757,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>2:27</v>
@@ -2795,7 +2795,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:34</v>
@@ -2833,7 +2833,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:13</v>
@@ -2871,7 +2871,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:13</v>
@@ -2909,7 +2909,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:08</v>
@@ -3213,7 +3213,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:06</v>
@@ -3251,7 +3251,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:21</v>

--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>שלוש ציפורים דמיון חופשי</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%a9-%d7%a6%d7%99%d7%a4%d7%95%d7%a8%d7%99%d7%9d-%d7%93%d7%9e%d7%99%d7%95%d7%9f-%d7%97%d7%95%d7%a4%d7%a9%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>"דמיון חופשי” של יצחק קלפטר הוא מן השירים שבהם הפשטות הלירית נושאת על גבה עומק רגשי גדול. זהו שיר על אהבה שאינה מתממשת, על פער בין תשוקה למציאות, ועל המקום שבו הדמיון הופך למרחב מפלט – אך גם למרחב של</v>
       </c>
       <c r="G2" t="str">
-        <v>4:58</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>The Warning</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>שלוש ציפורים דמיון חופשי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>5:08</v>
+        <v>4:58</v>
       </c>
       <c r="H3" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-01</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:38</v>
+        <v>5:08</v>
       </c>
       <c r="H4" t="str">
-        <v>Roxette</v>
+        <v>The Offspring</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-01</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:50</v>
+        <v>4:38</v>
       </c>
       <c r="H5" t="str">
-        <v>Jessie Ware</v>
+        <v>Roxette</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-01</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:10</v>
+        <v>3:50</v>
       </c>
       <c r="H6" t="str">
-        <v>Joseph</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-01</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:44</v>
+        <v>3:10</v>
       </c>
       <c r="H7" t="str">
-        <v>Dean Lewis</v>
+        <v>Joseph</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-01</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:57</v>
+        <v>2:44</v>
       </c>
       <c r="H8" t="str">
-        <v>Take That</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-01</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H9" t="str">
-        <v>The Cure</v>
+        <v>Take That</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-01</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:07</v>
+        <v>2:39</v>
       </c>
       <c r="H10" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>The Cure</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-01</v>
@@ -796,10 +796,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:47</v>
+        <v>3:07</v>
       </c>
       <c r="H11" t="str">
-        <v>Paris Paloma</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-01</v>
@@ -834,10 +834,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:22</v>
+        <v>4:47</v>
       </c>
       <c r="H12" t="str">
-        <v>Zara Larsson</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B13" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-01</v>
@@ -872,10 +872,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:48</v>
+        <v>3:22</v>
       </c>
       <c r="H13" t="str">
-        <v>only the poets</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B14" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-01</v>
@@ -910,10 +910,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H14" t="str">
-        <v>Katelyn Tarver</v>
+        <v>only the poets</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-01</v>
@@ -948,10 +948,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:33</v>
+        <v>2:52</v>
       </c>
       <c r="H15" t="str">
-        <v>David Guetta</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B16" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-01</v>
@@ -986,10 +986,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:41</v>
+        <v>3:33</v>
       </c>
       <c r="H16" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-01</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:01</v>
+        <v>2:41</v>
       </c>
       <c r="H17" t="str">
-        <v>Ella Langley</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-01</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>4:01</v>
       </c>
       <c r="H18" t="str">
-        <v>Dogpark</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-01</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:03</v>
+        <v>3:16</v>
       </c>
       <c r="H19" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Dogpark</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-01</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:41</v>
+        <v>3:03</v>
       </c>
       <c r="H20" t="str">
-        <v>ERNEST</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:05</v>
+        <v>2:41</v>
       </c>
       <c r="H21" t="str">
-        <v>Labrinth</v>
+        <v>ERNEST</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:46</v>
+        <v>3:05</v>
       </c>
       <c r="H22" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Labrinth</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:32</v>
+        <v>2:46</v>
       </c>
       <c r="H23" t="str">
-        <v>VOILÀ</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:42</v>
+        <v>3:32</v>
       </c>
       <c r="H24" t="str">
-        <v>Cannons</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:38</v>
+        <v>3:42</v>
       </c>
       <c r="H25" t="str">
-        <v>Kylie Morgan</v>
+        <v>Cannons</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:10</v>
+        <v>2:38</v>
       </c>
       <c r="H26" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:57</v>
+        <v>3:10</v>
       </c>
       <c r="H27" t="str">
-        <v>Willie Nelson</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:19</v>
+        <v>3:57</v>
       </c>
       <c r="H28" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:04</v>
+        <v>2:19</v>
       </c>
       <c r="H29" t="str">
-        <v>India Martínez</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:16</v>
+        <v>4:04</v>
       </c>
       <c r="H30" t="str">
-        <v>Chelsea Cutler</v>
+        <v>India Martínez</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:58</v>
+        <v>2:16</v>
       </c>
       <c r="H31" t="str">
-        <v>TINI</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:26</v>
+        <v>5:58</v>
       </c>
       <c r="H32" t="str">
-        <v>Charley</v>
+        <v>TINI</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-01</v>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H33" t="str">
-        <v>Demi Lovato</v>
+        <v>Charley</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-01</v>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H34" t="str">
-        <v>Teddy Swims</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-01</v>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:14</v>
+        <v>3:16</v>
       </c>
       <c r="H35" t="str">
-        <v>Beck</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H36" t="str">
-        <v>The Offspring</v>
+        <v>Beck</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-01</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:10</v>
+        <v>2:57</v>
       </c>
       <c r="H37" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>The Offspring</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-01</v>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:10</v>
+        <v>4:10</v>
       </c>
       <c r="H38" t="str">
-        <v>Jason Derulo</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-01</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:52</v>
+        <v>2:10</v>
       </c>
       <c r="H39" t="str">
-        <v>lights</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-01</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H40" t="str">
-        <v>Telenova</v>
+        <v>lights</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-01</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:32</v>
+        <v>3:50</v>
       </c>
       <c r="H41" t="str">
-        <v>Marcin</v>
+        <v>Telenova</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-01</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:27</v>
+        <v>5:32</v>
       </c>
       <c r="H42" t="str">
-        <v>We Three</v>
+        <v>Marcin</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:01</v>
+        <v>4:27</v>
       </c>
       <c r="H43" t="str">
-        <v>Timebelle Official</v>
+        <v>We Three</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H44" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H45" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-01</v>
@@ -2126,10 +2126,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H46" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-01</v>
@@ -2164,10 +2164,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H47" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-01</v>
@@ -2202,10 +2202,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H48" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-01</v>
@@ -2240,10 +2240,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H49" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-01</v>
@@ -2278,10 +2278,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H50" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-01</v>
@@ -2316,10 +2316,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H51" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-01</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H52" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-01</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H53" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:37</v>
+        <v>3:46</v>
       </c>
       <c r="H54" t="str">
-        <v>Bella White</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-01</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H55" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-01</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H56" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-01</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:10</v>
+        <v>3:54</v>
       </c>
       <c r="H57" t="str">
-        <v>Parker McCollum</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-01</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H58" t="str">
-        <v>Matt Hansen</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H59" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-01</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H61" t="str">
-        <v>Tauren Wells</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-01</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H62" t="str">
-        <v>Maiah Manser</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-01</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H63" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-01</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H64" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-01</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H65" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-01</v>
@@ -2889,7 +2889,7 @@
         <v>3:13</v>
       </c>
       <c r="H66" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-01</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H67" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-01</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:14</v>
+        <v>3:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Harry Styles</v>
+        <v>CAIN</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-01</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:59</v>
+        <v>5:14</v>
       </c>
       <c r="H69" t="str">
-        <v>Lana Lubany</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-01</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="H70" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H71" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="H72" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-01</v>
@@ -3152,10 +3152,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H73" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B74" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-01</v>
@@ -3190,10 +3190,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H74" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H75" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-01</v>
@@ -3266,10 +3266,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H76" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-01</v>
@@ -3304,10 +3304,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B78" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-01</v>
@@ -3342,10 +3342,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="H78" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H79" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="H80" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-01</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="H81" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-01</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="H82" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-01</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="H83" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-01</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="H84" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-01</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H85" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-01</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="H86" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-01</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="H87" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-01</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="H88" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-01</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="H89" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-01</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H90" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-01</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H91" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-01</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H92" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-01</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="H93" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-01</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-01</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="H95" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-01</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H96" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-01</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H97" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-01</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="H98" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-01</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H99" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-01</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="H100" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-01</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="H101" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Body</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/body/1871258331</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>OCTANE</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:35</v>
+        <v>3:11</v>
       </c>
       <c r="H102" t="str">
-        <v>Don Toliver</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/body/1871258329</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Body - Don Toliver</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dandelion</v>
+        <v>Body</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
+        <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Dandelion</v>
+        <v>OCTANE</v>
       </c>
       <c r="G103" t="str">
-        <v>4:00</v>
+        <v>2:35</v>
       </c>
       <c r="H103" t="str">
-        <v>Ella Langley</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
+        <v>https://music.apple.com/us/album/body/1871258329</v>
       </c>
       <c r="L103" t="str">
-        <v>Dandelion - Ella Langley</v>
+        <v>Body - Don Toliver</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>LIGHTS GO OUT</v>
+        <v>Dandelion</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
+        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>LIGHTS GO OUT - Single</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>2:38</v>
+        <v>4:00</v>
       </c>
       <c r="H104" t="str">
-        <v>John Summit</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
+        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>LIGHTS GO OUT - John Summit</v>
+        <v>Dandelion - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Great Divide</v>
+        <v>LIGHTS GO OUT</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
+        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Great Divide</v>
+        <v>LIGHTS GO OUT - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>5:17</v>
+        <v>2:38</v>
       </c>
       <c r="H105" t="str">
-        <v>Noah Kahan</v>
+        <v>John Summit</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
+        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
       </c>
       <c r="L105" t="str">
-        <v>The Great Divide - Noah Kahan</v>
+        <v>LIGHTS GO OUT - John Summit</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>tristón</v>
+        <v>The Great Divide</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
+        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>tristón - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G106" t="str">
-        <v>3:36</v>
+        <v>5:17</v>
       </c>
       <c r="H106" t="str">
-        <v>Fuerza Regida</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
+        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
       </c>
       <c r="L106" t="str">
-        <v>tristón - Fuerza Regida</v>
+        <v>The Great Divide - Noah Kahan</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Feed the Streets</v>
+        <v>tristón</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
+        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Feed the Streets - Single</v>
+        <v>tristón - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:58</v>
+        <v>3:36</v>
       </c>
       <c r="H107" t="str">
-        <v>Rod Wave</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
+        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
       </c>
       <c r="L107" t="str">
-        <v>Feed the Streets - Rod Wave</v>
+        <v>tristón - Fuerza Regida</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Did This To Myself</v>
+        <v>Feed the Streets</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Distracted</v>
+        <v>Feed the Streets - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:30</v>
+        <v>2:58</v>
       </c>
       <c r="H108" t="str">
-        <v>Thundercat</v>
+        <v>Rod Wave</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
       </c>
       <c r="L108" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>Feed the Streets - Rod Wave</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>For Hire</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>For Hire - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G109" t="str">
-        <v>3:44</v>
+        <v>2:30</v>
       </c>
       <c r="H109" t="str">
-        <v>People I’ve Met</v>
+        <v>Thundercat</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L109" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>McArthur</v>
+        <v>For Hire</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>McArthur - Single</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:51</v>
+        <v>3:44</v>
       </c>
       <c r="H110" t="str">
-        <v>HARDY</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L110" t="str">
-        <v>McArthur - HARDY</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Debris</v>
+        <v>McArthur</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:55</v>
+        <v>3:51</v>
       </c>
       <c r="H111" t="str">
-        <v>Labrinth</v>
+        <v>HARDY</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L111" t="str">
-        <v>Debris - Labrinth</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Debris</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G112" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H112" t="str">
-        <v>Militarie Gun</v>
+        <v>Labrinth</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L112" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G113" t="str">
-        <v>4:38</v>
+        <v>3:25</v>
       </c>
       <c r="H113" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>1+1</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>1+1 - Single</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:06</v>
+        <v>4:38</v>
       </c>
       <c r="H114" t="str">
-        <v>Maluma</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L114" t="str">
-        <v>1+1 - Maluma</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>1+1</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:08</v>
+        <v>3:06</v>
       </c>
       <c r="H115" t="str">
-        <v>MJ Cole</v>
+        <v>Maluma</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L115" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Two Car Garage</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:02</v>
+        <v>3:08</v>
       </c>
       <c r="H116" t="str">
-        <v>Jon Bellion</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L116" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>fml .</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:40</v>
+        <v>3:02</v>
       </c>
       <c r="H117" t="str">
-        <v>fakemink</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L117" t="str">
-        <v>fml . - fakemink</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Faked It All The Time</v>
+        <v>fml .</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G118" t="str">
-        <v>3:01</v>
+        <v>2:40</v>
       </c>
       <c r="H118" t="str">
-        <v>Allie Sherlock</v>
+        <v>fakemink</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L118" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>House of the Rising Sun</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:08</v>
+        <v>3:01</v>
       </c>
       <c r="H119" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L119" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Lorelei</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Lorelei - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:35</v>
+        <v>3:08</v>
       </c>
       <c r="H120" t="str">
-        <v>ERNEST</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L120" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Free</v>
+        <v>Lorelei</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Free - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:56</v>
+        <v>2:35</v>
       </c>
       <c r="H121" t="str">
-        <v>SLANDER</v>
+        <v>ERNEST</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L121" t="str">
-        <v>Free - SLANDER</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>professional heartbreaker</v>
+        <v>Free</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:55</v>
+        <v>3:56</v>
       </c>
       <c r="H122" t="str">
-        <v>Artemas</v>
+        <v>SLANDER</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L122" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>tell me what you want</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ACT II</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:56</v>
+        <v>2:55</v>
       </c>
       <c r="H123" t="str">
-        <v>Sasha Keable</v>
+        <v>Artemas</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L123" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Aguas</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Aguas - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>2:52</v>
+        <v>3:56</v>
       </c>
       <c r="H124" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L124" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Ants In My Room</v>
+        <v>Aguas</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H125" t="str">
-        <v>Carter Vail</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L125" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Baddie</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Bohemio</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H126" t="str">
-        <v>Nicky Jam</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L126" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>Baddie</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>Bohemio</v>
       </c>
       <c r="G127" t="str">
-        <v>3:51</v>
+        <v>3:11</v>
       </c>
       <c r="H127" t="str">
-        <v>Tems</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L127" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:16</v>
+        <v>3:51</v>
       </c>
       <c r="H128" t="str">
-        <v>Fred again..</v>
+        <v>Tems</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L128" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:50</v>
+        <v>3:16</v>
       </c>
       <c r="H129" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Fred again..</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:33</v>
+        <v>3:50</v>
       </c>
       <c r="H130" t="str">
-        <v>Tyler Ballgame</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L130" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Liars Tale</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Liars Tale - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G131" t="str">
-        <v>3:17</v>
+        <v>3:33</v>
       </c>
       <c r="H131" t="str">
-        <v>Kneecap</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L131" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:38</v>
+        <v>3:17</v>
       </c>
       <c r="H132" t="str">
-        <v>Motionless In White</v>
+        <v>Kneecap</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L132" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Wake Up Calling</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:49</v>
+        <v>4:38</v>
       </c>
       <c r="H133" t="str">
-        <v>Papa Roach</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L133" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>HIGH</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:23</v>
+        <v>3:49</v>
       </c>
       <c r="H134" t="str">
-        <v>Magnolia Park</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L134" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Villain</v>
+        <v>HIGH</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Reflections</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G135" t="str">
-        <v>3:53</v>
+        <v>3:23</v>
       </c>
       <c r="H135" t="str">
-        <v>From Ashes to New</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L135" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Villain</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>Reflections</v>
       </c>
       <c r="G136" t="str">
-        <v>3:00</v>
+        <v>3:53</v>
       </c>
       <c r="H136" t="str">
-        <v>Caleb Chan</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L136" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Residue</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G137" t="str">
-        <v>3:28</v>
+        <v>3:00</v>
       </c>
       <c r="H137" t="str">
-        <v>A. G. Cook</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L137" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Residue</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G138" t="str">
-        <v>2:12</v>
+        <v>3:28</v>
       </c>
       <c r="H138" t="str">
-        <v>Joyce Manor</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L138" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Starlight</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Everything Glows</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G139" t="str">
-        <v>3:21</v>
+        <v>2:12</v>
       </c>
       <c r="H139" t="str">
-        <v>Cannons</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L139" t="str">
-        <v>Starlight - Cannons</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Dandelion</v>
+        <v>Starlight</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G140" t="str">
-        <v>3:14</v>
+        <v>3:21</v>
       </c>
       <c r="H140" t="str">
-        <v>Dogpark</v>
+        <v>Cannons</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L140" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>THEMSELVES</v>
+        <v>Dandelion</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BACKWARD</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G141" t="str">
-        <v>2:46</v>
+        <v>3:14</v>
       </c>
       <c r="H141" t="str">
-        <v>Jordan Ward</v>
+        <v>Dogpark</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L141" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>High Maintenance</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Miracle Mile</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G142" t="str">
-        <v>2:24</v>
+        <v>2:46</v>
       </c>
       <c r="H142" t="str">
-        <v>Paul Russell</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L142" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Trackhawk</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Da Realest</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G143" t="str">
-        <v>1:59</v>
+        <v>2:24</v>
       </c>
       <c r="H143" t="str">
-        <v>Babyfxce E</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L143" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Wheel Man</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Xavier</v>
+        <v>Da Realest</v>
       </c>
       <c r="G144" t="str">
-        <v>3:05</v>
+        <v>1:59</v>
       </c>
       <c r="H144" t="str">
-        <v>xaviersobased</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L144" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Natural Disaster</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Xavier</v>
       </c>
       <c r="G145" t="str">
-        <v>3:02</v>
+        <v>3:05</v>
       </c>
       <c r="H145" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L145" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Prettier</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Prettier - Single</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H146" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L146" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Prettier</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H147" t="str">
-        <v>NLE Choppa</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L147" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Die To Fall</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:20</v>
+        <v>3:21</v>
       </c>
       <c r="H148" t="str">
-        <v>The Maine</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L148" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:58</v>
+        <v>3:20</v>
       </c>
       <c r="H149" t="str">
-        <v>Steve Aoki</v>
+        <v>The Maine</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Slow Burn</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Still There’s a Glow</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:14</v>
+        <v>2:58</v>
       </c>
       <c r="H150" t="str">
-        <v>Sweet Pill</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L150" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Too Late</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/too-late/1866685876</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Too Late - EP</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G151" t="str">
-        <v>2:56</v>
+        <v>2:14</v>
       </c>
       <c r="H151" t="str">
-        <v>Hunter Hayes</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/too-late/1866685875</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L151" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Too Late</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/too-late/1866685876</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Too Late - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H152" t="str">
-        <v>i-dle</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/too-late/1866685875</v>
       </c>
       <c r="L152" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>1:55</v>
+        <v>2:50</v>
       </c>
       <c r="H153" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>i-dle</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L153" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>RIDIN</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>RIDIN - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G154" t="str">
-        <v>2:00</v>
+        <v>1:55</v>
       </c>
       <c r="H154" t="str">
-        <v>Tokischa</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L154" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>POSSESSION</v>
+        <v>RIDIN</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>POSSESSION - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H155" t="str">
-        <v>Melanie Martinez</v>
+        <v>Tokischa</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L155" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Poema</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Poema - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:14</v>
+        <v>3:07</v>
       </c>
       <c r="H156" t="str">
-        <v>Óscar Maydon</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L156" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Live Without</v>
+        <v>Poema</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:55</v>
+        <v>3:14</v>
       </c>
       <c r="H157" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L157" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>FANÁTICO</v>
+        <v>Live Without</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G158" t="str">
-        <v>3:55</v>
+        <v>2:55</v>
       </c>
       <c r="H158" t="str">
-        <v>Blessd</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L158" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Frozen Lake</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:29</v>
+        <v>3:55</v>
       </c>
       <c r="H159" t="str">
-        <v>VOILÀ</v>
+        <v>Blessd</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L159" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:45</v>
+        <v>3:29</v>
       </c>
       <c r="H160" t="str">
-        <v>VEDO</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H161" t="str">
-        <v>Chris Lorenzo</v>
+        <v>VEDO</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>It’s Like That</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:20</v>
+        <v>3:32</v>
       </c>
       <c r="H162" t="str">
-        <v>The Black Crowes</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L162" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>A.S.A.P.</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G163" t="str">
-        <v>2:48</v>
+        <v>3:20</v>
       </c>
       <c r="H163" t="str">
-        <v>Mýa</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L163" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Once I Say</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>PASSION</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>Terrace Martin</v>
+        <v>Mýa</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L164" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>believer</v>
+        <v>Once I Say</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>believer - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G165" t="str">
-        <v>2:57</v>
+        <v>3:21</v>
       </c>
       <c r="H165" t="str">
-        <v>Yuna</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L165" t="str">
-        <v>believer - Yuna</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I Envy The Wind</v>
+        <v>believer</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:51</v>
+        <v>2:57</v>
       </c>
       <c r="H166" t="str">
-        <v>Molly Parden</v>
+        <v>Yuna</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L166" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>3:51</v>
       </c>
       <c r="H167" t="str">
-        <v>Bre Kennedy</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L167" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Daysa</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Daysa - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G168" t="str">
-        <v>4:36</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L168" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fabulous</v>
+        <v>Daysa</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Fabulous - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:33</v>
+        <v>4:36</v>
       </c>
       <c r="H169" t="str">
-        <v>MEEK</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L169" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Fabulous</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:22</v>
+        <v>2:33</v>
       </c>
       <c r="H170" t="str">
-        <v>RUBIO</v>
+        <v>MEEK</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>brainchem</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>brainchem - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:28</v>
+        <v>3:22</v>
       </c>
       <c r="H171" t="str">
-        <v>EMJAY</v>
+        <v>RUBIO</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L171" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>brainchem</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>With No Due Respect</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:48</v>
+        <v>2:28</v>
       </c>
       <c r="H172" t="str">
-        <v>Foggieraw</v>
+        <v>EMJAY</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L172" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Giants</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Giants - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G173" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H173" t="str">
-        <v>Picture This</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L173" t="str">
-        <v>Giants - Picture This</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Scooby</v>
+        <v>Giants</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Scooby - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H174" t="str">
-        <v>corook</v>
+        <v>Picture This</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L174" t="str">
-        <v>Scooby - corook</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>La Racha</v>
+        <v>Scooby</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>La Racha - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:48</v>
+        <v>3:41</v>
       </c>
       <c r="H175" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>corook</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L175" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>So Am I</v>
+        <v>La Racha</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H176" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L176" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>best thing</v>
+        <v>So Am I</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>best thing - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G177" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H177" t="str">
-        <v>WRABEL</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L177" t="str">
-        <v>best thing - WRABEL</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Count It Back</v>
+        <v>best thing</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Magic Boy</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:52</v>
+        <v>4:27</v>
       </c>
       <c r="H178" t="str">
-        <v>Bartees Strange</v>
+        <v>WRABEL</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L178" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Good Girl</v>
+        <v>Count It Back</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Good Girl - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G179" t="str">
-        <v>4:23</v>
+        <v>2:52</v>
       </c>
       <c r="H179" t="str">
-        <v>Paris Paloma</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L179" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>MY REVIVAL</v>
+        <v>Good Girl</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:34</v>
+        <v>4:23</v>
       </c>
       <c r="H180" t="str">
-        <v>MORGXN</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L180" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Run My Way</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Run My Way - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G181" t="str">
-        <v>2:44</v>
+        <v>3:34</v>
       </c>
       <c r="H181" t="str">
-        <v>December 10</v>
+        <v>MORGXN</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L181" t="str">
-        <v>Run My Way - December 10</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Cold Night</v>
+        <v>Run My Way</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Cold Night - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:12</v>
+        <v>2:44</v>
       </c>
       <c r="H182" t="str">
-        <v>HANA</v>
+        <v>December 10</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L182" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Away With The Fairies</v>
+        <v>Cold Night</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:28</v>
+        <v>3:12</v>
       </c>
       <c r="H183" t="str">
-        <v>LUNA</v>
+        <v>HANA</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L183" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fragile</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Fragile - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:10</v>
+        <v>2:28</v>
       </c>
       <c r="H184" t="str">
-        <v>Anajah</v>
+        <v>LUNA</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L184" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Slow Dancin'</v>
+        <v>Fragile</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:04</v>
+        <v>3:10</v>
       </c>
       <c r="H185" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Anajah</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L185" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:04</v>
+        <v>2:04</v>
       </c>
       <c r="H186" t="str">
-        <v>Lily Meola</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L186" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>More Of What Matters</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:41</v>
+        <v>3:04</v>
       </c>
       <c r="H187" t="str">
-        <v>Jamey Johnson</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L187" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Is This The Real You</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>ONE</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:46</v>
+        <v>3:41</v>
       </c>
       <c r="H188" t="str">
-        <v>Sevendust</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L188" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Hud</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>DREAMCRUSH</v>
+        <v>ONE</v>
       </c>
       <c r="G189" t="str">
-        <v>4:46</v>
+        <v>3:46</v>
       </c>
       <c r="H189" t="str">
-        <v>MØL</v>
+        <v>Sevendust</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L189" t="str">
-        <v>Hud - MØL</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Ego Death</v>
+        <v>Hud</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Ego Death - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G190" t="str">
-        <v>2:12</v>
+        <v>4:46</v>
       </c>
       <c r="H190" t="str">
-        <v>Atreyu</v>
+        <v>MØL</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L190" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Ego Death</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:05</v>
+        <v>2:12</v>
       </c>
       <c r="H191" t="str">
-        <v>EJ Jones</v>
+        <v>Atreyu</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L191" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>5:50</v>
+        <v>4:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Lane 8</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L192" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Misbehave</v>
+        <v>Disappear</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Misbehave - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G193" t="str">
-        <v>3:43</v>
+        <v>5:50</v>
       </c>
       <c r="H193" t="str">
-        <v>Aluna</v>
+        <v>Lane 8</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L193" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Club Bizarre</v>
+        <v>Misbehave</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:47</v>
+        <v>3:43</v>
       </c>
       <c r="H194" t="str">
-        <v>Alok</v>
+        <v>Aluna</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L194" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Fly</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Fly - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H195" t="str">
-        <v>Stephen Stanley</v>
+        <v>Alok</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L195" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>ily anyway</v>
+        <v>Fly</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>ily anyway - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L196" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>ily anyway</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Nellene - EP</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:35</v>
+        <v>3:05</v>
       </c>
       <c r="H197" t="str">
-        <v>Deloyd Elze</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L197" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Kiss Big</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Kiss Big</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G198" t="str">
-        <v>3:41</v>
+        <v>3:35</v>
       </c>
       <c r="H198" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L198" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>praxis</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G199" t="str">
-        <v>3:28</v>
+        <v>3:41</v>
       </c>
       <c r="H199" t="str">
-        <v>Lauren Auder</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L199" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>House</v>
+        <v>praxis</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>House - Single</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G200" t="str">
-        <v>2:30</v>
+        <v>3:28</v>
       </c>
       <c r="H200" t="str">
-        <v>Connie Converse</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L200" t="str">
-        <v>House - Connie Converse</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>House</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>House - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:57</v>
+        <v>2:30</v>
       </c>
       <c r="H201" t="str">
-        <v>Yumi Zouma</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L201" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Brincar</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D202" t="str">
         <v>2026-02-01</v>
@@ -8051,68 +8051,106 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>JET LAG - EP</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G202" t="str">
-        <v>3:06</v>
+        <v>3:57</v>
       </c>
       <c r="H202" t="str">
-        <v>J Castle</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L202" t="str">
-        <v>Brincar - J Castle</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H203" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
         <v>Quién</v>
       </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D203" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
+      <c r="D204" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G203" t="str">
+      <c r="G204" t="str">
         <v>4:19</v>
       </c>
-      <c r="H203" t="str">
+      <c r="H204" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K203" t="str">
+      <c r="K204" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L203" t="str">
+      <c r="L204" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלוש ציפורים דמיון חופשי</v>
+        <v>שלוש ציפורים – דמיון חופשי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-01</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלוש ציפורים דמיון חופשי</v>
+        <v>שלוש ציפורים – דמיון חופשי</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:58</v>
@@ -515,7 +515,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:08</v>
@@ -553,7 +553,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:38</v>
@@ -591,7 +591,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B6" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:50</v>
@@ -933,7 +933,7 @@
         <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:52</v>
@@ -971,7 +971,7 @@
         <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:33</v>

--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלוש ציפורים – דמיון חופשי</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-01</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%a9-%d7%a6%d7%99%d7%a4%d7%95%d7%a8%d7%99%d7%9d-%d7%93%d7%9e%d7%99%d7%95%d7%9f-%d7%97%d7%95%d7%a4%d7%a9%d7%99/</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"דמיון חופשי” של יצחק קלפטר הוא מן השירים שבהם הפשטות הלירית נושאת על גבה עומק רגשי גדול. זהו שיר על אהבה שאינה מתממשת, על פער בין תשוקה למציאות, ועל המקום שבו הדמיון הופך למרחב מפלט – אך גם למרחב של</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:58</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>The Warning</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלוש ציפורים – דמיון חופשי</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:58</v>
+        <v>5:08</v>
       </c>
       <c r="H3" t="str">
-        <v>The Warning</v>
+        <v>The Offspring</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-01</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>5:08</v>
+        <v>4:38</v>
       </c>
       <c r="H4" t="str">
-        <v>The Offspring</v>
+        <v>Roxette</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-01</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:38</v>
+        <v>3:50</v>
       </c>
       <c r="H5" t="str">
-        <v>Roxette</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-01</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:50</v>
+        <v>3:10</v>
       </c>
       <c r="H6" t="str">
-        <v>Jessie Ware</v>
+        <v>Joseph</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-01</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:10</v>
+        <v>2:44</v>
       </c>
       <c r="H7" t="str">
-        <v>Joseph</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-01</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:44</v>
+        <v>2:57</v>
       </c>
       <c r="H8" t="str">
-        <v>Dean Lewis</v>
+        <v>Take That</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-01</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:57</v>
+        <v>2:39</v>
       </c>
       <c r="H9" t="str">
-        <v>Take That</v>
+        <v>The Cure</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-01</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:39</v>
+        <v>3:07</v>
       </c>
       <c r="H10" t="str">
-        <v>The Cure</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-01</v>
@@ -796,10 +796,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:07</v>
+        <v>4:47</v>
       </c>
       <c r="H11" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-01</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:47</v>
+        <v>3:22</v>
       </c>
       <c r="H12" t="str">
-        <v>Paris Paloma</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:22</v>
+        <v>2:48</v>
       </c>
       <c r="H13" t="str">
-        <v>Zara Larsson</v>
+        <v>only the poets</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H14" t="str">
-        <v>only the poets</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-01</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:52</v>
+        <v>3:33</v>
       </c>
       <c r="H15" t="str">
-        <v>Katelyn Tarver</v>
+        <v>David Guetta</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-01</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:33</v>
+        <v>2:41</v>
       </c>
       <c r="H16" t="str">
-        <v>David Guetta</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-01</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:41</v>
+        <v>4:01</v>
       </c>
       <c r="H17" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-01</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:01</v>
+        <v>3:16</v>
       </c>
       <c r="H18" t="str">
-        <v>Ella Langley</v>
+        <v>Dogpark</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-01</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:16</v>
+        <v>3:03</v>
       </c>
       <c r="H19" t="str">
-        <v>Dogpark</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-01</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:03</v>
+        <v>2:41</v>
       </c>
       <c r="H20" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>ERNEST</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:41</v>
+        <v>3:05</v>
       </c>
       <c r="H21" t="str">
-        <v>ERNEST</v>
+        <v>Labrinth</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H22" t="str">
-        <v>Labrinth</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:46</v>
+        <v>3:32</v>
       </c>
       <c r="H23" t="str">
-        <v>Grace VanderWaal</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:32</v>
+        <v>3:42</v>
       </c>
       <c r="H24" t="str">
-        <v>VOILÀ</v>
+        <v>Cannons</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:42</v>
+        <v>2:38</v>
       </c>
       <c r="H25" t="str">
-        <v>Cannons</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:38</v>
+        <v>3:10</v>
       </c>
       <c r="H26" t="str">
-        <v>Kylie Morgan</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:10</v>
+        <v>3:57</v>
       </c>
       <c r="H27" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:57</v>
+        <v>2:19</v>
       </c>
       <c r="H28" t="str">
-        <v>Willie Nelson</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H29" t="str">
-        <v>JeremyCampMusic</v>
+        <v>India Martínez</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:04</v>
+        <v>2:16</v>
       </c>
       <c r="H30" t="str">
-        <v>India Martínez</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:16</v>
+        <v>5:58</v>
       </c>
       <c r="H31" t="str">
-        <v>Chelsea Cutler</v>
+        <v>TINI</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>5:58</v>
+        <v>3:26</v>
       </c>
       <c r="H32" t="str">
-        <v>TINI</v>
+        <v>Charley</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-01</v>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:26</v>
+        <v>4:05</v>
       </c>
       <c r="H33" t="str">
-        <v>Charley</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-01</v>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:05</v>
+        <v>3:16</v>
       </c>
       <c r="H34" t="str">
-        <v>Demi Lovato</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-01</v>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:16</v>
+        <v>3:14</v>
       </c>
       <c r="H35" t="str">
-        <v>Teddy Swims</v>
+        <v>Beck</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:14</v>
+        <v>2:57</v>
       </c>
       <c r="H36" t="str">
-        <v>Beck</v>
+        <v>The Offspring</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-01</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:57</v>
+        <v>4:10</v>
       </c>
       <c r="H37" t="str">
-        <v>The Offspring</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-01</v>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:10</v>
+        <v>2:10</v>
       </c>
       <c r="H38" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-01</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:10</v>
+        <v>3:52</v>
       </c>
       <c r="H39" t="str">
-        <v>Jason Derulo</v>
+        <v>lights</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-01</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:52</v>
+        <v>3:50</v>
       </c>
       <c r="H40" t="str">
-        <v>lights</v>
+        <v>Telenova</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-01</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:50</v>
+        <v>5:32</v>
       </c>
       <c r="H41" t="str">
-        <v>Telenova</v>
+        <v>Marcin</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>5:32</v>
+        <v>4:27</v>
       </c>
       <c r="H42" t="str">
-        <v>Marcin</v>
+        <v>We Three</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:27</v>
+        <v>3:01</v>
       </c>
       <c r="H43" t="str">
-        <v>We Three</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:01</v>
+        <v>3:20</v>
       </c>
       <c r="H44" t="str">
-        <v>Timebelle Official</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:20</v>
+        <v>3:34</v>
       </c>
       <c r="H45" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-01</v>
@@ -2126,10 +2126,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:34</v>
+        <v>4:01</v>
       </c>
       <c r="H46" t="str">
-        <v>Clinton Kane</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-01</v>
@@ -2164,10 +2164,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:01</v>
+        <v>3:24</v>
       </c>
       <c r="H47" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-01</v>
@@ -2202,10 +2202,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:24</v>
+        <v>5:52</v>
       </c>
       <c r="H48" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-01</v>
@@ -2240,10 +2240,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:52</v>
+        <v>5:01</v>
       </c>
       <c r="H49" t="str">
-        <v>Harry Styles</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-01</v>
@@ -2278,10 +2278,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>5:01</v>
+        <v>4:12</v>
       </c>
       <c r="H50" t="str">
-        <v>Neal Francis</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-01</v>
@@ -2316,10 +2316,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:12</v>
+        <v>3:59</v>
       </c>
       <c r="H51" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-01</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:59</v>
+        <v>2:56</v>
       </c>
       <c r="H52" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:56</v>
+        <v>3:46</v>
       </c>
       <c r="H53" t="str">
-        <v>Cliff Richard</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:46</v>
+        <v>4:37</v>
       </c>
       <c r="H54" t="str">
-        <v>Jessie Ware</v>
+        <v>Bella White</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-01</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:37</v>
+        <v>4:06</v>
       </c>
       <c r="H55" t="str">
-        <v>Bella White</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-01</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:06</v>
+        <v>3:54</v>
       </c>
       <c r="H56" t="str">
-        <v>Ryan Wright</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-01</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:54</v>
+        <v>4:10</v>
       </c>
       <c r="H57" t="str">
-        <v>Dove Cameron</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-01</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:10</v>
+        <v>3:26</v>
       </c>
       <c r="H58" t="str">
-        <v>Parker McCollum</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H59" t="str">
-        <v>Matt Hansen</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-01</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H61" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-01</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:01</v>
+        <v>3:05</v>
       </c>
       <c r="H62" t="str">
-        <v>Tauren Wells</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-01</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:05</v>
+        <v>2:27</v>
       </c>
       <c r="H63" t="str">
-        <v>Maiah Manser</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-01</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:27</v>
+        <v>2:34</v>
       </c>
       <c r="H64" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-01</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H65" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-01</v>
@@ -2889,7 +2889,7 @@
         <v>3:13</v>
       </c>
       <c r="H66" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-01</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Louis Tomlinson</v>
+        <v>CAIN</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-01</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:08</v>
+        <v>5:14</v>
       </c>
       <c r="H68" t="str">
-        <v>CAIN</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-01</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>5:14</v>
+        <v>2:59</v>
       </c>
       <c r="H69" t="str">
-        <v>Harry Styles</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-01</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:59</v>
+        <v>4:21</v>
       </c>
       <c r="H70" t="str">
-        <v>Lana Lubany</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:21</v>
+        <v>4:09</v>
       </c>
       <c r="H71" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:09</v>
+        <v>2:34</v>
       </c>
       <c r="H72" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B73" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-01</v>
@@ -3152,10 +3152,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:34</v>
+        <v>3:10</v>
       </c>
       <c r="H73" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B74" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-01</v>
@@ -3190,10 +3190,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H74" t="str">
-        <v>Olivia Dean</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H75" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-01</v>
@@ -3266,10 +3266,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H76" t="str">
-        <v>The Avett Brothers</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B77" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-01</v>
@@ -3304,10 +3304,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:21</v>
+        <v>7:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Jordana Bryant</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B78" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-01</v>
@@ -3342,10 +3342,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>7:21</v>
+        <v>3:17</v>
       </c>
       <c r="H78" t="str">
-        <v>Katy Perry</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:17</v>
+        <v>3:45</v>
       </c>
       <c r="H79" t="str">
-        <v>Lauren Watkins</v>
+        <v>Tones And I</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:45</v>
+        <v>3:57</v>
       </c>
       <c r="H80" t="str">
-        <v>Tones And I</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-01</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:57</v>
+        <v>3:03</v>
       </c>
       <c r="H81" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-01</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:03</v>
+        <v>4:27</v>
       </c>
       <c r="H82" t="str">
-        <v>Charlie Puth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-01</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:27</v>
+        <v>4:34</v>
       </c>
       <c r="H83" t="str">
-        <v>Chappell Roan</v>
+        <v>Armik</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-01</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:34</v>
+        <v>2:54</v>
       </c>
       <c r="H84" t="str">
-        <v>Armik</v>
+        <v>LØLØ</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-01</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:54</v>
+        <v>3:25</v>
       </c>
       <c r="H85" t="str">
-        <v>LØLØ</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-01</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:25</v>
+        <v>2:01</v>
       </c>
       <c r="H86" t="str">
-        <v>Tenille Townes</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-01</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:01</v>
+        <v>2:25</v>
       </c>
       <c r="H87" t="str">
-        <v>Alan Walker</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-01</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:25</v>
+        <v>1:14</v>
       </c>
       <c r="H88" t="str">
-        <v>Charli xcx</v>
+        <v>Labrinth</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-01</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>1:14</v>
+        <v>2:59</v>
       </c>
       <c r="H89" t="str">
-        <v>Labrinth</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-01</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:59</v>
+        <v>2:29</v>
       </c>
       <c r="H90" t="str">
-        <v>Charlie Puth</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-01</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:29</v>
+        <v>2:34</v>
       </c>
       <c r="H91" t="str">
-        <v>Girl Tones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-01</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:34</v>
+        <v>3:48</v>
       </c>
       <c r="H92" t="str">
-        <v>Jagwar Twin</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-01</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:48</v>
+        <v>3:32</v>
       </c>
       <c r="H93" t="str">
-        <v>Caroline Jones</v>
+        <v>The Beaches</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-01</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:32</v>
+        <v>3:49</v>
       </c>
       <c r="H94" t="str">
-        <v>The Beaches</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-01</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:49</v>
+        <v>4:28</v>
       </c>
       <c r="H95" t="str">
-        <v>Dolly Parton</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-01</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:28</v>
+        <v>3:37</v>
       </c>
       <c r="H96" t="str">
-        <v>Madison Beer</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-01</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:37</v>
+        <v>3:35</v>
       </c>
       <c r="H97" t="str">
-        <v>Ty Myers</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-01</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:35</v>
+        <v>2:31</v>
       </c>
       <c r="H98" t="str">
-        <v>Megan Moroney</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-01</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:31</v>
+        <v>3:21</v>
       </c>
       <c r="H99" t="str">
-        <v>Julia Cole Music</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-01</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:21</v>
+        <v>5:24</v>
       </c>
       <c r="H100" t="str">
-        <v>Lily Allen</v>
+        <v>Nickless</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-01</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:24</v>
+        <v>3:11</v>
       </c>
       <c r="H101" t="str">
-        <v>Nickless</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Body</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>OCTANE</v>
       </c>
       <c r="G102" t="str">
-        <v>3:11</v>
+        <v>2:35</v>
       </c>
       <c r="H102" t="str">
-        <v>Peach PRC</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/body/1871258329</v>
       </c>
       <c r="L102" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Body - Don Toliver</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Body</v>
+        <v>Dandelion</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/body/1871258331</v>
+        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>OCTANE</v>
+        <v>Dandelion</v>
       </c>
       <c r="G103" t="str">
-        <v>2:35</v>
+        <v>4:00</v>
       </c>
       <c r="H103" t="str">
-        <v>Don Toliver</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/body/1871258329</v>
+        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
       </c>
       <c r="L103" t="str">
-        <v>Body - Don Toliver</v>
+        <v>Dandelion - Ella Langley</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Dandelion</v>
+        <v>LIGHTS GO OUT</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
+        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>LIGHTS GO OUT - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>4:00</v>
+        <v>2:38</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>John Summit</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
+        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
       </c>
       <c r="L104" t="str">
-        <v>Dandelion - Ella Langley</v>
+        <v>LIGHTS GO OUT - John Summit</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>LIGHTS GO OUT</v>
+        <v>The Great Divide</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
+        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>LIGHTS GO OUT - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G105" t="str">
-        <v>2:38</v>
+        <v>5:17</v>
       </c>
       <c r="H105" t="str">
-        <v>John Summit</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
+        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
       </c>
       <c r="L105" t="str">
-        <v>LIGHTS GO OUT - John Summit</v>
+        <v>The Great Divide - Noah Kahan</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>The Great Divide</v>
+        <v>tristón</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
+        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide</v>
+        <v>tristón - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>5:17</v>
+        <v>3:36</v>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
+        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
       </c>
       <c r="L106" t="str">
-        <v>The Great Divide - Noah Kahan</v>
+        <v>tristón - Fuerza Regida</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>tristón</v>
+        <v>Feed the Streets</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
+        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>tristón - Single</v>
+        <v>Feed the Streets - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H107" t="str">
-        <v>Fuerza Regida</v>
+        <v>Rod Wave</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
+        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
       </c>
       <c r="L107" t="str">
-        <v>tristón - Fuerza Regida</v>
+        <v>Feed the Streets - Rod Wave</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Feed the Streets</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Feed the Streets - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G108" t="str">
-        <v>2:58</v>
+        <v>2:30</v>
       </c>
       <c r="H108" t="str">
-        <v>Rod Wave</v>
+        <v>Thundercat</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L108" t="str">
-        <v>Feed the Streets - Rod Wave</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>I Did This To Myself</v>
+        <v>For Hire</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Distracted</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:30</v>
+        <v>3:44</v>
       </c>
       <c r="H109" t="str">
-        <v>Thundercat</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L109" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>For Hire</v>
+        <v>McArthur</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>For Hire - Single</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:44</v>
+        <v>3:51</v>
       </c>
       <c r="H110" t="str">
-        <v>People I’ve Met</v>
+        <v>HARDY</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L110" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>McArthur</v>
+        <v>Debris</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>McArthur - Single</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G111" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H111" t="str">
-        <v>HARDY</v>
+        <v>Labrinth</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L111" t="str">
-        <v>McArthur - HARDY</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Debris</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G112" t="str">
-        <v>2:55</v>
+        <v>3:25</v>
       </c>
       <c r="H112" t="str">
-        <v>Labrinth</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L112" t="str">
-        <v>Debris - Labrinth</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:25</v>
+        <v>4:38</v>
       </c>
       <c r="H113" t="str">
-        <v>Militarie Gun</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L113" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>1+1</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:38</v>
+        <v>3:06</v>
       </c>
       <c r="H114" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Maluma</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L114" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>1+1</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>1+1 - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:06</v>
+        <v>3:08</v>
       </c>
       <c r="H115" t="str">
-        <v>Maluma</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L115" t="str">
-        <v>1+1 - Maluma</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:08</v>
+        <v>3:02</v>
       </c>
       <c r="H116" t="str">
-        <v>MJ Cole</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L116" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Two Car Garage</v>
+        <v>fml .</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G117" t="str">
-        <v>3:02</v>
+        <v>2:40</v>
       </c>
       <c r="H117" t="str">
-        <v>Jon Bellion</v>
+        <v>fakemink</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L117" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>fml .</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:40</v>
+        <v>3:01</v>
       </c>
       <c r="H118" t="str">
-        <v>fakemink</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L118" t="str">
-        <v>fml . - fakemink</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Faked It All The Time</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:01</v>
+        <v>3:08</v>
       </c>
       <c r="H119" t="str">
-        <v>Allie Sherlock</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L119" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>House of the Rising Sun</v>
+        <v>Lorelei</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:08</v>
+        <v>2:35</v>
       </c>
       <c r="H120" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>ERNEST</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L120" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Lorelei</v>
+        <v>Free</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Lorelei - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:35</v>
+        <v>3:56</v>
       </c>
       <c r="H121" t="str">
-        <v>ERNEST</v>
+        <v>SLANDER</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L121" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Free</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Free - Single</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:56</v>
+        <v>2:55</v>
       </c>
       <c r="H122" t="str">
-        <v>SLANDER</v>
+        <v>Artemas</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L122" t="str">
-        <v>Free - SLANDER</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>professional heartbreaker</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G123" t="str">
-        <v>2:55</v>
+        <v>3:56</v>
       </c>
       <c r="H123" t="str">
-        <v>Artemas</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L123" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>tell me what you want</v>
+        <v>Aguas</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>ACT II</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:56</v>
+        <v>2:52</v>
       </c>
       <c r="H124" t="str">
-        <v>Sasha Keable</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L124" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Aguas</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Aguas - Single</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H125" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L125" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Ants In My Room</v>
+        <v>Baddie</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Bohemio</v>
       </c>
       <c r="G126" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H126" t="str">
-        <v>Carter Vail</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L126" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Baddie</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Bohemio</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:11</v>
+        <v>3:51</v>
       </c>
       <c r="H127" t="str">
-        <v>Nicky Jam</v>
+        <v>Tems</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L127" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:51</v>
+        <v>3:16</v>
       </c>
       <c r="H128" t="str">
-        <v>Tems</v>
+        <v>Fred again..</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L128" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:16</v>
+        <v>3:50</v>
       </c>
       <c r="H129" t="str">
-        <v>Fred again..</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L129" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G130" t="str">
-        <v>3:50</v>
+        <v>3:33</v>
       </c>
       <c r="H130" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L130" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>For The First Time, Again</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>For The First Time, Again</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:33</v>
+        <v>3:17</v>
       </c>
       <c r="H131" t="str">
-        <v>Tyler Ballgame</v>
+        <v>Kneecap</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L131" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Liars Tale</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Liars Tale - Single</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:17</v>
+        <v>4:38</v>
       </c>
       <c r="H132" t="str">
-        <v>Kneecap</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L132" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:38</v>
+        <v>3:49</v>
       </c>
       <c r="H133" t="str">
-        <v>Motionless In White</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L133" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Wake Up Calling</v>
+        <v>HIGH</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G134" t="str">
-        <v>3:49</v>
+        <v>3:23</v>
       </c>
       <c r="H134" t="str">
-        <v>Papa Roach</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L134" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>HIGH</v>
+        <v>Villain</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Reflections</v>
       </c>
       <c r="G135" t="str">
-        <v>3:23</v>
+        <v>3:53</v>
       </c>
       <c r="H135" t="str">
-        <v>Magnolia Park</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L135" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Villain</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Reflections</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G136" t="str">
-        <v>3:53</v>
+        <v>3:00</v>
       </c>
       <c r="H136" t="str">
-        <v>From Ashes to New</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L136" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Residue</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G137" t="str">
-        <v>3:00</v>
+        <v>3:28</v>
       </c>
       <c r="H137" t="str">
-        <v>Caleb Chan</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L137" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Residue</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>The Moment (The Score)</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G138" t="str">
-        <v>3:28</v>
+        <v>2:12</v>
       </c>
       <c r="H138" t="str">
-        <v>A. G. Cook</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L138" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Starlight</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G139" t="str">
-        <v>2:12</v>
+        <v>3:21</v>
       </c>
       <c r="H139" t="str">
-        <v>Joyce Manor</v>
+        <v>Cannons</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L139" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Starlight</v>
+        <v>Dandelion</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Everything Glows</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G140" t="str">
-        <v>3:21</v>
+        <v>3:14</v>
       </c>
       <c r="H140" t="str">
-        <v>Cannons</v>
+        <v>Dogpark</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L140" t="str">
-        <v>Starlight - Cannons</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Dandelion</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G141" t="str">
-        <v>3:14</v>
+        <v>2:46</v>
       </c>
       <c r="H141" t="str">
-        <v>Dogpark</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L141" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>THEMSELVES</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>BACKWARD</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G142" t="str">
-        <v>2:46</v>
+        <v>2:24</v>
       </c>
       <c r="H142" t="str">
-        <v>Jordan Ward</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L142" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>High Maintenance</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Miracle Mile</v>
+        <v>Da Realest</v>
       </c>
       <c r="G143" t="str">
-        <v>2:24</v>
+        <v>1:59</v>
       </c>
       <c r="H143" t="str">
-        <v>Paul Russell</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L143" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Trackhawk</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Da Realest</v>
+        <v>Xavier</v>
       </c>
       <c r="G144" t="str">
-        <v>1:59</v>
+        <v>3:05</v>
       </c>
       <c r="H144" t="str">
-        <v>Babyfxce E</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L144" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Wheel Man</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Xavier</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:05</v>
+        <v>3:02</v>
       </c>
       <c r="H145" t="str">
-        <v>xaviersobased</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L145" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Natural Disaster</v>
+        <v>Prettier</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:02</v>
+        <v>2:34</v>
       </c>
       <c r="H146" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L146" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Prettier</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Prettier - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:34</v>
+        <v>3:21</v>
       </c>
       <c r="H147" t="str">
-        <v>Grace VanderWaal</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L147" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:21</v>
+        <v>3:20</v>
       </c>
       <c r="H148" t="str">
-        <v>NLE Choppa</v>
+        <v>The Maine</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L148" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Die To Fall</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Die To Fall - Single</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:20</v>
+        <v>2:58</v>
       </c>
       <c r="H149" t="str">
-        <v>The Maine</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L149" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G150" t="str">
-        <v>2:58</v>
+        <v>2:14</v>
       </c>
       <c r="H150" t="str">
-        <v>Steve Aoki</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L150" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Slow Burn</v>
+        <v>Too Late</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/too-late/1866685876</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Still There’s a Glow</v>
+        <v>Too Late - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>2:14</v>
+        <v>2:56</v>
       </c>
       <c r="H151" t="str">
-        <v>Sweet Pill</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/too-late/1866685875</v>
       </c>
       <c r="L151" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Too Late</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/too-late/1866685876</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Too Late - EP</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:56</v>
+        <v>2:50</v>
       </c>
       <c r="H152" t="str">
-        <v>Hunter Hayes</v>
+        <v>i-dle</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/too-late/1866685875</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L152" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G153" t="str">
-        <v>2:50</v>
+        <v>1:55</v>
       </c>
       <c r="H153" t="str">
-        <v>i-dle</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L153" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Thank You Is Enough</v>
+        <v>RIDIN</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>1:55</v>
+        <v>2:00</v>
       </c>
       <c r="H154" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>Tokischa</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L154" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>RIDIN</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>RIDIN - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:00</v>
+        <v>3:07</v>
       </c>
       <c r="H155" t="str">
-        <v>Tokischa</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L155" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>POSSESSION</v>
+        <v>Poema</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>POSSESSION - Single</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:07</v>
+        <v>3:14</v>
       </c>
       <c r="H156" t="str">
-        <v>Melanie Martinez</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L156" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Poema</v>
+        <v>Live Without</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Poema - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G157" t="str">
-        <v>3:14</v>
+        <v>2:55</v>
       </c>
       <c r="H157" t="str">
-        <v>Óscar Maydon</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L157" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Live Without</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:55</v>
+        <v>3:55</v>
       </c>
       <c r="H158" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Blessd</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L158" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>FANÁTICO</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:55</v>
+        <v>3:29</v>
       </c>
       <c r="H159" t="str">
-        <v>Blessd</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L159" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Frozen Lake</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:29</v>
+        <v>2:45</v>
       </c>
       <c r="H160" t="str">
-        <v>VOILÀ</v>
+        <v>VEDO</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L160" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:45</v>
+        <v>3:32</v>
       </c>
       <c r="H161" t="str">
-        <v>VEDO</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L161" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G162" t="str">
-        <v>3:32</v>
+        <v>3:20</v>
       </c>
       <c r="H162" t="str">
-        <v>Chris Lorenzo</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L162" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>It’s Like That</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>A Pound of Feathers</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:20</v>
+        <v>2:48</v>
       </c>
       <c r="H163" t="str">
-        <v>The Black Crowes</v>
+        <v>Mýa</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L163" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>A.S.A.P.</v>
+        <v>Once I Say</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>3:21</v>
       </c>
       <c r="H164" t="str">
-        <v>Mýa</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L164" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Once I Say</v>
+        <v>believer</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>PASSION</v>
+        <v>believer - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:21</v>
+        <v>2:57</v>
       </c>
       <c r="H165" t="str">
-        <v>Terrace Martin</v>
+        <v>Yuna</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L165" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>believer</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>believer - Single</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:57</v>
+        <v>3:51</v>
       </c>
       <c r="H166" t="str">
-        <v>Yuna</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L166" t="str">
-        <v>believer - Yuna</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>I Envy The Wind</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G167" t="str">
-        <v>3:51</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>Molly Parden</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L167" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Alchemist</v>
+        <v>Daysa</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Alchemist</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:13</v>
+        <v>4:36</v>
       </c>
       <c r="H168" t="str">
-        <v>Bre Kennedy</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L168" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Daysa</v>
+        <v>Fabulous</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Daysa - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:36</v>
+        <v>2:33</v>
       </c>
       <c r="H169" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>MEEK</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L169" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Fabulous</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Fabulous - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:33</v>
+        <v>3:22</v>
       </c>
       <c r="H170" t="str">
-        <v>MEEK</v>
+        <v>RUBIO</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L170" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>brainchem</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:22</v>
+        <v>2:28</v>
       </c>
       <c r="H171" t="str">
-        <v>RUBIO</v>
+        <v>EMJAY</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L171" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>brainchem</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>brainchem - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G172" t="str">
-        <v>2:28</v>
+        <v>2:48</v>
       </c>
       <c r="H172" t="str">
-        <v>EMJAY</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L172" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>Giants</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>With No Due Respect</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:48</v>
+        <v>3:12</v>
       </c>
       <c r="H173" t="str">
-        <v>Foggieraw</v>
+        <v>Picture This</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L173" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Giants</v>
+        <v>Scooby</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Giants - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:12</v>
+        <v>3:41</v>
       </c>
       <c r="H174" t="str">
-        <v>Picture This</v>
+        <v>corook</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L174" t="str">
-        <v>Giants - Picture This</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Scooby</v>
+        <v>La Racha</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Scooby - Single</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:41</v>
+        <v>2:48</v>
       </c>
       <c r="H175" t="str">
-        <v>corook</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L175" t="str">
-        <v>Scooby - corook</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>La Racha</v>
+        <v>So Am I</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>La Racha - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G176" t="str">
-        <v>2:48</v>
+        <v>2:50</v>
       </c>
       <c r="H176" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L176" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>So Am I</v>
+        <v>best thing</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:50</v>
+        <v>4:27</v>
       </c>
       <c r="H177" t="str">
-        <v>Katelyn Tarver</v>
+        <v>WRABEL</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L177" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>best thing</v>
+        <v>Count It Back</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>best thing - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G178" t="str">
-        <v>4:27</v>
+        <v>2:52</v>
       </c>
       <c r="H178" t="str">
-        <v>WRABEL</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L178" t="str">
-        <v>best thing - WRABEL</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Count It Back</v>
+        <v>Good Girl</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Magic Boy</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:52</v>
+        <v>4:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Bartees Strange</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L179" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Good Girl</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Good Girl - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G180" t="str">
-        <v>4:23</v>
+        <v>3:34</v>
       </c>
       <c r="H180" t="str">
-        <v>Paris Paloma</v>
+        <v>MORGXN</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L180" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>MY REVIVAL</v>
+        <v>Run My Way</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:34</v>
+        <v>2:44</v>
       </c>
       <c r="H181" t="str">
-        <v>MORGXN</v>
+        <v>December 10</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L181" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Run My Way</v>
+        <v>Cold Night</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Run My Way - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:44</v>
+        <v>3:12</v>
       </c>
       <c r="H182" t="str">
-        <v>December 10</v>
+        <v>HANA</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L182" t="str">
-        <v>Run My Way - December 10</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Cold Night</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Cold Night - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:12</v>
+        <v>2:28</v>
       </c>
       <c r="H183" t="str">
-        <v>HANA</v>
+        <v>LUNA</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L183" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Away With The Fairies</v>
+        <v>Fragile</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:28</v>
+        <v>3:10</v>
       </c>
       <c r="H184" t="str">
-        <v>LUNA</v>
+        <v>Anajah</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L184" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Fragile</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Fragile - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:10</v>
+        <v>2:04</v>
       </c>
       <c r="H185" t="str">
-        <v>Anajah</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L185" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Slow Dancin'</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:04</v>
+        <v>3:04</v>
       </c>
       <c r="H186" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L186" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:04</v>
+        <v>3:41</v>
       </c>
       <c r="H187" t="str">
-        <v>Lily Meola</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L187" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>More Of What Matters</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>ONE</v>
       </c>
       <c r="G188" t="str">
-        <v>3:41</v>
+        <v>3:46</v>
       </c>
       <c r="H188" t="str">
-        <v>Jamey Johnson</v>
+        <v>Sevendust</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L188" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Is This The Real You</v>
+        <v>Hud</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>ONE</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G189" t="str">
-        <v>3:46</v>
+        <v>4:46</v>
       </c>
       <c r="H189" t="str">
-        <v>Sevendust</v>
+        <v>MØL</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L189" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Hud</v>
+        <v>Ego Death</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>DREAMCRUSH</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:46</v>
+        <v>2:12</v>
       </c>
       <c r="H190" t="str">
-        <v>MØL</v>
+        <v>Atreyu</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L190" t="str">
-        <v>Hud - MØL</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Ego Death</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Ego Death - Single</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:12</v>
+        <v>4:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Atreyu</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L191" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Disappear</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G192" t="str">
-        <v>4:05</v>
+        <v>5:50</v>
       </c>
       <c r="H192" t="str">
-        <v>EJ Jones</v>
+        <v>Lane 8</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L192" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Disappear</v>
+        <v>Misbehave</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Disappear</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>5:50</v>
+        <v>3:43</v>
       </c>
       <c r="H193" t="str">
-        <v>Lane 8</v>
+        <v>Aluna</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L193" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Misbehave</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Misbehave - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:43</v>
+        <v>2:47</v>
       </c>
       <c r="H194" t="str">
-        <v>Aluna</v>
+        <v>Alok</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L194" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Club Bizarre</v>
+        <v>Fly</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:47</v>
+        <v>3:04</v>
       </c>
       <c r="H195" t="str">
-        <v>Alok</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L195" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Fly</v>
+        <v>ily anyway</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Fly - Single</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:04</v>
+        <v>3:05</v>
       </c>
       <c r="H196" t="str">
-        <v>Stephen Stanley</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L196" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>ily anyway</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>ily anyway - Single</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G197" t="str">
-        <v>3:05</v>
+        <v>3:35</v>
       </c>
       <c r="H197" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L197" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Nellene - EP</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G198" t="str">
-        <v>3:35</v>
+        <v>3:41</v>
       </c>
       <c r="H198" t="str">
-        <v>Deloyd Elze</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L198" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Kiss Big</v>
+        <v>praxis</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Kiss Big</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G199" t="str">
-        <v>3:41</v>
+        <v>3:28</v>
       </c>
       <c r="H199" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L199" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>praxis</v>
+        <v>House</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Whole World As Vigil</v>
+        <v>House - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:28</v>
+        <v>2:30</v>
       </c>
       <c r="H200" t="str">
-        <v>Lauren Auder</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L200" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>House</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>House - Single</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G201" t="str">
-        <v>2:30</v>
+        <v>3:57</v>
       </c>
       <c r="H201" t="str">
-        <v>Connie Converse</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L201" t="str">
-        <v>House - Connie Converse</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>Brincar</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
       </c>
       <c r="D202" t="str">
         <v>2026-02-01</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>JET LAG - EP</v>
       </c>
       <c r="G202" t="str">
-        <v>3:57</v>
+        <v>3:06</v>
       </c>
       <c r="H202" t="str">
-        <v>Yumi Zouma</v>
+        <v>J Castle</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
       </c>
       <c r="L202" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>Brincar - J Castle</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Brincar</v>
+        <v>Quién</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
       <c r="D203" t="str">
         <v>2026-02-01</v>
@@ -8089,68 +8089,30 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>JET LAG - EP</v>
+        <v>Quién - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:06</v>
+        <v>4:19</v>
       </c>
       <c r="H203" t="str">
-        <v>J Castle</v>
+        <v>Daniela Darcourt</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
       <c r="L203" t="str">
-        <v>Brincar - J Castle</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Quién</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Quién - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>4:19</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Daniela Darcourt</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
-      </c>
-      <c r="L204" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -781,7 +781,7 @@
         <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>4:47</v>
@@ -2339,7 +2339,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>2:56</v>

--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -2301,7 +2301,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:59</v>

--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -743,7 +743,7 @@
         <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:07</v>
@@ -3023,7 +3023,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>4:21</v>

--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -705,7 +705,7 @@
         <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:39</v>
@@ -1997,7 +1997,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:01</v>
@@ -3175,7 +3175,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>3:21</v>

--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>חנן בן ארי לא המשוגע היחידי</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://yosmusic.com/%d7%97%d7%a0%d7%9f-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%9c%d7%90-%d7%94%d7%9e%d7%a9%d7%95%d7%92%d7%a2-%d7%94%d7%99%d7%97%d7%99%d7%93%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>חנן בן ארי לא מנסה להמציא את עצמו מחדש – אלא מעז להסיר שכבות. זהו אלבום שמעדיף אמת על פני פוזה, פגיעות על פני הצהרה, ושאלות פתוחות על פני תשובות מהודקות. בין תפילה להמנון, בין בלדת נשמה לפולק־רוק אמריקאי ובין</v>
       </c>
       <c r="G2" t="str">
-        <v>4:58</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>The Warning</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>חנן בן ארי לא המשוגע היחידי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>5:08</v>
+        <v>4:58</v>
       </c>
       <c r="H3" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-01</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:38</v>
+        <v>5:08</v>
       </c>
       <c r="H4" t="str">
-        <v>Roxette</v>
+        <v>The Offspring</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-01</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:50</v>
+        <v>4:38</v>
       </c>
       <c r="H5" t="str">
-        <v>Jessie Ware</v>
+        <v>Roxette</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-01</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:10</v>
+        <v>3:50</v>
       </c>
       <c r="H6" t="str">
-        <v>Joseph</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-01</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:44</v>
+        <v>3:10</v>
       </c>
       <c r="H7" t="str">
-        <v>Dean Lewis</v>
+        <v>Joseph</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:57</v>
+        <v>2:44</v>
       </c>
       <c r="H8" t="str">
-        <v>Take That</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-01</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H9" t="str">
-        <v>The Cure</v>
+        <v>Take That</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-01</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:07</v>
+        <v>2:39</v>
       </c>
       <c r="H10" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>The Cure</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-01</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:47</v>
+        <v>3:07</v>
       </c>
       <c r="H11" t="str">
-        <v>Paris Paloma</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-01</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:22</v>
+        <v>4:47</v>
       </c>
       <c r="H12" t="str">
-        <v>Zara Larsson</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-01</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:48</v>
+        <v>3:22</v>
       </c>
       <c r="H13" t="str">
-        <v>only the poets</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-01</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H14" t="str">
-        <v>Katelyn Tarver</v>
+        <v>only the poets</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-01</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:33</v>
+        <v>2:52</v>
       </c>
       <c r="H15" t="str">
-        <v>David Guetta</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-01</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:41</v>
+        <v>3:33</v>
       </c>
       <c r="H16" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-01</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:01</v>
+        <v>2:41</v>
       </c>
       <c r="H17" t="str">
-        <v>Ella Langley</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-01</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>4:01</v>
       </c>
       <c r="H18" t="str">
-        <v>Dogpark</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-01</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:03</v>
+        <v>3:16</v>
       </c>
       <c r="H19" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Dogpark</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-01</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:41</v>
+        <v>3:03</v>
       </c>
       <c r="H20" t="str">
-        <v>ERNEST</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:05</v>
+        <v>2:41</v>
       </c>
       <c r="H21" t="str">
-        <v>Labrinth</v>
+        <v>ERNEST</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:46</v>
+        <v>3:05</v>
       </c>
       <c r="H22" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Labrinth</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:32</v>
+        <v>2:46</v>
       </c>
       <c r="H23" t="str">
-        <v>VOILÀ</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:42</v>
+        <v>3:32</v>
       </c>
       <c r="H24" t="str">
-        <v>Cannons</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:38</v>
+        <v>3:42</v>
       </c>
       <c r="H25" t="str">
-        <v>Kylie Morgan</v>
+        <v>Cannons</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:10</v>
+        <v>2:38</v>
       </c>
       <c r="H26" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:57</v>
+        <v>3:10</v>
       </c>
       <c r="H27" t="str">
-        <v>Willie Nelson</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:19</v>
+        <v>3:57</v>
       </c>
       <c r="H28" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:04</v>
+        <v>2:19</v>
       </c>
       <c r="H29" t="str">
-        <v>India Martínez</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:16</v>
+        <v>4:04</v>
       </c>
       <c r="H30" t="str">
-        <v>Chelsea Cutler</v>
+        <v>India Martínez</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:58</v>
+        <v>2:16</v>
       </c>
       <c r="H31" t="str">
-        <v>TINI</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:26</v>
+        <v>5:58</v>
       </c>
       <c r="H32" t="str">
-        <v>Charley</v>
+        <v>TINI</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-01</v>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H33" t="str">
-        <v>Demi Lovato</v>
+        <v>Charley</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-01</v>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H34" t="str">
-        <v>Teddy Swims</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-01</v>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:14</v>
+        <v>3:16</v>
       </c>
       <c r="H35" t="str">
-        <v>Beck</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H36" t="str">
-        <v>The Offspring</v>
+        <v>Beck</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-01</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:10</v>
+        <v>2:57</v>
       </c>
       <c r="H37" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>The Offspring</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-01</v>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:10</v>
+        <v>4:10</v>
       </c>
       <c r="H38" t="str">
-        <v>Jason Derulo</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-01</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:52</v>
+        <v>2:10</v>
       </c>
       <c r="H39" t="str">
-        <v>lights</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-01</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H40" t="str">
-        <v>Telenova</v>
+        <v>lights</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:32</v>
+        <v>3:50</v>
       </c>
       <c r="H41" t="str">
-        <v>Marcin</v>
+        <v>Telenova</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-01</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:27</v>
+        <v>5:32</v>
       </c>
       <c r="H42" t="str">
-        <v>We Three</v>
+        <v>Marcin</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:01</v>
+        <v>4:27</v>
       </c>
       <c r="H43" t="str">
-        <v>Timebelle Official</v>
+        <v>We Three</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B44" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-01</v>
@@ -2050,10 +2050,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H44" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H45" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-01</v>
@@ -2126,10 +2126,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H46" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-01</v>
@@ -2164,10 +2164,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H47" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-01</v>
@@ -2202,10 +2202,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H48" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-01</v>
@@ -2240,10 +2240,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H49" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-01</v>
@@ -2278,10 +2278,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H50" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H51" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B52" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-01</v>
@@ -2354,10 +2354,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H52" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B53" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-01</v>
@@ -2392,10 +2392,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H53" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B54" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-01</v>
@@ -2430,10 +2430,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:37</v>
+        <v>3:46</v>
       </c>
       <c r="H54" t="str">
-        <v>Bella White</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-01</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H55" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-01</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H56" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-01</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:10</v>
+        <v>3:54</v>
       </c>
       <c r="H57" t="str">
-        <v>Parker McCollum</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-01</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H58" t="str">
-        <v>Matt Hansen</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H59" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-01</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H61" t="str">
-        <v>Tauren Wells</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-01</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H62" t="str">
-        <v>Maiah Manser</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-01</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H63" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-01</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H64" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-01</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H65" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-01</v>
@@ -2889,7 +2889,7 @@
         <v>3:13</v>
       </c>
       <c r="H66" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-01</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H67" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-01</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:14</v>
+        <v>3:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Harry Styles</v>
+        <v>CAIN</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-01</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:59</v>
+        <v>5:14</v>
       </c>
       <c r="H69" t="str">
-        <v>Lana Lubany</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-01</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="H70" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-01</v>
@@ -3076,10 +3076,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H71" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="H72" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-01</v>
@@ -3152,10 +3152,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H73" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B74" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-01</v>
@@ -3190,10 +3190,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H74" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B75" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-01</v>
@@ -3228,10 +3228,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H75" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-01</v>
@@ -3266,10 +3266,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H76" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-01</v>
@@ -3304,10 +3304,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B78" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-01</v>
@@ -3342,10 +3342,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="H78" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H79" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="H80" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-01</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="H81" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-01</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="H82" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-01</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="H83" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-01</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="H84" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-01</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H85" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-01</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="H86" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-01</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="H87" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-01</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="H88" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-01</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="H89" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-01</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H90" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-01</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H91" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-01</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H92" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-01</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="H93" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-01</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-01</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="H95" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-01</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H96" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-01</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H97" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-01</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="H98" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-01</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H99" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-01</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="H100" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-01</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="H101" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Body</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/body/1871258331</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>OCTANE</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:35</v>
+        <v>3:11</v>
       </c>
       <c r="H102" t="str">
-        <v>Don Toliver</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/body/1871258329</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Body - Don Toliver</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dandelion</v>
+        <v>Body</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
+        <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Dandelion</v>
+        <v>OCTANE</v>
       </c>
       <c r="G103" t="str">
-        <v>4:00</v>
+        <v>2:35</v>
       </c>
       <c r="H103" t="str">
-        <v>Ella Langley</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
+        <v>https://music.apple.com/us/album/body/1871258329</v>
       </c>
       <c r="L103" t="str">
-        <v>Dandelion - Ella Langley</v>
+        <v>Body - Don Toliver</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>LIGHTS GO OUT</v>
+        <v>Dandelion</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
+        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>LIGHTS GO OUT - Single</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>2:38</v>
+        <v>4:00</v>
       </c>
       <c r="H104" t="str">
-        <v>John Summit</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
+        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>LIGHTS GO OUT - John Summit</v>
+        <v>Dandelion - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Great Divide</v>
+        <v>LIGHTS GO OUT</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
+        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Great Divide</v>
+        <v>LIGHTS GO OUT - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>5:17</v>
+        <v>2:38</v>
       </c>
       <c r="H105" t="str">
-        <v>Noah Kahan</v>
+        <v>John Summit</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
+        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
       </c>
       <c r="L105" t="str">
-        <v>The Great Divide - Noah Kahan</v>
+        <v>LIGHTS GO OUT - John Summit</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>tristón</v>
+        <v>The Great Divide</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
+        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>tristón - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G106" t="str">
-        <v>3:36</v>
+        <v>5:17</v>
       </c>
       <c r="H106" t="str">
-        <v>Fuerza Regida</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
+        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
       </c>
       <c r="L106" t="str">
-        <v>tristón - Fuerza Regida</v>
+        <v>The Great Divide - Noah Kahan</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Feed the Streets</v>
+        <v>tristón</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
+        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Feed the Streets - Single</v>
+        <v>tristón - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:58</v>
+        <v>3:36</v>
       </c>
       <c r="H107" t="str">
-        <v>Rod Wave</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
+        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
       </c>
       <c r="L107" t="str">
-        <v>Feed the Streets - Rod Wave</v>
+        <v>tristón - Fuerza Regida</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Did This To Myself</v>
+        <v>Feed the Streets</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Distracted</v>
+        <v>Feed the Streets - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:30</v>
+        <v>2:58</v>
       </c>
       <c r="H108" t="str">
-        <v>Thundercat</v>
+        <v>Rod Wave</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
       </c>
       <c r="L108" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>Feed the Streets - Rod Wave</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>For Hire</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>For Hire - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G109" t="str">
-        <v>3:44</v>
+        <v>2:30</v>
       </c>
       <c r="H109" t="str">
-        <v>People I’ve Met</v>
+        <v>Thundercat</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L109" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>McArthur</v>
+        <v>For Hire</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>McArthur - Single</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:51</v>
+        <v>3:44</v>
       </c>
       <c r="H110" t="str">
-        <v>HARDY</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L110" t="str">
-        <v>McArthur - HARDY</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Debris</v>
+        <v>McArthur</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:55</v>
+        <v>3:51</v>
       </c>
       <c r="H111" t="str">
-        <v>Labrinth</v>
+        <v>HARDY</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L111" t="str">
-        <v>Debris - Labrinth</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Debris</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G112" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H112" t="str">
-        <v>Militarie Gun</v>
+        <v>Labrinth</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L112" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G113" t="str">
-        <v>4:38</v>
+        <v>3:25</v>
       </c>
       <c r="H113" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>1+1</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>1+1 - Single</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:06</v>
+        <v>4:38</v>
       </c>
       <c r="H114" t="str">
-        <v>Maluma</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L114" t="str">
-        <v>1+1 - Maluma</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>1+1</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:08</v>
+        <v>3:06</v>
       </c>
       <c r="H115" t="str">
-        <v>MJ Cole</v>
+        <v>Maluma</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L115" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Two Car Garage</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:02</v>
+        <v>3:08</v>
       </c>
       <c r="H116" t="str">
-        <v>Jon Bellion</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L116" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>fml .</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:40</v>
+        <v>3:02</v>
       </c>
       <c r="H117" t="str">
-        <v>fakemink</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L117" t="str">
-        <v>fml . - fakemink</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Faked It All The Time</v>
+        <v>fml .</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G118" t="str">
-        <v>3:01</v>
+        <v>2:40</v>
       </c>
       <c r="H118" t="str">
-        <v>Allie Sherlock</v>
+        <v>fakemink</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L118" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>House of the Rising Sun</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:08</v>
+        <v>3:01</v>
       </c>
       <c r="H119" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L119" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Lorelei</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Lorelei - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:35</v>
+        <v>3:08</v>
       </c>
       <c r="H120" t="str">
-        <v>ERNEST</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L120" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Free</v>
+        <v>Lorelei</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Free - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:56</v>
+        <v>2:35</v>
       </c>
       <c r="H121" t="str">
-        <v>SLANDER</v>
+        <v>ERNEST</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L121" t="str">
-        <v>Free - SLANDER</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>professional heartbreaker</v>
+        <v>Free</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:55</v>
+        <v>3:56</v>
       </c>
       <c r="H122" t="str">
-        <v>Artemas</v>
+        <v>SLANDER</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L122" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>tell me what you want</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ACT II</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:56</v>
+        <v>2:55</v>
       </c>
       <c r="H123" t="str">
-        <v>Sasha Keable</v>
+        <v>Artemas</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L123" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Aguas</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Aguas - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>2:52</v>
+        <v>3:56</v>
       </c>
       <c r="H124" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L124" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Ants In My Room</v>
+        <v>Aguas</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H125" t="str">
-        <v>Carter Vail</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L125" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Baddie</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Bohemio</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H126" t="str">
-        <v>Nicky Jam</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L126" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>Baddie</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>Bohemio</v>
       </c>
       <c r="G127" t="str">
-        <v>3:51</v>
+        <v>3:11</v>
       </c>
       <c r="H127" t="str">
-        <v>Tems</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L127" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:16</v>
+        <v>3:51</v>
       </c>
       <c r="H128" t="str">
-        <v>Fred again..</v>
+        <v>Tems</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L128" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:50</v>
+        <v>3:16</v>
       </c>
       <c r="H129" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Fred again..</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:33</v>
+        <v>3:50</v>
       </c>
       <c r="H130" t="str">
-        <v>Tyler Ballgame</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L130" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Liars Tale</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Liars Tale - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G131" t="str">
-        <v>3:17</v>
+        <v>3:33</v>
       </c>
       <c r="H131" t="str">
-        <v>Kneecap</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L131" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:38</v>
+        <v>3:17</v>
       </c>
       <c r="H132" t="str">
-        <v>Motionless In White</v>
+        <v>Kneecap</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L132" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Wake Up Calling</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:49</v>
+        <v>4:38</v>
       </c>
       <c r="H133" t="str">
-        <v>Papa Roach</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L133" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>HIGH</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:23</v>
+        <v>3:49</v>
       </c>
       <c r="H134" t="str">
-        <v>Magnolia Park</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L134" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Villain</v>
+        <v>HIGH</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Reflections</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G135" t="str">
-        <v>3:53</v>
+        <v>3:23</v>
       </c>
       <c r="H135" t="str">
-        <v>From Ashes to New</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L135" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Villain</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>Reflections</v>
       </c>
       <c r="G136" t="str">
-        <v>3:00</v>
+        <v>3:53</v>
       </c>
       <c r="H136" t="str">
-        <v>Caleb Chan</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L136" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Residue</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G137" t="str">
-        <v>3:28</v>
+        <v>3:00</v>
       </c>
       <c r="H137" t="str">
-        <v>A. G. Cook</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L137" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Residue</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G138" t="str">
-        <v>2:12</v>
+        <v>3:28</v>
       </c>
       <c r="H138" t="str">
-        <v>Joyce Manor</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L138" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Starlight</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Everything Glows</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G139" t="str">
-        <v>3:21</v>
+        <v>2:12</v>
       </c>
       <c r="H139" t="str">
-        <v>Cannons</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L139" t="str">
-        <v>Starlight - Cannons</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Dandelion</v>
+        <v>Starlight</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G140" t="str">
-        <v>3:14</v>
+        <v>3:21</v>
       </c>
       <c r="H140" t="str">
-        <v>Dogpark</v>
+        <v>Cannons</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L140" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>THEMSELVES</v>
+        <v>Dandelion</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BACKWARD</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G141" t="str">
-        <v>2:46</v>
+        <v>3:14</v>
       </c>
       <c r="H141" t="str">
-        <v>Jordan Ward</v>
+        <v>Dogpark</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L141" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>High Maintenance</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Miracle Mile</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G142" t="str">
-        <v>2:24</v>
+        <v>2:46</v>
       </c>
       <c r="H142" t="str">
-        <v>Paul Russell</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L142" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Trackhawk</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Da Realest</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G143" t="str">
-        <v>1:59</v>
+        <v>2:24</v>
       </c>
       <c r="H143" t="str">
-        <v>Babyfxce E</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L143" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Wheel Man</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Xavier</v>
+        <v>Da Realest</v>
       </c>
       <c r="G144" t="str">
-        <v>3:05</v>
+        <v>1:59</v>
       </c>
       <c r="H144" t="str">
-        <v>xaviersobased</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L144" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Natural Disaster</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Xavier</v>
       </c>
       <c r="G145" t="str">
-        <v>3:02</v>
+        <v>3:05</v>
       </c>
       <c r="H145" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L145" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Prettier</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Prettier - Single</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H146" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L146" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Prettier</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H147" t="str">
-        <v>NLE Choppa</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L147" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Die To Fall</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:20</v>
+        <v>3:21</v>
       </c>
       <c r="H148" t="str">
-        <v>The Maine</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L148" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:58</v>
+        <v>3:20</v>
       </c>
       <c r="H149" t="str">
-        <v>Steve Aoki</v>
+        <v>The Maine</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Slow Burn</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Still There’s a Glow</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:14</v>
+        <v>2:58</v>
       </c>
       <c r="H150" t="str">
-        <v>Sweet Pill</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L150" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Too Late</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/too-late/1866685876</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Too Late - EP</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G151" t="str">
-        <v>2:56</v>
+        <v>2:14</v>
       </c>
       <c r="H151" t="str">
-        <v>Hunter Hayes</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/too-late/1866685875</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L151" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Too Late</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/too-late/1866685876</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Too Late - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H152" t="str">
-        <v>i-dle</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/too-late/1866685875</v>
       </c>
       <c r="L152" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>1:55</v>
+        <v>2:50</v>
       </c>
       <c r="H153" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>i-dle</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L153" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>RIDIN</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>RIDIN - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G154" t="str">
-        <v>2:00</v>
+        <v>1:55</v>
       </c>
       <c r="H154" t="str">
-        <v>Tokischa</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L154" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>POSSESSION</v>
+        <v>RIDIN</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>POSSESSION - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H155" t="str">
-        <v>Melanie Martinez</v>
+        <v>Tokischa</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L155" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Poema</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Poema - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:14</v>
+        <v>3:07</v>
       </c>
       <c r="H156" t="str">
-        <v>Óscar Maydon</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L156" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Live Without</v>
+        <v>Poema</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:55</v>
+        <v>3:14</v>
       </c>
       <c r="H157" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L157" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>FANÁTICO</v>
+        <v>Live Without</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G158" t="str">
-        <v>3:55</v>
+        <v>2:55</v>
       </c>
       <c r="H158" t="str">
-        <v>Blessd</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L158" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Frozen Lake</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:29</v>
+        <v>3:55</v>
       </c>
       <c r="H159" t="str">
-        <v>VOILÀ</v>
+        <v>Blessd</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L159" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:45</v>
+        <v>3:29</v>
       </c>
       <c r="H160" t="str">
-        <v>VEDO</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H161" t="str">
-        <v>Chris Lorenzo</v>
+        <v>VEDO</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>It’s Like That</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:20</v>
+        <v>3:32</v>
       </c>
       <c r="H162" t="str">
-        <v>The Black Crowes</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L162" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>A.S.A.P.</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G163" t="str">
-        <v>2:48</v>
+        <v>3:20</v>
       </c>
       <c r="H163" t="str">
-        <v>Mýa</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L163" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Once I Say</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>PASSION</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>Terrace Martin</v>
+        <v>Mýa</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L164" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>believer</v>
+        <v>Once I Say</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>believer - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G165" t="str">
-        <v>2:57</v>
+        <v>3:21</v>
       </c>
       <c r="H165" t="str">
-        <v>Yuna</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L165" t="str">
-        <v>believer - Yuna</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I Envy The Wind</v>
+        <v>believer</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:51</v>
+        <v>2:57</v>
       </c>
       <c r="H166" t="str">
-        <v>Molly Parden</v>
+        <v>Yuna</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L166" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>3:51</v>
       </c>
       <c r="H167" t="str">
-        <v>Bre Kennedy</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L167" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Daysa</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Daysa - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G168" t="str">
-        <v>4:36</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L168" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fabulous</v>
+        <v>Daysa</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Fabulous - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:33</v>
+        <v>4:36</v>
       </c>
       <c r="H169" t="str">
-        <v>MEEK</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L169" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Fabulous</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:22</v>
+        <v>2:33</v>
       </c>
       <c r="H170" t="str">
-        <v>RUBIO</v>
+        <v>MEEK</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>brainchem</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>brainchem - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:28</v>
+        <v>3:22</v>
       </c>
       <c r="H171" t="str">
-        <v>EMJAY</v>
+        <v>RUBIO</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L171" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>brainchem</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>With No Due Respect</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:48</v>
+        <v>2:28</v>
       </c>
       <c r="H172" t="str">
-        <v>Foggieraw</v>
+        <v>EMJAY</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L172" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Giants</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Giants - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G173" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H173" t="str">
-        <v>Picture This</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L173" t="str">
-        <v>Giants - Picture This</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Scooby</v>
+        <v>Giants</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Scooby - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H174" t="str">
-        <v>corook</v>
+        <v>Picture This</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L174" t="str">
-        <v>Scooby - corook</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>La Racha</v>
+        <v>Scooby</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>La Racha - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:48</v>
+        <v>3:41</v>
       </c>
       <c r="H175" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>corook</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L175" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>So Am I</v>
+        <v>La Racha</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H176" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L176" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>best thing</v>
+        <v>So Am I</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>best thing - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G177" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H177" t="str">
-        <v>WRABEL</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L177" t="str">
-        <v>best thing - WRABEL</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Count It Back</v>
+        <v>best thing</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Magic Boy</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:52</v>
+        <v>4:27</v>
       </c>
       <c r="H178" t="str">
-        <v>Bartees Strange</v>
+        <v>WRABEL</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L178" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Good Girl</v>
+        <v>Count It Back</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Good Girl - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G179" t="str">
-        <v>4:23</v>
+        <v>2:52</v>
       </c>
       <c r="H179" t="str">
-        <v>Paris Paloma</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L179" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>MY REVIVAL</v>
+        <v>Good Girl</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:34</v>
+        <v>4:23</v>
       </c>
       <c r="H180" t="str">
-        <v>MORGXN</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L180" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Run My Way</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Run My Way - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G181" t="str">
-        <v>2:44</v>
+        <v>3:34</v>
       </c>
       <c r="H181" t="str">
-        <v>December 10</v>
+        <v>MORGXN</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L181" t="str">
-        <v>Run My Way - December 10</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Cold Night</v>
+        <v>Run My Way</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Cold Night - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:12</v>
+        <v>2:44</v>
       </c>
       <c r="H182" t="str">
-        <v>HANA</v>
+        <v>December 10</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L182" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Away With The Fairies</v>
+        <v>Cold Night</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:28</v>
+        <v>3:12</v>
       </c>
       <c r="H183" t="str">
-        <v>LUNA</v>
+        <v>HANA</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L183" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fragile</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Fragile - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:10</v>
+        <v>2:28</v>
       </c>
       <c r="H184" t="str">
-        <v>Anajah</v>
+        <v>LUNA</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L184" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Slow Dancin'</v>
+        <v>Fragile</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:04</v>
+        <v>3:10</v>
       </c>
       <c r="H185" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Anajah</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L185" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:04</v>
+        <v>2:04</v>
       </c>
       <c r="H186" t="str">
-        <v>Lily Meola</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L186" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>More Of What Matters</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:41</v>
+        <v>3:04</v>
       </c>
       <c r="H187" t="str">
-        <v>Jamey Johnson</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L187" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Is This The Real You</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>ONE</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:46</v>
+        <v>3:41</v>
       </c>
       <c r="H188" t="str">
-        <v>Sevendust</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L188" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Hud</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>DREAMCRUSH</v>
+        <v>ONE</v>
       </c>
       <c r="G189" t="str">
-        <v>4:46</v>
+        <v>3:46</v>
       </c>
       <c r="H189" t="str">
-        <v>MØL</v>
+        <v>Sevendust</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L189" t="str">
-        <v>Hud - MØL</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Ego Death</v>
+        <v>Hud</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Ego Death - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G190" t="str">
-        <v>2:12</v>
+        <v>4:46</v>
       </c>
       <c r="H190" t="str">
-        <v>Atreyu</v>
+        <v>MØL</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L190" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Ego Death</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:05</v>
+        <v>2:12</v>
       </c>
       <c r="H191" t="str">
-        <v>EJ Jones</v>
+        <v>Atreyu</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L191" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>5:50</v>
+        <v>4:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Lane 8</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L192" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Misbehave</v>
+        <v>Disappear</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Misbehave - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G193" t="str">
-        <v>3:43</v>
+        <v>5:50</v>
       </c>
       <c r="H193" t="str">
-        <v>Aluna</v>
+        <v>Lane 8</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L193" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Club Bizarre</v>
+        <v>Misbehave</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:47</v>
+        <v>3:43</v>
       </c>
       <c r="H194" t="str">
-        <v>Alok</v>
+        <v>Aluna</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L194" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Fly</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Fly - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H195" t="str">
-        <v>Stephen Stanley</v>
+        <v>Alok</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L195" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>ily anyway</v>
+        <v>Fly</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>ily anyway - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L196" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>ily anyway</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Nellene - EP</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:35</v>
+        <v>3:05</v>
       </c>
       <c r="H197" t="str">
-        <v>Deloyd Elze</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L197" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Kiss Big</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Kiss Big</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G198" t="str">
-        <v>3:41</v>
+        <v>3:35</v>
       </c>
       <c r="H198" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L198" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>praxis</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G199" t="str">
-        <v>3:28</v>
+        <v>3:41</v>
       </c>
       <c r="H199" t="str">
-        <v>Lauren Auder</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L199" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>House</v>
+        <v>praxis</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>House - Single</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G200" t="str">
-        <v>2:30</v>
+        <v>3:28</v>
       </c>
       <c r="H200" t="str">
-        <v>Connie Converse</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L200" t="str">
-        <v>House - Connie Converse</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>House</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>House - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:57</v>
+        <v>2:30</v>
       </c>
       <c r="H201" t="str">
-        <v>Yumi Zouma</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L201" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Brincar</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D202" t="str">
         <v>2026-02-01</v>
@@ -8051,68 +8051,106 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>JET LAG - EP</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G202" t="str">
-        <v>3:06</v>
+        <v>3:57</v>
       </c>
       <c r="H202" t="str">
-        <v>J Castle</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L202" t="str">
-        <v>Brincar - J Castle</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H203" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
         <v>Quién</v>
       </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D203" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
+      <c r="D204" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G203" t="str">
+      <c r="G204" t="str">
         <v>4:19</v>
       </c>
-      <c r="H203" t="str">
+      <c r="H204" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K203" t="str">
+      <c r="K204" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L203" t="str">
+      <c r="L204" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חנן בן ארי לא המשוגע היחידי</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-01</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%97%d7%a0%d7%9f-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%9c%d7%90-%d7%94%d7%9e%d7%a9%d7%95%d7%92%d7%a2-%d7%94%d7%99%d7%97%d7%99%d7%93%d7%99/</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>חנן בן ארי לא מנסה להמציא את עצמו מחדש – אלא מעז להסיר שכבות. זהו אלבום שמעדיף אמת על פני פוזה, פגיעות על פני הצהרה, ושאלות פתוחות על פני תשובות מהודקות. בין תפילה להמנון, בין בלדת נשמה לפולק־רוק אמריקאי ובין</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:58</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>The Warning</v>
       </c>
       <c r="I2" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חנן בן ארי לא המשוגע היחידי</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:58</v>
+        <v>5:08</v>
       </c>
       <c r="H3" t="str">
-        <v>The Warning</v>
+        <v>The Offspring</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-01</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>5:08</v>
+        <v>4:38</v>
       </c>
       <c r="H4" t="str">
-        <v>The Offspring</v>
+        <v>Roxette</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-01</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:38</v>
+        <v>3:50</v>
       </c>
       <c r="H5" t="str">
-        <v>Roxette</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-01</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:50</v>
+        <v>3:10</v>
       </c>
       <c r="H6" t="str">
-        <v>Jessie Ware</v>
+        <v>Joseph</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-01</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:10</v>
+        <v>2:44</v>
       </c>
       <c r="H7" t="str">
-        <v>Joseph</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-01</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:44</v>
+        <v>2:57</v>
       </c>
       <c r="H8" t="str">
-        <v>Dean Lewis</v>
+        <v>Take That</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-01</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:57</v>
+        <v>2:39</v>
       </c>
       <c r="H9" t="str">
-        <v>Take That</v>
+        <v>The Cure</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-01</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:39</v>
+        <v>3:07</v>
       </c>
       <c r="H10" t="str">
-        <v>The Cure</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-01</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:07</v>
+        <v>4:47</v>
       </c>
       <c r="H11" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-01</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:47</v>
+        <v>3:22</v>
       </c>
       <c r="H12" t="str">
-        <v>Paris Paloma</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-01</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:22</v>
+        <v>2:48</v>
       </c>
       <c r="H13" t="str">
-        <v>Zara Larsson</v>
+        <v>only the poets</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-01</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H14" t="str">
-        <v>only the poets</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-01</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:52</v>
+        <v>3:33</v>
       </c>
       <c r="H15" t="str">
-        <v>Katelyn Tarver</v>
+        <v>David Guetta</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-01</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:33</v>
+        <v>2:41</v>
       </c>
       <c r="H16" t="str">
-        <v>David Guetta</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-01</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:41</v>
+        <v>4:01</v>
       </c>
       <c r="H17" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-01</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:01</v>
+        <v>3:16</v>
       </c>
       <c r="H18" t="str">
-        <v>Ella Langley</v>
+        <v>Dogpark</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-01</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:16</v>
+        <v>3:03</v>
       </c>
       <c r="H19" t="str">
-        <v>Dogpark</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-01</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:03</v>
+        <v>2:41</v>
       </c>
       <c r="H20" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>ERNEST</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:41</v>
+        <v>3:05</v>
       </c>
       <c r="H21" t="str">
-        <v>ERNEST</v>
+        <v>Labrinth</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H22" t="str">
-        <v>Labrinth</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:46</v>
+        <v>3:32</v>
       </c>
       <c r="H23" t="str">
-        <v>Grace VanderWaal</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:32</v>
+        <v>3:42</v>
       </c>
       <c r="H24" t="str">
-        <v>VOILÀ</v>
+        <v>Cannons</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:42</v>
+        <v>2:38</v>
       </c>
       <c r="H25" t="str">
-        <v>Cannons</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:38</v>
+        <v>3:10</v>
       </c>
       <c r="H26" t="str">
-        <v>Kylie Morgan</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:10</v>
+        <v>3:57</v>
       </c>
       <c r="H27" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:57</v>
+        <v>2:19</v>
       </c>
       <c r="H28" t="str">
-        <v>Willie Nelson</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H29" t="str">
-        <v>JeremyCampMusic</v>
+        <v>India Martínez</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:04</v>
+        <v>2:16</v>
       </c>
       <c r="H30" t="str">
-        <v>India Martínez</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:16</v>
+        <v>5:58</v>
       </c>
       <c r="H31" t="str">
-        <v>Chelsea Cutler</v>
+        <v>TINI</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>5:58</v>
+        <v>3:26</v>
       </c>
       <c r="H32" t="str">
-        <v>TINI</v>
+        <v>Charley</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-01</v>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:26</v>
+        <v>4:05</v>
       </c>
       <c r="H33" t="str">
-        <v>Charley</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-01</v>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:05</v>
+        <v>3:16</v>
       </c>
       <c r="H34" t="str">
-        <v>Demi Lovato</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-01</v>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:16</v>
+        <v>3:14</v>
       </c>
       <c r="H35" t="str">
-        <v>Teddy Swims</v>
+        <v>Beck</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:14</v>
+        <v>2:57</v>
       </c>
       <c r="H36" t="str">
-        <v>Beck</v>
+        <v>The Offspring</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-01</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:57</v>
+        <v>4:10</v>
       </c>
       <c r="H37" t="str">
-        <v>The Offspring</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-01</v>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:10</v>
+        <v>2:10</v>
       </c>
       <c r="H38" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-01</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:10</v>
+        <v>3:52</v>
       </c>
       <c r="H39" t="str">
-        <v>Jason Derulo</v>
+        <v>lights</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:52</v>
+        <v>3:50</v>
       </c>
       <c r="H40" t="str">
-        <v>lights</v>
+        <v>Telenova</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>I Explained "How Music Works" LIVE At My Concert</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-01</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:50</v>
+        <v>5:32</v>
       </c>
       <c r="H41" t="str">
-        <v>Telenova</v>
+        <v>Marcin</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>I Explained "How Music Works" LIVE At My Concert - Marcin</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-01</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>5:32</v>
+        <v>4:27</v>
       </c>
       <c r="H42" t="str">
-        <v>Marcin</v>
+        <v>We Three</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:27</v>
+        <v>3:01</v>
       </c>
       <c r="H43" t="str">
-        <v>We Three</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B44" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-01</v>
@@ -2050,10 +2050,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:01</v>
+        <v>3:20</v>
       </c>
       <c r="H44" t="str">
-        <v>Timebelle Official</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:20</v>
+        <v>3:34</v>
       </c>
       <c r="H45" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-01</v>
@@ -2126,10 +2126,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:34</v>
+        <v>4:01</v>
       </c>
       <c r="H46" t="str">
-        <v>Clinton Kane</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-01</v>
@@ -2164,10 +2164,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:01</v>
+        <v>3:24</v>
       </c>
       <c r="H47" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-01</v>
@@ -2202,10 +2202,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:24</v>
+        <v>5:52</v>
       </c>
       <c r="H48" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-01</v>
@@ -2240,10 +2240,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:52</v>
+        <v>5:01</v>
       </c>
       <c r="H49" t="str">
-        <v>Harry Styles</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-01</v>
@@ -2278,10 +2278,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>5:01</v>
+        <v>4:12</v>
       </c>
       <c r="H50" t="str">
-        <v>Neal Francis</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:12</v>
+        <v>3:59</v>
       </c>
       <c r="H51" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B52" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-01</v>
@@ -2354,10 +2354,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:59</v>
+        <v>2:56</v>
       </c>
       <c r="H52" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B53" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-01</v>
@@ -2392,10 +2392,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:56</v>
+        <v>3:46</v>
       </c>
       <c r="H53" t="str">
-        <v>Cliff Richard</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B54" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-01</v>
@@ -2430,10 +2430,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:46</v>
+        <v>4:37</v>
       </c>
       <c r="H54" t="str">
-        <v>Jessie Ware</v>
+        <v>Bella White</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-01</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:37</v>
+        <v>4:06</v>
       </c>
       <c r="H55" t="str">
-        <v>Bella White</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-01</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:06</v>
+        <v>3:54</v>
       </c>
       <c r="H56" t="str">
-        <v>Ryan Wright</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-01</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:54</v>
+        <v>4:10</v>
       </c>
       <c r="H57" t="str">
-        <v>Dove Cameron</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-01</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:10</v>
+        <v>3:26</v>
       </c>
       <c r="H58" t="str">
-        <v>Parker McCollum</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H59" t="str">
-        <v>Matt Hansen</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-01</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H61" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-01</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:01</v>
+        <v>3:05</v>
       </c>
       <c r="H62" t="str">
-        <v>Tauren Wells</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-01</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:05</v>
+        <v>2:27</v>
       </c>
       <c r="H63" t="str">
-        <v>Maiah Manser</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-01</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:27</v>
+        <v>2:34</v>
       </c>
       <c r="H64" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-01</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H65" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-01</v>
@@ -2889,7 +2889,7 @@
         <v>3:13</v>
       </c>
       <c r="H66" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-01</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Louis Tomlinson</v>
+        <v>CAIN</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-01</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:08</v>
+        <v>5:14</v>
       </c>
       <c r="H68" t="str">
-        <v>CAIN</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-01</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>5:14</v>
+        <v>2:59</v>
       </c>
       <c r="H69" t="str">
-        <v>Harry Styles</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-01</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:59</v>
+        <v>4:21</v>
       </c>
       <c r="H70" t="str">
-        <v>Lana Lubany</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-01</v>
@@ -3076,10 +3076,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:21</v>
+        <v>4:09</v>
       </c>
       <c r="H71" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:09</v>
+        <v>2:34</v>
       </c>
       <c r="H72" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:34</v>
+        <v>3:10</v>
       </c>
       <c r="H73" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B74" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-01</v>
@@ -3190,10 +3190,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H74" t="str">
-        <v>Olivia Dean</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-01</v>
@@ -3228,10 +3228,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H75" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-01</v>
@@ -3266,10 +3266,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H76" t="str">
-        <v>The Avett Brothers</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B77" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-01</v>
@@ -3304,10 +3304,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:21</v>
+        <v>7:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Jordana Bryant</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B78" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-01</v>
@@ -3342,10 +3342,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>7:21</v>
+        <v>3:17</v>
       </c>
       <c r="H78" t="str">
-        <v>Katy Perry</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:17</v>
+        <v>3:45</v>
       </c>
       <c r="H79" t="str">
-        <v>Lauren Watkins</v>
+        <v>Tones And I</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:45</v>
+        <v>3:57</v>
       </c>
       <c r="H80" t="str">
-        <v>Tones And I</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-01</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:57</v>
+        <v>3:03</v>
       </c>
       <c r="H81" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-01</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:03</v>
+        <v>4:27</v>
       </c>
       <c r="H82" t="str">
-        <v>Charlie Puth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-01</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:27</v>
+        <v>4:34</v>
       </c>
       <c r="H83" t="str">
-        <v>Chappell Roan</v>
+        <v>Armik</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-01</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:34</v>
+        <v>2:54</v>
       </c>
       <c r="H84" t="str">
-        <v>Armik</v>
+        <v>LØLØ</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-01</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:54</v>
+        <v>3:25</v>
       </c>
       <c r="H85" t="str">
-        <v>LØLØ</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-01</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:25</v>
+        <v>2:01</v>
       </c>
       <c r="H86" t="str">
-        <v>Tenille Townes</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-01</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:01</v>
+        <v>2:25</v>
       </c>
       <c r="H87" t="str">
-        <v>Alan Walker</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-01</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:25</v>
+        <v>1:14</v>
       </c>
       <c r="H88" t="str">
-        <v>Charli xcx</v>
+        <v>Labrinth</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-01</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>1:14</v>
+        <v>2:59</v>
       </c>
       <c r="H89" t="str">
-        <v>Labrinth</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-01</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:59</v>
+        <v>2:29</v>
       </c>
       <c r="H90" t="str">
-        <v>Charlie Puth</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-01</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:29</v>
+        <v>2:34</v>
       </c>
       <c r="H91" t="str">
-        <v>Girl Tones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-01</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:34</v>
+        <v>3:48</v>
       </c>
       <c r="H92" t="str">
-        <v>Jagwar Twin</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-01</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:48</v>
+        <v>3:32</v>
       </c>
       <c r="H93" t="str">
-        <v>Caroline Jones</v>
+        <v>The Beaches</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-01</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:32</v>
+        <v>3:49</v>
       </c>
       <c r="H94" t="str">
-        <v>The Beaches</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-01</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:49</v>
+        <v>4:28</v>
       </c>
       <c r="H95" t="str">
-        <v>Dolly Parton</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-01</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:28</v>
+        <v>3:37</v>
       </c>
       <c r="H96" t="str">
-        <v>Madison Beer</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-01</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:37</v>
+        <v>3:35</v>
       </c>
       <c r="H97" t="str">
-        <v>Ty Myers</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-01</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:35</v>
+        <v>2:31</v>
       </c>
       <c r="H98" t="str">
-        <v>Megan Moroney</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-01</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:31</v>
+        <v>3:21</v>
       </c>
       <c r="H99" t="str">
-        <v>Julia Cole Music</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-01</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:21</v>
+        <v>5:24</v>
       </c>
       <c r="H100" t="str">
-        <v>Lily Allen</v>
+        <v>Nickless</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-01</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:24</v>
+        <v>3:11</v>
       </c>
       <c r="H101" t="str">
-        <v>Nickless</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Body</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>OCTANE</v>
       </c>
       <c r="G102" t="str">
-        <v>3:11</v>
+        <v>2:35</v>
       </c>
       <c r="H102" t="str">
-        <v>Peach PRC</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/body/1871258329</v>
       </c>
       <c r="L102" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Body - Don Toliver</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Body</v>
+        <v>Dandelion</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/body/1871258331</v>
+        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>OCTANE</v>
+        <v>Dandelion</v>
       </c>
       <c r="G103" t="str">
-        <v>2:35</v>
+        <v>4:00</v>
       </c>
       <c r="H103" t="str">
-        <v>Don Toliver</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/body/1871258329</v>
+        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
       </c>
       <c r="L103" t="str">
-        <v>Body - Don Toliver</v>
+        <v>Dandelion - Ella Langley</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Dandelion</v>
+        <v>LIGHTS GO OUT</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
+        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>LIGHTS GO OUT - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>4:00</v>
+        <v>2:38</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>John Summit</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
+        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
       </c>
       <c r="L104" t="str">
-        <v>Dandelion - Ella Langley</v>
+        <v>LIGHTS GO OUT - John Summit</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>LIGHTS GO OUT</v>
+        <v>The Great Divide</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
+        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>LIGHTS GO OUT - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G105" t="str">
-        <v>2:38</v>
+        <v>5:17</v>
       </c>
       <c r="H105" t="str">
-        <v>John Summit</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
+        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
       </c>
       <c r="L105" t="str">
-        <v>LIGHTS GO OUT - John Summit</v>
+        <v>The Great Divide - Noah Kahan</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>The Great Divide</v>
+        <v>tristón</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
+        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide</v>
+        <v>tristón - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>5:17</v>
+        <v>3:36</v>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
+        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
       </c>
       <c r="L106" t="str">
-        <v>The Great Divide - Noah Kahan</v>
+        <v>tristón - Fuerza Regida</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>tristón</v>
+        <v>Feed the Streets</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
+        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>tristón - Single</v>
+        <v>Feed the Streets - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H107" t="str">
-        <v>Fuerza Regida</v>
+        <v>Rod Wave</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
+        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
       </c>
       <c r="L107" t="str">
-        <v>tristón - Fuerza Regida</v>
+        <v>Feed the Streets - Rod Wave</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Feed the Streets</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Feed the Streets - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G108" t="str">
-        <v>2:58</v>
+        <v>2:30</v>
       </c>
       <c r="H108" t="str">
-        <v>Rod Wave</v>
+        <v>Thundercat</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L108" t="str">
-        <v>Feed the Streets - Rod Wave</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>I Did This To Myself</v>
+        <v>For Hire</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Distracted</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:30</v>
+        <v>3:44</v>
       </c>
       <c r="H109" t="str">
-        <v>Thundercat</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L109" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>For Hire</v>
+        <v>McArthur</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>For Hire - Single</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:44</v>
+        <v>3:51</v>
       </c>
       <c r="H110" t="str">
-        <v>People I’ve Met</v>
+        <v>HARDY</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L110" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>McArthur</v>
+        <v>Debris</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>McArthur - Single</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G111" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H111" t="str">
-        <v>HARDY</v>
+        <v>Labrinth</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L111" t="str">
-        <v>McArthur - HARDY</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Debris</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G112" t="str">
-        <v>2:55</v>
+        <v>3:25</v>
       </c>
       <c r="H112" t="str">
-        <v>Labrinth</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L112" t="str">
-        <v>Debris - Labrinth</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:25</v>
+        <v>4:38</v>
       </c>
       <c r="H113" t="str">
-        <v>Militarie Gun</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L113" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>1+1</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:38</v>
+        <v>3:06</v>
       </c>
       <c r="H114" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Maluma</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L114" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>1+1</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>1+1 - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:06</v>
+        <v>3:08</v>
       </c>
       <c r="H115" t="str">
-        <v>Maluma</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L115" t="str">
-        <v>1+1 - Maluma</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:08</v>
+        <v>3:02</v>
       </c>
       <c r="H116" t="str">
-        <v>MJ Cole</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L116" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Two Car Garage</v>
+        <v>fml .</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G117" t="str">
-        <v>3:02</v>
+        <v>2:40</v>
       </c>
       <c r="H117" t="str">
-        <v>Jon Bellion</v>
+        <v>fakemink</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L117" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>fml .</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:40</v>
+        <v>3:01</v>
       </c>
       <c r="H118" t="str">
-        <v>fakemink</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L118" t="str">
-        <v>fml . - fakemink</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Faked It All The Time</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:01</v>
+        <v>3:08</v>
       </c>
       <c r="H119" t="str">
-        <v>Allie Sherlock</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L119" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>House of the Rising Sun</v>
+        <v>Lorelei</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:08</v>
+        <v>2:35</v>
       </c>
       <c r="H120" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>ERNEST</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L120" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Lorelei</v>
+        <v>Free</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Lorelei - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:35</v>
+        <v>3:56</v>
       </c>
       <c r="H121" t="str">
-        <v>ERNEST</v>
+        <v>SLANDER</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L121" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Free</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Free - Single</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:56</v>
+        <v>2:55</v>
       </c>
       <c r="H122" t="str">
-        <v>SLANDER</v>
+        <v>Artemas</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L122" t="str">
-        <v>Free - SLANDER</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>professional heartbreaker</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G123" t="str">
-        <v>2:55</v>
+        <v>3:56</v>
       </c>
       <c r="H123" t="str">
-        <v>Artemas</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L123" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>tell me what you want</v>
+        <v>Aguas</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>ACT II</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:56</v>
+        <v>2:52</v>
       </c>
       <c r="H124" t="str">
-        <v>Sasha Keable</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L124" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Aguas</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Aguas - Single</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H125" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L125" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Ants In My Room</v>
+        <v>Baddie</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Bohemio</v>
       </c>
       <c r="G126" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H126" t="str">
-        <v>Carter Vail</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L126" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Baddie</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Bohemio</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:11</v>
+        <v>3:51</v>
       </c>
       <c r="H127" t="str">
-        <v>Nicky Jam</v>
+        <v>Tems</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L127" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:51</v>
+        <v>3:16</v>
       </c>
       <c r="H128" t="str">
-        <v>Tems</v>
+        <v>Fred again..</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L128" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:16</v>
+        <v>3:50</v>
       </c>
       <c r="H129" t="str">
-        <v>Fred again..</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L129" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G130" t="str">
-        <v>3:50</v>
+        <v>3:33</v>
       </c>
       <c r="H130" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L130" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>For The First Time, Again</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>For The First Time, Again</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:33</v>
+        <v>3:17</v>
       </c>
       <c r="H131" t="str">
-        <v>Tyler Ballgame</v>
+        <v>Kneecap</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L131" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Liars Tale</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Liars Tale - Single</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:17</v>
+        <v>4:38</v>
       </c>
       <c r="H132" t="str">
-        <v>Kneecap</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L132" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:38</v>
+        <v>3:49</v>
       </c>
       <c r="H133" t="str">
-        <v>Motionless In White</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L133" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Wake Up Calling</v>
+        <v>HIGH</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G134" t="str">
-        <v>3:49</v>
+        <v>3:23</v>
       </c>
       <c r="H134" t="str">
-        <v>Papa Roach</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L134" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>HIGH</v>
+        <v>Villain</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Reflections</v>
       </c>
       <c r="G135" t="str">
-        <v>3:23</v>
+        <v>3:53</v>
       </c>
       <c r="H135" t="str">
-        <v>Magnolia Park</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L135" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Villain</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Reflections</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G136" t="str">
-        <v>3:53</v>
+        <v>3:00</v>
       </c>
       <c r="H136" t="str">
-        <v>From Ashes to New</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L136" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Residue</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G137" t="str">
-        <v>3:00</v>
+        <v>3:28</v>
       </c>
       <c r="H137" t="str">
-        <v>Caleb Chan</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L137" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Residue</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>The Moment (The Score)</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G138" t="str">
-        <v>3:28</v>
+        <v>2:12</v>
       </c>
       <c r="H138" t="str">
-        <v>A. G. Cook</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L138" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Starlight</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G139" t="str">
-        <v>2:12</v>
+        <v>3:21</v>
       </c>
       <c r="H139" t="str">
-        <v>Joyce Manor</v>
+        <v>Cannons</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L139" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Starlight</v>
+        <v>Dandelion</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Everything Glows</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G140" t="str">
-        <v>3:21</v>
+        <v>3:14</v>
       </c>
       <c r="H140" t="str">
-        <v>Cannons</v>
+        <v>Dogpark</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L140" t="str">
-        <v>Starlight - Cannons</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Dandelion</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G141" t="str">
-        <v>3:14</v>
+        <v>2:46</v>
       </c>
       <c r="H141" t="str">
-        <v>Dogpark</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L141" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>THEMSELVES</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>BACKWARD</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G142" t="str">
-        <v>2:46</v>
+        <v>2:24</v>
       </c>
       <c r="H142" t="str">
-        <v>Jordan Ward</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L142" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>High Maintenance</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Miracle Mile</v>
+        <v>Da Realest</v>
       </c>
       <c r="G143" t="str">
-        <v>2:24</v>
+        <v>1:59</v>
       </c>
       <c r="H143" t="str">
-        <v>Paul Russell</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L143" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Trackhawk</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Da Realest</v>
+        <v>Xavier</v>
       </c>
       <c r="G144" t="str">
-        <v>1:59</v>
+        <v>3:05</v>
       </c>
       <c r="H144" t="str">
-        <v>Babyfxce E</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L144" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Wheel Man</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Xavier</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:05</v>
+        <v>3:02</v>
       </c>
       <c r="H145" t="str">
-        <v>xaviersobased</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L145" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Natural Disaster</v>
+        <v>Prettier</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:02</v>
+        <v>2:34</v>
       </c>
       <c r="H146" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L146" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Prettier</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Prettier - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:34</v>
+        <v>3:21</v>
       </c>
       <c r="H147" t="str">
-        <v>Grace VanderWaal</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L147" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:21</v>
+        <v>3:20</v>
       </c>
       <c r="H148" t="str">
-        <v>NLE Choppa</v>
+        <v>The Maine</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L148" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Die To Fall</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Die To Fall - Single</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:20</v>
+        <v>2:58</v>
       </c>
       <c r="H149" t="str">
-        <v>The Maine</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L149" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G150" t="str">
-        <v>2:58</v>
+        <v>2:14</v>
       </c>
       <c r="H150" t="str">
-        <v>Steve Aoki</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L150" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Slow Burn</v>
+        <v>Too Late</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/too-late/1866685876</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Still There’s a Glow</v>
+        <v>Too Late - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>2:14</v>
+        <v>2:56</v>
       </c>
       <c r="H151" t="str">
-        <v>Sweet Pill</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/too-late/1866685875</v>
       </c>
       <c r="L151" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Too Late</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/too-late/1866685876</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Too Late - EP</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:56</v>
+        <v>2:50</v>
       </c>
       <c r="H152" t="str">
-        <v>Hunter Hayes</v>
+        <v>i-dle</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/too-late/1866685875</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L152" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G153" t="str">
-        <v>2:50</v>
+        <v>1:55</v>
       </c>
       <c r="H153" t="str">
-        <v>i-dle</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L153" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Thank You Is Enough</v>
+        <v>RIDIN</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>1:55</v>
+        <v>2:00</v>
       </c>
       <c r="H154" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>Tokischa</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L154" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>RIDIN</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>RIDIN - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:00</v>
+        <v>3:07</v>
       </c>
       <c r="H155" t="str">
-        <v>Tokischa</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L155" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>POSSESSION</v>
+        <v>Poema</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>POSSESSION - Single</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:07</v>
+        <v>3:14</v>
       </c>
       <c r="H156" t="str">
-        <v>Melanie Martinez</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L156" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Poema</v>
+        <v>Live Without</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Poema - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G157" t="str">
-        <v>3:14</v>
+        <v>2:55</v>
       </c>
       <c r="H157" t="str">
-        <v>Óscar Maydon</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L157" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Live Without</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:55</v>
+        <v>3:55</v>
       </c>
       <c r="H158" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Blessd</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L158" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>FANÁTICO</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:55</v>
+        <v>3:29</v>
       </c>
       <c r="H159" t="str">
-        <v>Blessd</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L159" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Frozen Lake</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:29</v>
+        <v>2:45</v>
       </c>
       <c r="H160" t="str">
-        <v>VOILÀ</v>
+        <v>VEDO</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L160" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:45</v>
+        <v>3:32</v>
       </c>
       <c r="H161" t="str">
-        <v>VEDO</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L161" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G162" t="str">
-        <v>3:32</v>
+        <v>3:20</v>
       </c>
       <c r="H162" t="str">
-        <v>Chris Lorenzo</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L162" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>It’s Like That</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>A Pound of Feathers</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:20</v>
+        <v>2:48</v>
       </c>
       <c r="H163" t="str">
-        <v>The Black Crowes</v>
+        <v>Mýa</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L163" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>A.S.A.P.</v>
+        <v>Once I Say</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>3:21</v>
       </c>
       <c r="H164" t="str">
-        <v>Mýa</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L164" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Once I Say</v>
+        <v>believer</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>PASSION</v>
+        <v>believer - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:21</v>
+        <v>2:57</v>
       </c>
       <c r="H165" t="str">
-        <v>Terrace Martin</v>
+        <v>Yuna</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L165" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>believer</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>believer - Single</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:57</v>
+        <v>3:51</v>
       </c>
       <c r="H166" t="str">
-        <v>Yuna</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L166" t="str">
-        <v>believer - Yuna</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>I Envy The Wind</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G167" t="str">
-        <v>3:51</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>Molly Parden</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L167" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Alchemist</v>
+        <v>Daysa</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Alchemist</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:13</v>
+        <v>4:36</v>
       </c>
       <c r="H168" t="str">
-        <v>Bre Kennedy</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L168" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Daysa</v>
+        <v>Fabulous</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Daysa - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:36</v>
+        <v>2:33</v>
       </c>
       <c r="H169" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>MEEK</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L169" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Fabulous</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Fabulous - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:33</v>
+        <v>3:22</v>
       </c>
       <c r="H170" t="str">
-        <v>MEEK</v>
+        <v>RUBIO</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L170" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>brainchem</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:22</v>
+        <v>2:28</v>
       </c>
       <c r="H171" t="str">
-        <v>RUBIO</v>
+        <v>EMJAY</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L171" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>brainchem</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>brainchem - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G172" t="str">
-        <v>2:28</v>
+        <v>2:48</v>
       </c>
       <c r="H172" t="str">
-        <v>EMJAY</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L172" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>Giants</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>With No Due Respect</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:48</v>
+        <v>3:12</v>
       </c>
       <c r="H173" t="str">
-        <v>Foggieraw</v>
+        <v>Picture This</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L173" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Giants</v>
+        <v>Scooby</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Giants - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:12</v>
+        <v>3:41</v>
       </c>
       <c r="H174" t="str">
-        <v>Picture This</v>
+        <v>corook</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L174" t="str">
-        <v>Giants - Picture This</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Scooby</v>
+        <v>La Racha</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Scooby - Single</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:41</v>
+        <v>2:48</v>
       </c>
       <c r="H175" t="str">
-        <v>corook</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L175" t="str">
-        <v>Scooby - corook</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>La Racha</v>
+        <v>So Am I</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>La Racha - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G176" t="str">
-        <v>2:48</v>
+        <v>2:50</v>
       </c>
       <c r="H176" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L176" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>So Am I</v>
+        <v>best thing</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:50</v>
+        <v>4:27</v>
       </c>
       <c r="H177" t="str">
-        <v>Katelyn Tarver</v>
+        <v>WRABEL</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L177" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>best thing</v>
+        <v>Count It Back</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>best thing - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G178" t="str">
-        <v>4:27</v>
+        <v>2:52</v>
       </c>
       <c r="H178" t="str">
-        <v>WRABEL</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L178" t="str">
-        <v>best thing - WRABEL</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Count It Back</v>
+        <v>Good Girl</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Magic Boy</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:52</v>
+        <v>4:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Bartees Strange</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L179" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Good Girl</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Good Girl - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G180" t="str">
-        <v>4:23</v>
+        <v>3:34</v>
       </c>
       <c r="H180" t="str">
-        <v>Paris Paloma</v>
+        <v>MORGXN</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L180" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>MY REVIVAL</v>
+        <v>Run My Way</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:34</v>
+        <v>2:44</v>
       </c>
       <c r="H181" t="str">
-        <v>MORGXN</v>
+        <v>December 10</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L181" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Run My Way</v>
+        <v>Cold Night</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Run My Way - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:44</v>
+        <v>3:12</v>
       </c>
       <c r="H182" t="str">
-        <v>December 10</v>
+        <v>HANA</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L182" t="str">
-        <v>Run My Way - December 10</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Cold Night</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Cold Night - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:12</v>
+        <v>2:28</v>
       </c>
       <c r="H183" t="str">
-        <v>HANA</v>
+        <v>LUNA</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L183" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Away With The Fairies</v>
+        <v>Fragile</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:28</v>
+        <v>3:10</v>
       </c>
       <c r="H184" t="str">
-        <v>LUNA</v>
+        <v>Anajah</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L184" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Fragile</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Fragile - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:10</v>
+        <v>2:04</v>
       </c>
       <c r="H185" t="str">
-        <v>Anajah</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L185" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Slow Dancin'</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:04</v>
+        <v>3:04</v>
       </c>
       <c r="H186" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L186" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:04</v>
+        <v>3:41</v>
       </c>
       <c r="H187" t="str">
-        <v>Lily Meola</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L187" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>More Of What Matters</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>ONE</v>
       </c>
       <c r="G188" t="str">
-        <v>3:41</v>
+        <v>3:46</v>
       </c>
       <c r="H188" t="str">
-        <v>Jamey Johnson</v>
+        <v>Sevendust</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L188" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Is This The Real You</v>
+        <v>Hud</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>ONE</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G189" t="str">
-        <v>3:46</v>
+        <v>4:46</v>
       </c>
       <c r="H189" t="str">
-        <v>Sevendust</v>
+        <v>MØL</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L189" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Hud</v>
+        <v>Ego Death</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>DREAMCRUSH</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:46</v>
+        <v>2:12</v>
       </c>
       <c r="H190" t="str">
-        <v>MØL</v>
+        <v>Atreyu</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L190" t="str">
-        <v>Hud - MØL</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Ego Death</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Ego Death - Single</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:12</v>
+        <v>4:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Atreyu</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L191" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Disappear</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G192" t="str">
-        <v>4:05</v>
+        <v>5:50</v>
       </c>
       <c r="H192" t="str">
-        <v>EJ Jones</v>
+        <v>Lane 8</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L192" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Disappear</v>
+        <v>Misbehave</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Disappear</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>5:50</v>
+        <v>3:43</v>
       </c>
       <c r="H193" t="str">
-        <v>Lane 8</v>
+        <v>Aluna</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L193" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Misbehave</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Misbehave - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:43</v>
+        <v>2:47</v>
       </c>
       <c r="H194" t="str">
-        <v>Aluna</v>
+        <v>Alok</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L194" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Club Bizarre</v>
+        <v>Fly</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:47</v>
+        <v>3:04</v>
       </c>
       <c r="H195" t="str">
-        <v>Alok</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L195" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Fly</v>
+        <v>ily anyway</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Fly - Single</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:04</v>
+        <v>3:05</v>
       </c>
       <c r="H196" t="str">
-        <v>Stephen Stanley</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L196" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>ily anyway</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>ily anyway - Single</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G197" t="str">
-        <v>3:05</v>
+        <v>3:35</v>
       </c>
       <c r="H197" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L197" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Nellene - EP</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G198" t="str">
-        <v>3:35</v>
+        <v>3:41</v>
       </c>
       <c r="H198" t="str">
-        <v>Deloyd Elze</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L198" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Kiss Big</v>
+        <v>praxis</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Kiss Big</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G199" t="str">
-        <v>3:41</v>
+        <v>3:28</v>
       </c>
       <c r="H199" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L199" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>praxis</v>
+        <v>House</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Whole World As Vigil</v>
+        <v>House - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:28</v>
+        <v>2:30</v>
       </c>
       <c r="H200" t="str">
-        <v>Lauren Auder</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L200" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>House</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>House - Single</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G201" t="str">
-        <v>2:30</v>
+        <v>3:57</v>
       </c>
       <c r="H201" t="str">
-        <v>Connie Converse</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L201" t="str">
-        <v>House - Connie Converse</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>Brincar</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
       </c>
       <c r="D202" t="str">
         <v>2026-02-01</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>JET LAG - EP</v>
       </c>
       <c r="G202" t="str">
-        <v>3:57</v>
+        <v>3:06</v>
       </c>
       <c r="H202" t="str">
-        <v>Yumi Zouma</v>
+        <v>J Castle</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
       </c>
       <c r="L202" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>Brincar - J Castle</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Brincar</v>
+        <v>Quién</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
       <c r="D203" t="str">
         <v>2026-02-01</v>
@@ -8089,68 +8089,30 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>JET LAG - EP</v>
+        <v>Quién - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:06</v>
+        <v>4:19</v>
       </c>
       <c r="H203" t="str">
-        <v>J Castle</v>
+        <v>Daniela Darcourt</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
       <c r="L203" t="str">
-        <v>Brincar - J Castle</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Quién</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Quién - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>4:19</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Daniela Darcourt</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
-      </c>
-      <c r="L204" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -1693,7 +1693,7 @@
         <v>Beck - Love (Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:14</v>
@@ -1845,7 +1845,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:52</v>

--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -1655,7 +1655,7 @@
         <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:16</v>
@@ -1769,7 +1769,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>4:10</v>
@@ -1807,7 +1807,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:10</v>
@@ -2225,7 +2225,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>5:01</v>
@@ -2263,7 +2263,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:12</v>
@@ -3365,7 +3365,7 @@
         <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v>3:45</v>

--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -1617,7 +1617,7 @@
         <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>4:05</v>
@@ -1731,7 +1731,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>2:57</v>
@@ -2149,7 +2149,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:24</v>
@@ -2187,7 +2187,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>5:52</v>
@@ -2605,7 +2605,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>2:56</v>
@@ -2985,7 +2985,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:59</v>

--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L212"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>יוסף עבאדי - רגעים של אושר</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409439&amp;sid=755baf5a9e427242a5603345f7826207</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>4:58</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>The Warning</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>יוסף עבאדי - רגעים של אושר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
+        <v>יהונתן ישראל - אבא תודה</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409438&amp;sid=755baf5a9e427242a5603345f7826207</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>5:08</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>The Offspring</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
+        <v>יהונתן ישראל - אבא תודה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>דניאל יטיב - תודה</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409437&amp;sid=755baf5a9e427242a5603345f7826207</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-01</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>4:38</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Roxette</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>דניאל יטיב - תודה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>בניה ברבי - מהודו להודו</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409436&amp;sid=755baf5a9e427242a5603345f7826207</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-01</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:50</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Jessie Ware</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>בניה ברבי - מהודו להודו</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>בניה ברבי - מהודו להודו</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409435&amp;sid=755baf5a9e427242a5603345f7826207</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-01</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3:10</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>בניה ברבי - מהודו להודו</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>בן שוקרון - יותר שמיים</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409434&amp;sid=755baf5a9e427242a5603345f7826207</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-01</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>2:44</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Dean Lewis</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>בן שוקרון - יותר שמיים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>אסף בר נתן - אם זה שורף</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409433&amp;sid=755baf5a9e427242a5603345f7826207</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-01</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>2:57</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Take That</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>אסף בר נתן - אם זה שורף</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>איציק וינגרטן - רק מנגינות</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409432&amp;sid=755baf5a9e427242a5603345f7826207</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-01</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>2:39</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>The Cure</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>איציק וינגרטן - רק מנגינות</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>אביחי פרץ - מי לי</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409431&amp;sid=755baf5a9e427242a5603345f7826207</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-01</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>3:07</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>אביחי פרץ - מי לי</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-01</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:47</v>
+        <v>4:58</v>
       </c>
       <c r="H11" t="str">
-        <v>Paris Paloma</v>
+        <v>The Warning</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-01</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:22</v>
+        <v>5:08</v>
       </c>
       <c r="H12" t="str">
-        <v>Zara Larsson</v>
+        <v>The Offspring</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:48</v>
+        <v>4:38</v>
       </c>
       <c r="H13" t="str">
-        <v>only the poets</v>
+        <v>Roxette</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:52</v>
+        <v>3:50</v>
       </c>
       <c r="H14" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-01</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:33</v>
+        <v>3:10</v>
       </c>
       <c r="H15" t="str">
-        <v>David Guetta</v>
+        <v>Joseph</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-01</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:41</v>
+        <v>2:44</v>
       </c>
       <c r="H16" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-01</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:01</v>
+        <v>2:57</v>
       </c>
       <c r="H17" t="str">
-        <v>Ella Langley</v>
+        <v>Take That</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-01</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>2:39</v>
       </c>
       <c r="H18" t="str">
-        <v>Dogpark</v>
+        <v>The Cure</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-01</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:03</v>
+        <v>3:07</v>
       </c>
       <c r="H19" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-01</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:41</v>
+        <v>4:47</v>
       </c>
       <c r="H20" t="str">
-        <v>ERNEST</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:05</v>
+        <v>3:22</v>
       </c>
       <c r="H21" t="str">
-        <v>Labrinth</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:46</v>
+        <v>2:48</v>
       </c>
       <c r="H22" t="str">
-        <v>Grace VanderWaal</v>
+        <v>only the poets</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:32</v>
+        <v>2:52</v>
       </c>
       <c r="H23" t="str">
-        <v>VOILÀ</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:42</v>
+        <v>3:33</v>
       </c>
       <c r="H24" t="str">
-        <v>Cannons</v>
+        <v>David Guetta</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:38</v>
+        <v>2:41</v>
       </c>
       <c r="H25" t="str">
-        <v>Kylie Morgan</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:10</v>
+        <v>4:01</v>
       </c>
       <c r="H26" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:57</v>
+        <v>3:16</v>
       </c>
       <c r="H27" t="str">
-        <v>Willie Nelson</v>
+        <v>Dogpark</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:19</v>
+        <v>3:03</v>
       </c>
       <c r="H28" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:04</v>
+        <v>2:41</v>
       </c>
       <c r="H29" t="str">
-        <v>India Martínez</v>
+        <v>ERNEST</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:16</v>
+        <v>3:05</v>
       </c>
       <c r="H30" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Labrinth</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:58</v>
+        <v>2:46</v>
       </c>
       <c r="H31" t="str">
-        <v>TINI</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:26</v>
+        <v>3:32</v>
       </c>
       <c r="H32" t="str">
-        <v>Charley</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-01</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:05</v>
+        <v>3:42</v>
       </c>
       <c r="H33" t="str">
-        <v>Demi Lovato</v>
+        <v>Cannons</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-01</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:16</v>
+        <v>2:38</v>
       </c>
       <c r="H34" t="str">
-        <v>Teddy Swims</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-01</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:14</v>
+        <v>3:10</v>
       </c>
       <c r="H35" t="str">
-        <v>Beck</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:57</v>
+        <v>3:57</v>
       </c>
       <c r="H36" t="str">
-        <v>The Offspring</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-01</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:10</v>
+        <v>2:19</v>
       </c>
       <c r="H37" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-01</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:10</v>
+        <v>4:04</v>
       </c>
       <c r="H38" t="str">
-        <v>Jason Derulo</v>
+        <v>India Martínez</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:52</v>
+        <v>2:16</v>
       </c>
       <c r="H39" t="str">
-        <v>lights</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:50</v>
+        <v>5:58</v>
       </c>
       <c r="H40" t="str">
-        <v>Telenova</v>
+        <v>TINI</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>I Explained "How Music Works" LIVE At My Concert</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:32</v>
+        <v>3:26</v>
       </c>
       <c r="H41" t="str">
-        <v>Marcin</v>
+        <v>Charley</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>I Explained "How Music Works" LIVE At My Concert - Marcin</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:27</v>
+        <v>4:05</v>
       </c>
       <c r="H42" t="str">
-        <v>We Three</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:01</v>
+        <v>3:16</v>
       </c>
       <c r="H43" t="str">
-        <v>Timebelle Official</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:20</v>
+        <v>3:14</v>
       </c>
       <c r="H44" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Beck</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:34</v>
+        <v>2:57</v>
       </c>
       <c r="H45" t="str">
-        <v>Clinton Kane</v>
+        <v>The Offspring</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:01</v>
+        <v>4:10</v>
       </c>
       <c r="H46" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:24</v>
+        <v>2:10</v>
       </c>
       <c r="H47" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>5:52</v>
+        <v>3:52</v>
       </c>
       <c r="H48" t="str">
-        <v>Harry Styles</v>
+        <v>lights</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:01</v>
+        <v>3:50</v>
       </c>
       <c r="H49" t="str">
-        <v>Neal Francis</v>
+        <v>Telenova</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>I Explained "How Music Works" LIVE At My Concert</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:12</v>
+        <v>5:32</v>
       </c>
       <c r="H50" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Marcin</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>I Explained "How Music Works" LIVE At My Concert - Marcin</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:59</v>
+        <v>4:27</v>
       </c>
       <c r="H51" t="str">
-        <v>Holly Humberstone</v>
+        <v>We Three</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:56</v>
+        <v>3:01</v>
       </c>
       <c r="H52" t="str">
-        <v>Cliff Richard</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:46</v>
+        <v>3:20</v>
       </c>
       <c r="H53" t="str">
-        <v>Jessie Ware</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:37</v>
+        <v>3:34</v>
       </c>
       <c r="H54" t="str">
-        <v>Bella White</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-01</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:06</v>
+        <v>4:01</v>
       </c>
       <c r="H55" t="str">
-        <v>Ryan Wright</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-01</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:54</v>
+        <v>3:24</v>
       </c>
       <c r="H56" t="str">
-        <v>Dove Cameron</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-01</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:10</v>
+        <v>5:52</v>
       </c>
       <c r="H57" t="str">
-        <v>Parker McCollum</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-01</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:26</v>
+        <v>5:01</v>
       </c>
       <c r="H58" t="str">
-        <v>Matt Hansen</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:56</v>
+        <v>4:12</v>
       </c>
       <c r="H59" t="str">
-        <v>Louis Tomlinson</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-01</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H60" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-01</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H61" t="str">
-        <v>Tauren Wells</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-01</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:05</v>
+        <v>3:46</v>
       </c>
       <c r="H62" t="str">
-        <v>Maiah Manser</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-01</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>4:37</v>
       </c>
       <c r="H63" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Bella White</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-01</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:34</v>
+        <v>4:06</v>
       </c>
       <c r="H64" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-01</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:13</v>
+        <v>3:54</v>
       </c>
       <c r="H65" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-01</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:13</v>
+        <v>4:10</v>
       </c>
       <c r="H66" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-01</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:08</v>
+        <v>3:26</v>
       </c>
       <c r="H67" t="str">
-        <v>CAIN</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-01</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:14</v>
+        <v>2:56</v>
       </c>
       <c r="H68" t="str">
-        <v>Harry Styles</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-01</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:59</v>
+        <v>2:56</v>
       </c>
       <c r="H69" t="str">
-        <v>Lana Lubany</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-01</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:21</v>
+        <v>4:01</v>
       </c>
       <c r="H70" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:09</v>
+        <v>3:05</v>
       </c>
       <c r="H71" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H72" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H73" t="str">
-        <v>Olivia Dean</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-01</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:21</v>
+        <v>3:13</v>
       </c>
       <c r="H74" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:06</v>
+        <v>3:13</v>
       </c>
       <c r="H75" t="str">
-        <v>The Avett Brothers</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-01</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:21</v>
+        <v>3:08</v>
       </c>
       <c r="H76" t="str">
-        <v>Jordana Bryant</v>
+        <v>CAIN</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-01</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>7:21</v>
+        <v>5:14</v>
       </c>
       <c r="H77" t="str">
-        <v>Katy Perry</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-01</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:17</v>
+        <v>2:59</v>
       </c>
       <c r="H78" t="str">
-        <v>Lauren Watkins</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:45</v>
+        <v>4:21</v>
       </c>
       <c r="H79" t="str">
-        <v>Tones And I</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:57</v>
+        <v>4:09</v>
       </c>
       <c r="H80" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-01</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:03</v>
+        <v>2:34</v>
       </c>
       <c r="H81" t="str">
-        <v>Charlie Puth</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-01</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:27</v>
+        <v>3:10</v>
       </c>
       <c r="H82" t="str">
-        <v>Chappell Roan</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-01</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:34</v>
+        <v>3:21</v>
       </c>
       <c r="H83" t="str">
-        <v>Armik</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-01</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:54</v>
+        <v>3:06</v>
       </c>
       <c r="H84" t="str">
-        <v>LØLØ</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-01</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:25</v>
+        <v>3:21</v>
       </c>
       <c r="H85" t="str">
-        <v>Tenille Townes</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-01</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:01</v>
+        <v>7:21</v>
       </c>
       <c r="H86" t="str">
-        <v>Alan Walker</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-01</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:25</v>
+        <v>3:17</v>
       </c>
       <c r="H87" t="str">
-        <v>Charli xcx</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-01</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>1:14</v>
+        <v>3:45</v>
       </c>
       <c r="H88" t="str">
-        <v>Labrinth</v>
+        <v>Tones And I</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-01</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:59</v>
+        <v>3:57</v>
       </c>
       <c r="H89" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-01</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:29</v>
+        <v>3:03</v>
       </c>
       <c r="H90" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-01</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:34</v>
+        <v>4:27</v>
       </c>
       <c r="H91" t="str">
-        <v>Jagwar Twin</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-01</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:48</v>
+        <v>4:34</v>
       </c>
       <c r="H92" t="str">
-        <v>Caroline Jones</v>
+        <v>Armik</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-01</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:32</v>
+        <v>2:54</v>
       </c>
       <c r="H93" t="str">
-        <v>The Beaches</v>
+        <v>LØLØ</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-01</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:49</v>
+        <v>3:25</v>
       </c>
       <c r="H94" t="str">
-        <v>Dolly Parton</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-01</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:28</v>
+        <v>2:01</v>
       </c>
       <c r="H95" t="str">
-        <v>Madison Beer</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-01</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:37</v>
+        <v>2:25</v>
       </c>
       <c r="H96" t="str">
-        <v>Ty Myers</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-01</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:35</v>
+        <v>1:14</v>
       </c>
       <c r="H97" t="str">
-        <v>Megan Moroney</v>
+        <v>Labrinth</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-01</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:31</v>
+        <v>2:59</v>
       </c>
       <c r="H98" t="str">
-        <v>Julia Cole Music</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-01</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:21</v>
+        <v>2:29</v>
       </c>
       <c r="H99" t="str">
-        <v>Lily Allen</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-01</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:24</v>
+        <v>2:34</v>
       </c>
       <c r="H100" t="str">
-        <v>Nickless</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-01</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:11</v>
+        <v>3:48</v>
       </c>
       <c r="H101" t="str">
-        <v>Peach PRC</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Body</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/body/1871258331</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>OCTANE</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:35</v>
+        <v>3:32</v>
       </c>
       <c r="H102" t="str">
-        <v>Don Toliver</v>
+        <v>The Beaches</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/body/1871258329</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Body - Don Toliver</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dandelion</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Dandelion</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>4:00</v>
+        <v>3:49</v>
       </c>
       <c r="H103" t="str">
-        <v>Ella Langley</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Dandelion - Ella Langley</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>LIGHTS GO OUT</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>LIGHTS GO OUT - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>2:38</v>
+        <v>4:28</v>
       </c>
       <c r="H104" t="str">
-        <v>John Summit</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>LIGHTS GO OUT - John Summit</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Great Divide</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Great Divide</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>5:17</v>
+        <v>3:37</v>
       </c>
       <c r="H105" t="str">
-        <v>Noah Kahan</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>The Great Divide - Noah Kahan</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>tristón</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>tristón - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:36</v>
+        <v>3:35</v>
       </c>
       <c r="H106" t="str">
-        <v>Fuerza Regida</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>tristón - Fuerza Regida</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Feed the Streets</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Feed the Streets - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:58</v>
+        <v>2:31</v>
       </c>
       <c r="H107" t="str">
-        <v>Rod Wave</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Feed the Streets - Rod Wave</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Did This To Myself</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Distracted</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:30</v>
+        <v>3:21</v>
       </c>
       <c r="H108" t="str">
-        <v>Thundercat</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>For Hire</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>For Hire - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:44</v>
+        <v>5:24</v>
       </c>
       <c r="H109" t="str">
-        <v>People I’ve Met</v>
+        <v>Nickless</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>McArthur</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>McArthur - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:51</v>
+        <v>3:11</v>
       </c>
       <c r="H110" t="str">
-        <v>HARDY</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>McArthur - HARDY</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Debris</v>
+        <v>Body</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>OCTANE</v>
       </c>
       <c r="G111" t="str">
-        <v>2:55</v>
+        <v>2:35</v>
       </c>
       <c r="H111" t="str">
-        <v>Labrinth</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/body/1871258329</v>
       </c>
       <c r="L111" t="str">
-        <v>Debris - Labrinth</v>
+        <v>Body - Don Toliver</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Dandelion</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Dandelion</v>
       </c>
       <c r="G112" t="str">
-        <v>3:25</v>
+        <v>4:00</v>
       </c>
       <c r="H112" t="str">
-        <v>Militarie Gun</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
       </c>
       <c r="L112" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>Dandelion - Ella Langley</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>LIGHTS GO OUT</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>LIGHTS GO OUT - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>4:38</v>
+        <v>2:38</v>
       </c>
       <c r="H113" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>John Summit</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
       </c>
       <c r="L113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>LIGHTS GO OUT - John Summit</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>1+1</v>
+        <v>The Great Divide</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>1+1 - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G114" t="str">
-        <v>3:06</v>
+        <v>5:17</v>
       </c>
       <c r="H114" t="str">
-        <v>Maluma</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
       </c>
       <c r="L114" t="str">
-        <v>1+1 - Maluma</v>
+        <v>The Great Divide - Noah Kahan</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>tristón</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>tristón - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:08</v>
+        <v>3:36</v>
       </c>
       <c r="H115" t="str">
-        <v>MJ Cole</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
       </c>
       <c r="L115" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>tristón - Fuerza Regida</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Two Car Garage</v>
+        <v>Feed the Streets</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>Feed the Streets - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:02</v>
+        <v>2:58</v>
       </c>
       <c r="H116" t="str">
-        <v>Jon Bellion</v>
+        <v>Rod Wave</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
       </c>
       <c r="L116" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>Feed the Streets - Rod Wave</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>fml .</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Distracted</v>
       </c>
       <c r="G117" t="str">
-        <v>2:40</v>
+        <v>2:30</v>
       </c>
       <c r="H117" t="str">
-        <v>fakemink</v>
+        <v>Thundercat</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L117" t="str">
-        <v>fml . - fakemink</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Faked It All The Time</v>
+        <v>For Hire</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:01</v>
+        <v>3:44</v>
       </c>
       <c r="H118" t="str">
-        <v>Allie Sherlock</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L118" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>House of the Rising Sun</v>
+        <v>McArthur</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:08</v>
+        <v>3:51</v>
       </c>
       <c r="H119" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>HARDY</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L119" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Lorelei</v>
+        <v>Debris</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Lorelei - Single</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G120" t="str">
-        <v>2:35</v>
+        <v>2:55</v>
       </c>
       <c r="H120" t="str">
-        <v>ERNEST</v>
+        <v>Labrinth</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L120" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Free</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Free - Single</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G121" t="str">
-        <v>3:56</v>
+        <v>3:25</v>
       </c>
       <c r="H121" t="str">
-        <v>SLANDER</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L121" t="str">
-        <v>Free - SLANDER</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>professional heartbreaker</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:55</v>
+        <v>4:38</v>
       </c>
       <c r="H122" t="str">
-        <v>Artemas</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L122" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>tell me what you want</v>
+        <v>1+1</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ACT II</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:56</v>
+        <v>3:06</v>
       </c>
       <c r="H123" t="str">
-        <v>Sasha Keable</v>
+        <v>Maluma</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L123" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Aguas</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Aguas - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:52</v>
+        <v>3:08</v>
       </c>
       <c r="H124" t="str">
-        <v>Luis R Conriquez</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L124" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Ants In My Room</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:48</v>
+        <v>3:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Carter Vail</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L125" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Baddie</v>
+        <v>fml .</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Bohemio</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G126" t="str">
-        <v>3:11</v>
+        <v>2:40</v>
       </c>
       <c r="H126" t="str">
-        <v>Nicky Jam</v>
+        <v>fakemink</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L126" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:51</v>
+        <v>3:01</v>
       </c>
       <c r="H127" t="str">
-        <v>Tems</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L127" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:16</v>
+        <v>3:08</v>
       </c>
       <c r="H128" t="str">
-        <v>Fred again..</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L128" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>Lorelei</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:50</v>
+        <v>2:35</v>
       </c>
       <c r="H129" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>ERNEST</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>For The First Time, Again</v>
+        <v>Free</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>For The First Time, Again</v>
+        <v>Free - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:33</v>
+        <v>3:56</v>
       </c>
       <c r="H130" t="str">
-        <v>Tyler Ballgame</v>
+        <v>SLANDER</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L130" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Liars Tale</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Liars Tale - Single</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:17</v>
+        <v>2:55</v>
       </c>
       <c r="H131" t="str">
-        <v>Kneecap</v>
+        <v>Artemas</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L131" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G132" t="str">
-        <v>4:38</v>
+        <v>3:56</v>
       </c>
       <c r="H132" t="str">
-        <v>Motionless In White</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L132" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Wake Up Calling</v>
+        <v>Aguas</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:49</v>
+        <v>2:52</v>
       </c>
       <c r="H133" t="str">
-        <v>Papa Roach</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L133" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>HIGH</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:23</v>
+        <v>2:48</v>
       </c>
       <c r="H134" t="str">
-        <v>Magnolia Park</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L134" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Villain</v>
+        <v>Baddie</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Reflections</v>
+        <v>Bohemio</v>
       </c>
       <c r="G135" t="str">
-        <v>3:53</v>
+        <v>3:11</v>
       </c>
       <c r="H135" t="str">
-        <v>From Ashes to New</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L135" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Bad Idea Right?</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:00</v>
+        <v>3:51</v>
       </c>
       <c r="H136" t="str">
-        <v>Caleb Chan</v>
+        <v>Tems</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L136" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Residue</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>The Moment (The Score)</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:28</v>
+        <v>3:16</v>
       </c>
       <c r="H137" t="str">
-        <v>A. G. Cook</v>
+        <v>Fred again..</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L137" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:12</v>
+        <v>3:50</v>
       </c>
       <c r="H138" t="str">
-        <v>Joyce Manor</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L138" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Starlight</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Everything Glows</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G139" t="str">
-        <v>3:21</v>
+        <v>3:33</v>
       </c>
       <c r="H139" t="str">
-        <v>Cannons</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L139" t="str">
-        <v>Starlight - Cannons</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Dandelion</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H140" t="str">
-        <v>Dogpark</v>
+        <v>Kneecap</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L140" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>THEMSELVES</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BACKWARD</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:46</v>
+        <v>4:38</v>
       </c>
       <c r="H141" t="str">
-        <v>Jordan Ward</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L141" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>High Maintenance</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Miracle Mile</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:24</v>
+        <v>3:49</v>
       </c>
       <c r="H142" t="str">
-        <v>Paul Russell</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L142" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Trackhawk</v>
+        <v>HIGH</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Da Realest</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G143" t="str">
-        <v>1:59</v>
+        <v>3:23</v>
       </c>
       <c r="H143" t="str">
-        <v>Babyfxce E</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L143" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Wheel Man</v>
+        <v>Villain</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Xavier</v>
+        <v>Reflections</v>
       </c>
       <c r="G144" t="str">
-        <v>3:05</v>
+        <v>3:53</v>
       </c>
       <c r="H144" t="str">
-        <v>xaviersobased</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L144" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Natural Disaster</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G145" t="str">
-        <v>3:02</v>
+        <v>3:00</v>
       </c>
       <c r="H145" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L145" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Prettier</v>
+        <v>Residue</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Prettier - Single</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G146" t="str">
-        <v>2:34</v>
+        <v>3:28</v>
       </c>
       <c r="H146" t="str">
-        <v>Grace VanderWaal</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L146" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Shotta Flow 8</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G147" t="str">
-        <v>3:21</v>
+        <v>2:12</v>
       </c>
       <c r="H147" t="str">
-        <v>NLE Choppa</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L147" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Die To Fall</v>
+        <v>Starlight</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G148" t="str">
-        <v>3:20</v>
+        <v>3:21</v>
       </c>
       <c r="H148" t="str">
-        <v>The Maine</v>
+        <v>Cannons</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L148" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Dandelion</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>2:58</v>
+        <v>3:14</v>
       </c>
       <c r="H149" t="str">
-        <v>Steve Aoki</v>
+        <v>Dogpark</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Slow Burn</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Still There’s a Glow</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G150" t="str">
-        <v>2:14</v>
+        <v>2:46</v>
       </c>
       <c r="H150" t="str">
-        <v>Sweet Pill</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L150" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Too Late</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/too-late/1866685876</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Too Late - EP</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G151" t="str">
-        <v>2:56</v>
+        <v>2:24</v>
       </c>
       <c r="H151" t="str">
-        <v>Hunter Hayes</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/too-late/1866685875</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L151" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G152" t="str">
-        <v>2:50</v>
+        <v>1:59</v>
       </c>
       <c r="H152" t="str">
-        <v>i-dle</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L152" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Xavier</v>
       </c>
       <c r="G153" t="str">
-        <v>1:55</v>
+        <v>3:05</v>
       </c>
       <c r="H153" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L153" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>RIDIN</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>RIDIN - Single</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:00</v>
+        <v>3:02</v>
       </c>
       <c r="H154" t="str">
-        <v>Tokischa</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L154" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>POSSESSION</v>
+        <v>Prettier</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>POSSESSION - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:07</v>
+        <v>2:34</v>
       </c>
       <c r="H155" t="str">
-        <v>Melanie Martinez</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L155" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Poema</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Poema - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:14</v>
+        <v>3:21</v>
       </c>
       <c r="H156" t="str">
-        <v>Óscar Maydon</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L156" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Live Without</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:55</v>
+        <v>3:20</v>
       </c>
       <c r="H157" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>The Maine</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L157" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>FANÁTICO</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:55</v>
+        <v>2:58</v>
       </c>
       <c r="H158" t="str">
-        <v>Blessd</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L158" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Frozen Lake</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G159" t="str">
-        <v>3:29</v>
+        <v>2:14</v>
       </c>
       <c r="H159" t="str">
-        <v>VOILÀ</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L159" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Too Late</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/too-late/1866685876</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Too Late - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>2:45</v>
+        <v>2:56</v>
       </c>
       <c r="H160" t="str">
-        <v>VEDO</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/too-late/1866685875</v>
       </c>
       <c r="L160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:32</v>
+        <v>2:50</v>
       </c>
       <c r="H161" t="str">
-        <v>Chris Lorenzo</v>
+        <v>i-dle</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>It’s Like That</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G162" t="str">
-        <v>3:20</v>
+        <v>1:55</v>
       </c>
       <c r="H162" t="str">
-        <v>The Black Crowes</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L162" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>A.S.A.P.</v>
+        <v>RIDIN</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:48</v>
+        <v>2:00</v>
       </c>
       <c r="H163" t="str">
-        <v>Mýa</v>
+        <v>Tokischa</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L163" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Once I Say</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>PASSION</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:21</v>
+        <v>3:07</v>
       </c>
       <c r="H164" t="str">
-        <v>Terrace Martin</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L164" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>believer</v>
+        <v>Poema</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>believer - Single</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H165" t="str">
-        <v>Yuna</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L165" t="str">
-        <v>believer - Yuna</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I Envy The Wind</v>
+        <v>Live Without</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G166" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H166" t="str">
-        <v>Molly Parden</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L166" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>The Alchemist</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The Alchemist</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>3:55</v>
       </c>
       <c r="H167" t="str">
-        <v>Bre Kennedy</v>
+        <v>Blessd</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L167" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Daysa</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Daysa - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:36</v>
+        <v>3:29</v>
       </c>
       <c r="H168" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L168" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fabulous</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Fabulous - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:33</v>
+        <v>2:45</v>
       </c>
       <c r="H169" t="str">
-        <v>MEEK</v>
+        <v>VEDO</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L169" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:22</v>
+        <v>3:32</v>
       </c>
       <c r="H170" t="str">
-        <v>RUBIO</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>brainchem</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>brainchem - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G171" t="str">
-        <v>2:28</v>
+        <v>3:20</v>
       </c>
       <c r="H171" t="str">
-        <v>EMJAY</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L171" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>With No Due Respect</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G172" t="str">
         <v>2:48</v>
       </c>
       <c r="H172" t="str">
-        <v>Foggieraw</v>
+        <v>Mýa</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L172" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Giants</v>
+        <v>Once I Say</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Giants - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G173" t="str">
-        <v>3:12</v>
+        <v>3:21</v>
       </c>
       <c r="H173" t="str">
-        <v>Picture This</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L173" t="str">
-        <v>Giants - Picture This</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Scooby</v>
+        <v>believer</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Scooby - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:41</v>
+        <v>2:57</v>
       </c>
       <c r="H174" t="str">
-        <v>corook</v>
+        <v>Yuna</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L174" t="str">
-        <v>Scooby - corook</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>La Racha</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>La Racha - Single</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:48</v>
+        <v>3:51</v>
       </c>
       <c r="H175" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L175" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>So Am I</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G176" t="str">
-        <v>2:50</v>
+        <v>3:13</v>
       </c>
       <c r="H176" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L176" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>best thing</v>
+        <v>Daysa</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>best thing - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:27</v>
+        <v>4:36</v>
       </c>
       <c r="H177" t="str">
-        <v>WRABEL</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L177" t="str">
-        <v>best thing - WRABEL</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Count It Back</v>
+        <v>Fabulous</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Magic Boy</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:52</v>
+        <v>2:33</v>
       </c>
       <c r="H178" t="str">
-        <v>Bartees Strange</v>
+        <v>MEEK</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L178" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Good Girl</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Good Girl - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>4:23</v>
+        <v>3:22</v>
       </c>
       <c r="H179" t="str">
-        <v>Paris Paloma</v>
+        <v>RUBIO</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L179" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>MY REVIVAL</v>
+        <v>brainchem</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:34</v>
+        <v>2:28</v>
       </c>
       <c r="H180" t="str">
-        <v>MORGXN</v>
+        <v>EMJAY</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L180" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Run My Way</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Run My Way - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G181" t="str">
-        <v>2:44</v>
+        <v>2:48</v>
       </c>
       <c r="H181" t="str">
-        <v>December 10</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L181" t="str">
-        <v>Run My Way - December 10</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Cold Night</v>
+        <v>Giants</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Cold Night - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G182" t="str">
         <v>3:12</v>
       </c>
       <c r="H182" t="str">
-        <v>HANA</v>
+        <v>Picture This</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L182" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Away With The Fairies</v>
+        <v>Scooby</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:28</v>
+        <v>3:41</v>
       </c>
       <c r="H183" t="str">
-        <v>LUNA</v>
+        <v>corook</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L183" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fragile</v>
+        <v>La Racha</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Fragile - Single</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:10</v>
+        <v>2:48</v>
       </c>
       <c r="H184" t="str">
-        <v>Anajah</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L184" t="str">
-        <v>Fragile - Anajah</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Slow Dancin'</v>
+        <v>So Am I</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G185" t="str">
-        <v>2:04</v>
+        <v>2:50</v>
       </c>
       <c r="H185" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L185" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>best thing</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:04</v>
+        <v>4:27</v>
       </c>
       <c r="H186" t="str">
-        <v>Lily Meola</v>
+        <v>WRABEL</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L186" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>More Of What Matters</v>
+        <v>Count It Back</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G187" t="str">
-        <v>3:41</v>
+        <v>2:52</v>
       </c>
       <c r="H187" t="str">
-        <v>Jamey Johnson</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L187" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Is This The Real You</v>
+        <v>Good Girl</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>ONE</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:46</v>
+        <v>4:23</v>
       </c>
       <c r="H188" t="str">
-        <v>Sevendust</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L188" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Hud</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>DREAMCRUSH</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G189" t="str">
-        <v>4:46</v>
+        <v>3:34</v>
       </c>
       <c r="H189" t="str">
-        <v>MØL</v>
+        <v>MORGXN</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L189" t="str">
-        <v>Hud - MØL</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Ego Death</v>
+        <v>Run My Way</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Ego Death - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:12</v>
+        <v>2:44</v>
       </c>
       <c r="H190" t="str">
-        <v>Atreyu</v>
+        <v>December 10</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L190" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Cold Night</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:05</v>
+        <v>3:12</v>
       </c>
       <c r="H191" t="str">
-        <v>EJ Jones</v>
+        <v>HANA</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L191" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Disappear</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Disappear</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>5:50</v>
+        <v>2:28</v>
       </c>
       <c r="H192" t="str">
-        <v>Lane 8</v>
+        <v>LUNA</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L192" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Misbehave</v>
+        <v>Fragile</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Misbehave - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:43</v>
+        <v>3:10</v>
       </c>
       <c r="H193" t="str">
-        <v>Aluna</v>
+        <v>Anajah</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L193" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Club Bizarre</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:47</v>
+        <v>2:04</v>
       </c>
       <c r="H194" t="str">
-        <v>Alok</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L194" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Fly</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Fly - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G195" t="str">
         <v>3:04</v>
       </c>
       <c r="H195" t="str">
-        <v>Stephen Stanley</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L195" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>ily anyway</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>ily anyway - Single</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:05</v>
+        <v>3:41</v>
       </c>
       <c r="H196" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L196" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Nellene - EP</v>
+        <v>ONE</v>
       </c>
       <c r="G197" t="str">
-        <v>3:35</v>
+        <v>3:46</v>
       </c>
       <c r="H197" t="str">
-        <v>Deloyd Elze</v>
+        <v>Sevendust</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L197" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Kiss Big</v>
+        <v>Hud</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Kiss Big</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G198" t="str">
-        <v>3:41</v>
+        <v>4:46</v>
       </c>
       <c r="H198" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>MØL</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L198" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>praxis</v>
+        <v>Ego Death</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:28</v>
+        <v>2:12</v>
       </c>
       <c r="H199" t="str">
-        <v>Lauren Auder</v>
+        <v>Atreyu</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L199" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>House</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>House - Single</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>2:30</v>
+        <v>4:05</v>
       </c>
       <c r="H200" t="str">
-        <v>Connie Converse</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L200" t="str">
-        <v>House - Connie Converse</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>Disappear</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>Disappear</v>
       </c>
       <c r="G201" t="str">
-        <v>3:57</v>
+        <v>5:50</v>
       </c>
       <c r="H201" t="str">
-        <v>Yumi Zouma</v>
+        <v>Lane 8</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L201" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Brincar</v>
+        <v>Misbehave</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D202" t="str">
         <v>2026-02-01</v>
@@ -8051,68 +8051,410 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>JET LAG - EP</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:06</v>
+        <v>3:43</v>
       </c>
       <c r="H202" t="str">
-        <v>J Castle</v>
+        <v>Aluna</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L202" t="str">
-        <v>Brincar - J Castle</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
+        <v>Club Bizarre</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Club Bizarre - Single</v>
+      </c>
+      <c r="G203" t="str">
+        <v>2:47</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Alok</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Club Bizarre - Alok</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Fly</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Fly - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>3:04</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Stephen Stanley</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Fly - Stephen Stanley</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>ily anyway</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>ily anyway - Single</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:05</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Strings &amp; Heart</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+      </c>
+      <c r="L205" t="str">
+        <v>ily anyway - Strings &amp; Heart</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>George Jones (feat. Angela Autumn)</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Nellene - EP</v>
+      </c>
+      <c r="G206" t="str">
+        <v>3:35</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Deloyd Elze</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+      </c>
+      <c r="L206" t="str">
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Kiss Big</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Kiss Big</v>
+      </c>
+      <c r="G207" t="str">
+        <v>3:41</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Ailbhe Reddy</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Kiss Big - Ailbhe Reddy</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>praxis</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Whole World As Vigil</v>
+      </c>
+      <c r="G208" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Lauren Auder</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+      </c>
+      <c r="L208" t="str">
+        <v>praxis - Lauren Auder</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>House</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/house/1866696487</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>House - Single</v>
+      </c>
+      <c r="G209" t="str">
+        <v>2:30</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Connie Converse</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/house/1866696486</v>
+      </c>
+      <c r="L209" t="str">
+        <v>House - Connie Converse</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Cowboy Without a Clue</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>No Love Lost to Kindness</v>
+      </c>
+      <c r="G210" t="str">
+        <v>3:57</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Yumi Zouma</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G211" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H211" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
         <v>Quién</v>
       </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D203" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
+      <c r="D212" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G203" t="str">
+      <c r="G212" t="str">
         <v>4:19</v>
       </c>
-      <c r="H203" t="str">
+      <c r="H212" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K203" t="str">
+      <c r="K212" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L203" t="str">
+      <c r="L212" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L212"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L212"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוסף עבאדי - רגעים של אושר</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409439&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:58</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>The Warning</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוסף עבאדי - רגעים של אושר</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יהונתן ישראל - אבא תודה</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409438&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>5:08</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>The Offspring</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יהונתן ישראל - אבא תודה</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דניאל יטיב - תודה</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409437&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-01</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>4:38</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Roxette</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דניאל יטיב - תודה</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409436&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-01</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>3:50</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Jessie Ware</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409435&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-01</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>3:10</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>בן שוקרון - יותר שמיים</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409434&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-01</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>2:44</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Dean Lewis</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>בן שוקרון - יותר שמיים</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אסף בר נתן - אם זה שורף</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409433&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-01</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>2:57</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Take That</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אסף בר נתן - אם זה שורף</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>איציק וינגרטן - רק מנגינות</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409432&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-01</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>2:39</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>The Cure</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>איציק וינגרטן - רק מנגינות</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אביחי פרץ - מי לי</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409431&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-01</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>3:07</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אביחי פרץ - מי לי</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-01</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:58</v>
+        <v>4:47</v>
       </c>
       <c r="H11" t="str">
-        <v>The Warning</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-01</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:08</v>
+        <v>3:22</v>
       </c>
       <c r="H12" t="str">
-        <v>The Offspring</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:38</v>
+        <v>2:48</v>
       </c>
       <c r="H13" t="str">
-        <v>Roxette</v>
+        <v>only the poets</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:50</v>
+        <v>2:52</v>
       </c>
       <c r="H14" t="str">
-        <v>Jessie Ware</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-01</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:10</v>
+        <v>3:33</v>
       </c>
       <c r="H15" t="str">
-        <v>Joseph</v>
+        <v>David Guetta</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-01</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:44</v>
+        <v>2:41</v>
       </c>
       <c r="H16" t="str">
-        <v>Dean Lewis</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-01</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:57</v>
+        <v>4:01</v>
       </c>
       <c r="H17" t="str">
-        <v>Take That</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-01</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:39</v>
+        <v>3:16</v>
       </c>
       <c r="H18" t="str">
-        <v>The Cure</v>
+        <v>Dogpark</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-01</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:07</v>
+        <v>3:03</v>
       </c>
       <c r="H19" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-01</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:47</v>
+        <v>2:41</v>
       </c>
       <c r="H20" t="str">
-        <v>Paris Paloma</v>
+        <v>ERNEST</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:22</v>
+        <v>3:05</v>
       </c>
       <c r="H21" t="str">
-        <v>Zara Larsson</v>
+        <v>Labrinth</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:48</v>
+        <v>2:46</v>
       </c>
       <c r="H22" t="str">
-        <v>only the poets</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:52</v>
+        <v>3:32</v>
       </c>
       <c r="H23" t="str">
-        <v>Katelyn Tarver</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:33</v>
+        <v>3:42</v>
       </c>
       <c r="H24" t="str">
-        <v>David Guetta</v>
+        <v>Cannons</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:41</v>
+        <v>2:38</v>
       </c>
       <c r="H25" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:01</v>
+        <v>3:10</v>
       </c>
       <c r="H26" t="str">
-        <v>Ella Langley</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:16</v>
+        <v>3:57</v>
       </c>
       <c r="H27" t="str">
-        <v>Dogpark</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:03</v>
+        <v>2:19</v>
       </c>
       <c r="H28" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:41</v>
+        <v>4:04</v>
       </c>
       <c r="H29" t="str">
-        <v>ERNEST</v>
+        <v>India Martínez</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:05</v>
+        <v>2:16</v>
       </c>
       <c r="H30" t="str">
-        <v>Labrinth</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:46</v>
+        <v>5:58</v>
       </c>
       <c r="H31" t="str">
-        <v>Grace VanderWaal</v>
+        <v>TINI</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:32</v>
+        <v>3:26</v>
       </c>
       <c r="H32" t="str">
-        <v>VOILÀ</v>
+        <v>Charley</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-01</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:42</v>
+        <v>4:05</v>
       </c>
       <c r="H33" t="str">
-        <v>Cannons</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-01</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:38</v>
+        <v>3:16</v>
       </c>
       <c r="H34" t="str">
-        <v>Kylie Morgan</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-01</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:10</v>
+        <v>3:14</v>
       </c>
       <c r="H35" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Beck</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:57</v>
+        <v>2:57</v>
       </c>
       <c r="H36" t="str">
-        <v>Willie Nelson</v>
+        <v>The Offspring</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-01</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:19</v>
+        <v>4:10</v>
       </c>
       <c r="H37" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-01</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:04</v>
+        <v>2:10</v>
       </c>
       <c r="H38" t="str">
-        <v>India Martínez</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:16</v>
+        <v>3:52</v>
       </c>
       <c r="H39" t="str">
-        <v>Chelsea Cutler</v>
+        <v>lights</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>5:58</v>
+        <v>3:50</v>
       </c>
       <c r="H40" t="str">
-        <v>TINI</v>
+        <v>Telenova</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>I Explained "How Music Works" LIVE At My Concert</v>
       </c>
       <c r="B41" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:26</v>
+        <v>5:32</v>
       </c>
       <c r="H41" t="str">
-        <v>Charley</v>
+        <v>Marcin</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>I Explained "How Music Works" LIVE At My Concert - Marcin</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:05</v>
+        <v>4:27</v>
       </c>
       <c r="H42" t="str">
-        <v>Demi Lovato</v>
+        <v>We Three</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:16</v>
+        <v>3:01</v>
       </c>
       <c r="H43" t="str">
-        <v>Teddy Swims</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B44" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:14</v>
+        <v>3:20</v>
       </c>
       <c r="H44" t="str">
-        <v>Beck</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:57</v>
+        <v>3:34</v>
       </c>
       <c r="H45" t="str">
-        <v>The Offspring</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:10</v>
+        <v>4:01</v>
       </c>
       <c r="H46" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B47" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:10</v>
+        <v>3:24</v>
       </c>
       <c r="H47" t="str">
-        <v>Jason Derulo</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:52</v>
+        <v>5:52</v>
       </c>
       <c r="H48" t="str">
-        <v>lights</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B49" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:50</v>
+        <v>5:01</v>
       </c>
       <c r="H49" t="str">
-        <v>Telenova</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>I Explained "How Music Works" LIVE At My Concert</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B50" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>5:32</v>
+        <v>4:12</v>
       </c>
       <c r="H50" t="str">
-        <v>Marcin</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>I Explained "How Music Works" LIVE At My Concert - Marcin</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:27</v>
+        <v>3:59</v>
       </c>
       <c r="H51" t="str">
-        <v>We Three</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B52" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:01</v>
+        <v>2:56</v>
       </c>
       <c r="H52" t="str">
-        <v>Timebelle Official</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:20</v>
+        <v>3:46</v>
       </c>
       <c r="H53" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:34</v>
+        <v>4:37</v>
       </c>
       <c r="H54" t="str">
-        <v>Clinton Kane</v>
+        <v>Bella White</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-01</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:01</v>
+        <v>4:06</v>
       </c>
       <c r="H55" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-01</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:24</v>
+        <v>3:54</v>
       </c>
       <c r="H56" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-01</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:52</v>
+        <v>4:10</v>
       </c>
       <c r="H57" t="str">
-        <v>Harry Styles</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-01</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>5:01</v>
+        <v>3:26</v>
       </c>
       <c r="H58" t="str">
-        <v>Neal Francis</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:12</v>
+        <v>2:56</v>
       </c>
       <c r="H59" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-01</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:59</v>
+        <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>Holly Humberstone</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-01</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H61" t="str">
-        <v>Cliff Richard</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-01</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:46</v>
+        <v>3:05</v>
       </c>
       <c r="H62" t="str">
-        <v>Jessie Ware</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-01</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:37</v>
+        <v>2:27</v>
       </c>
       <c r="H63" t="str">
-        <v>Bella White</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-01</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:06</v>
+        <v>2:34</v>
       </c>
       <c r="H64" t="str">
-        <v>Ryan Wright</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-01</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:54</v>
+        <v>3:13</v>
       </c>
       <c r="H65" t="str">
-        <v>Dove Cameron</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-01</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:10</v>
+        <v>3:13</v>
       </c>
       <c r="H66" t="str">
-        <v>Parker McCollum</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-01</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:26</v>
+        <v>3:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Matt Hansen</v>
+        <v>CAIN</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-01</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:56</v>
+        <v>5:14</v>
       </c>
       <c r="H68" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-01</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:56</v>
+        <v>2:59</v>
       </c>
       <c r="H69" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-01</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:01</v>
+        <v>4:21</v>
       </c>
       <c r="H70" t="str">
-        <v>Tauren Wells</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:05</v>
+        <v>4:09</v>
       </c>
       <c r="H71" t="str">
-        <v>Maiah Manser</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:27</v>
+        <v>2:34</v>
       </c>
       <c r="H72" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:34</v>
+        <v>3:10</v>
       </c>
       <c r="H73" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-01</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:13</v>
+        <v>3:21</v>
       </c>
       <c r="H74" t="str">
-        <v>Ashley Kutcher</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:13</v>
+        <v>3:06</v>
       </c>
       <c r="H75" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-01</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:08</v>
+        <v>3:21</v>
       </c>
       <c r="H76" t="str">
-        <v>CAIN</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-01</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>5:14</v>
+        <v>7:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Harry Styles</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-01</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:59</v>
+        <v>3:17</v>
       </c>
       <c r="H78" t="str">
-        <v>Lana Lubany</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:21</v>
+        <v>3:45</v>
       </c>
       <c r="H79" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Tones And I</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:09</v>
+        <v>3:57</v>
       </c>
       <c r="H80" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-01</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:34</v>
+        <v>3:03</v>
       </c>
       <c r="H81" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-01</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:10</v>
+        <v>4:27</v>
       </c>
       <c r="H82" t="str">
-        <v>Olivia Dean</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-01</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:21</v>
+        <v>4:34</v>
       </c>
       <c r="H83" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Armik</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-01</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:06</v>
+        <v>2:54</v>
       </c>
       <c r="H84" t="str">
-        <v>The Avett Brothers</v>
+        <v>LØLØ</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-01</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:21</v>
+        <v>3:25</v>
       </c>
       <c r="H85" t="str">
-        <v>Jordana Bryant</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-01</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>7:21</v>
+        <v>2:01</v>
       </c>
       <c r="H86" t="str">
-        <v>Katy Perry</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B87" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-01</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:17</v>
+        <v>2:25</v>
       </c>
       <c r="H87" t="str">
-        <v>Lauren Watkins</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-01</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:45</v>
+        <v>1:14</v>
       </c>
       <c r="H88" t="str">
-        <v>Tones And I</v>
+        <v>Labrinth</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-01</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:57</v>
+        <v>2:59</v>
       </c>
       <c r="H89" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-01</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:03</v>
+        <v>2:29</v>
       </c>
       <c r="H90" t="str">
-        <v>Charlie Puth</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-01</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:27</v>
+        <v>2:34</v>
       </c>
       <c r="H91" t="str">
-        <v>Chappell Roan</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-01</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:34</v>
+        <v>3:48</v>
       </c>
       <c r="H92" t="str">
-        <v>Armik</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-01</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:54</v>
+        <v>3:32</v>
       </c>
       <c r="H93" t="str">
-        <v>LØLØ</v>
+        <v>The Beaches</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-01</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:25</v>
+        <v>3:49</v>
       </c>
       <c r="H94" t="str">
-        <v>Tenille Townes</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-01</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:01</v>
+        <v>4:28</v>
       </c>
       <c r="H95" t="str">
-        <v>Alan Walker</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-01</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:25</v>
+        <v>3:37</v>
       </c>
       <c r="H96" t="str">
-        <v>Charli xcx</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-01</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>1:14</v>
+        <v>3:35</v>
       </c>
       <c r="H97" t="str">
-        <v>Labrinth</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-01</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:59</v>
+        <v>2:31</v>
       </c>
       <c r="H98" t="str">
-        <v>Charlie Puth</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-01</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:29</v>
+        <v>3:21</v>
       </c>
       <c r="H99" t="str">
-        <v>Girl Tones</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-01</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:34</v>
+        <v>5:24</v>
       </c>
       <c r="H100" t="str">
-        <v>Jagwar Twin</v>
+        <v>Nickless</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-01</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:48</v>
+        <v>3:11</v>
       </c>
       <c r="H101" t="str">
-        <v>Caroline Jones</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Body</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>OCTANE</v>
       </c>
       <c r="G102" t="str">
-        <v>3:32</v>
+        <v>2:35</v>
       </c>
       <c r="H102" t="str">
-        <v>The Beaches</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/body/1871258329</v>
       </c>
       <c r="L102" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Body - Don Toliver</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Dandelion</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>Dandelion</v>
       </c>
       <c r="G103" t="str">
-        <v>3:49</v>
+        <v>4:00</v>
       </c>
       <c r="H103" t="str">
-        <v>Dolly Parton</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
       </c>
       <c r="L103" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Dandelion - Ella Langley</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>LIGHTS GO OUT</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>LIGHTS GO OUT - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>4:28</v>
+        <v>2:38</v>
       </c>
       <c r="H104" t="str">
-        <v>Madison Beer</v>
+        <v>John Summit</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
       </c>
       <c r="L104" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>LIGHTS GO OUT - John Summit</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>The Great Divide</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G105" t="str">
-        <v>3:37</v>
+        <v>5:17</v>
       </c>
       <c r="H105" t="str">
-        <v>Ty Myers</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
       </c>
       <c r="L105" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>The Great Divide - Noah Kahan</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>tristón</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>tristón - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:35</v>
+        <v>3:36</v>
       </c>
       <c r="H106" t="str">
-        <v>Megan Moroney</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
       </c>
       <c r="L106" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>tristón - Fuerza Regida</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Feed the Streets</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>Feed the Streets - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:31</v>
+        <v>2:58</v>
       </c>
       <c r="H107" t="str">
-        <v>Julia Cole Music</v>
+        <v>Rod Wave</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
       </c>
       <c r="L107" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Feed the Streets - Rod Wave</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>Distracted</v>
       </c>
       <c r="G108" t="str">
-        <v>3:21</v>
+        <v>2:30</v>
       </c>
       <c r="H108" t="str">
-        <v>Lily Allen</v>
+        <v>Thundercat</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L108" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>For Hire</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>5:24</v>
+        <v>3:44</v>
       </c>
       <c r="H109" t="str">
-        <v>Nickless</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L109" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>McArthur</v>
       </c>
       <c r="B110" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2 weeks ago</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:11</v>
+        <v>3:51</v>
       </c>
       <c r="H110" t="str">
-        <v>Peach PRC</v>
+        <v>HARDY</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L110" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Body</v>
+        <v>Debris</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/body/1871258331</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>OCTANE</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G111" t="str">
-        <v>2:35</v>
+        <v>2:55</v>
       </c>
       <c r="H111" t="str">
-        <v>Don Toliver</v>
+        <v>Labrinth</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/body/1871258329</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L111" t="str">
-        <v>Body - Don Toliver</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dandelion</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Dandelion</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G112" t="str">
-        <v>4:00</v>
+        <v>3:25</v>
       </c>
       <c r="H112" t="str">
-        <v>Ella Langley</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L112" t="str">
-        <v>Dandelion - Ella Langley</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>LIGHTS GO OUT</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>LIGHTS GO OUT - Single</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:38</v>
+        <v>4:38</v>
       </c>
       <c r="H113" t="str">
-        <v>John Summit</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L113" t="str">
-        <v>LIGHTS GO OUT - John Summit</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>The Great Divide</v>
+        <v>1+1</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Great Divide</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>5:17</v>
+        <v>3:06</v>
       </c>
       <c r="H114" t="str">
-        <v>Noah Kahan</v>
+        <v>Maluma</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L114" t="str">
-        <v>The Great Divide - Noah Kahan</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>tristón</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>tristón - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:36</v>
+        <v>3:08</v>
       </c>
       <c r="H115" t="str">
-        <v>Fuerza Regida</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L115" t="str">
-        <v>tristón - Fuerza Regida</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Feed the Streets</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Feed the Streets - Single</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:58</v>
+        <v>3:02</v>
       </c>
       <c r="H116" t="str">
-        <v>Rod Wave</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L116" t="str">
-        <v>Feed the Streets - Rod Wave</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>I Did This To Myself</v>
+        <v>fml .</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Distracted</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G117" t="str">
-        <v>2:30</v>
+        <v>2:40</v>
       </c>
       <c r="H117" t="str">
-        <v>Thundercat</v>
+        <v>fakemink</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L117" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>For Hire</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>For Hire - Single</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:44</v>
+        <v>3:01</v>
       </c>
       <c r="H118" t="str">
-        <v>People I’ve Met</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L118" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>McArthur</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>McArthur - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:51</v>
+        <v>3:08</v>
       </c>
       <c r="H119" t="str">
-        <v>HARDY</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L119" t="str">
-        <v>McArthur - HARDY</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Debris</v>
+        <v>Lorelei</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:55</v>
+        <v>2:35</v>
       </c>
       <c r="H120" t="str">
-        <v>Labrinth</v>
+        <v>ERNEST</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L120" t="str">
-        <v>Debris - Labrinth</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Free</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Free - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:25</v>
+        <v>3:56</v>
       </c>
       <c r="H121" t="str">
-        <v>Militarie Gun</v>
+        <v>SLANDER</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L121" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>4:38</v>
+        <v>2:55</v>
       </c>
       <c r="H122" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Artemas</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L122" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>1+1</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>1+1 - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G123" t="str">
-        <v>3:06</v>
+        <v>3:56</v>
       </c>
       <c r="H123" t="str">
-        <v>Maluma</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L123" t="str">
-        <v>1+1 - Maluma</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>Aguas</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:08</v>
+        <v>2:52</v>
       </c>
       <c r="H124" t="str">
-        <v>MJ Cole</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L124" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Two Car Garage</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:02</v>
+        <v>2:48</v>
       </c>
       <c r="H125" t="str">
-        <v>Jon Bellion</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L125" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>fml .</v>
+        <v>Baddie</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Bohemio</v>
       </c>
       <c r="G126" t="str">
-        <v>2:40</v>
+        <v>3:11</v>
       </c>
       <c r="H126" t="str">
-        <v>fakemink</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L126" t="str">
-        <v>fml . - fakemink</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Faked It All The Time</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:01</v>
+        <v>3:51</v>
       </c>
       <c r="H127" t="str">
-        <v>Allie Sherlock</v>
+        <v>Tems</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L127" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>House of the Rising Sun</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:08</v>
+        <v>3:16</v>
       </c>
       <c r="H128" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Fred again..</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L128" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Lorelei</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Lorelei - Single</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:35</v>
+        <v>3:50</v>
       </c>
       <c r="H129" t="str">
-        <v>ERNEST</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L129" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Free</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Free - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G130" t="str">
-        <v>3:56</v>
+        <v>3:33</v>
       </c>
       <c r="H130" t="str">
-        <v>SLANDER</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L130" t="str">
-        <v>Free - SLANDER</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>professional heartbreaker</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:55</v>
+        <v>3:17</v>
       </c>
       <c r="H131" t="str">
-        <v>Artemas</v>
+        <v>Kneecap</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L131" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>tell me what you want</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>ACT II</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:56</v>
+        <v>4:38</v>
       </c>
       <c r="H132" t="str">
-        <v>Sasha Keable</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L132" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Aguas</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Aguas - Single</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:52</v>
+        <v>3:49</v>
       </c>
       <c r="H133" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L133" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Ants In My Room</v>
+        <v>HIGH</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G134" t="str">
-        <v>2:48</v>
+        <v>3:23</v>
       </c>
       <c r="H134" t="str">
-        <v>Carter Vail</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L134" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Baddie</v>
+        <v>Villain</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Bohemio</v>
+        <v>Reflections</v>
       </c>
       <c r="G135" t="str">
-        <v>3:11</v>
+        <v>3:53</v>
       </c>
       <c r="H135" t="str">
-        <v>Nicky Jam</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L135" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G136" t="str">
-        <v>3:51</v>
+        <v>3:00</v>
       </c>
       <c r="H136" t="str">
-        <v>Tems</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L136" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>Residue</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G137" t="str">
-        <v>3:16</v>
+        <v>3:28</v>
       </c>
       <c r="H137" t="str">
-        <v>Fred again..</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L137" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G138" t="str">
-        <v>3:50</v>
+        <v>2:12</v>
       </c>
       <c r="H138" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L138" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>For The First Time, Again</v>
+        <v>Starlight</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>For The First Time, Again</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G139" t="str">
-        <v>3:33</v>
+        <v>3:21</v>
       </c>
       <c r="H139" t="str">
-        <v>Tyler Ballgame</v>
+        <v>Cannons</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L139" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Liars Tale</v>
+        <v>Dandelion</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Liars Tale - Single</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G140" t="str">
-        <v>3:17</v>
+        <v>3:14</v>
       </c>
       <c r="H140" t="str">
-        <v>Kneecap</v>
+        <v>Dogpark</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L140" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G141" t="str">
-        <v>4:38</v>
+        <v>2:46</v>
       </c>
       <c r="H141" t="str">
-        <v>Motionless In White</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L141" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Wake Up Calling</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G142" t="str">
-        <v>3:49</v>
+        <v>2:24</v>
       </c>
       <c r="H142" t="str">
-        <v>Papa Roach</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L142" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>HIGH</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Da Realest</v>
       </c>
       <c r="G143" t="str">
-        <v>3:23</v>
+        <v>1:59</v>
       </c>
       <c r="H143" t="str">
-        <v>Magnolia Park</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L143" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Villain</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Reflections</v>
+        <v>Xavier</v>
       </c>
       <c r="G144" t="str">
-        <v>3:53</v>
+        <v>3:05</v>
       </c>
       <c r="H144" t="str">
-        <v>From Ashes to New</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L144" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:00</v>
+        <v>3:02</v>
       </c>
       <c r="H145" t="str">
-        <v>Caleb Chan</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L145" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Residue</v>
+        <v>Prettier</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:28</v>
+        <v>2:34</v>
       </c>
       <c r="H146" t="str">
-        <v>A. G. Cook</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L146" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:12</v>
+        <v>3:21</v>
       </c>
       <c r="H147" t="str">
-        <v>Joyce Manor</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L147" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Starlight</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Everything Glows</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:21</v>
+        <v>3:20</v>
       </c>
       <c r="H148" t="str">
-        <v>Cannons</v>
+        <v>The Maine</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L148" t="str">
-        <v>Starlight - Cannons</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Dandelion</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:14</v>
+        <v>2:58</v>
       </c>
       <c r="H149" t="str">
-        <v>Dogpark</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L149" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>THEMSELVES</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>BACKWARD</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G150" t="str">
-        <v>2:46</v>
+        <v>2:14</v>
       </c>
       <c r="H150" t="str">
-        <v>Jordan Ward</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L150" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>High Maintenance</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Miracle Mile</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:24</v>
+        <v>2:50</v>
       </c>
       <c r="H151" t="str">
-        <v>Paul Russell</v>
+        <v>i-dle</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L151" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Trackhawk</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Da Realest</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G152" t="str">
-        <v>1:59</v>
+        <v>1:55</v>
       </c>
       <c r="H152" t="str">
-        <v>Babyfxce E</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L152" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Wheel Man</v>
+        <v>RIDIN</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Xavier</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:05</v>
+        <v>2:00</v>
       </c>
       <c r="H153" t="str">
-        <v>xaviersobased</v>
+        <v>Tokischa</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L153" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Natural Disaster</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:02</v>
+        <v>3:07</v>
       </c>
       <c r="H154" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L154" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Prettier</v>
+        <v>Poema</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Prettier - Single</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:34</v>
+        <v>3:14</v>
       </c>
       <c r="H155" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L155" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Live Without</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:21</v>
+        <v>2:55</v>
       </c>
       <c r="H156" t="str">
-        <v>NLE Choppa</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L156" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Die To Fall</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Die To Fall - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:20</v>
+        <v>3:55</v>
       </c>
       <c r="H157" t="str">
-        <v>The Maine</v>
+        <v>Blessd</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L157" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:58</v>
+        <v>3:29</v>
       </c>
       <c r="H158" t="str">
-        <v>Steve Aoki</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L158" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Slow Burn</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Still There’s a Glow</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:14</v>
+        <v>2:45</v>
       </c>
       <c r="H159" t="str">
-        <v>Sweet Pill</v>
+        <v>VEDO</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L159" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Too Late</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/too-late/1866685876</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Too Late - EP</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:56</v>
+        <v>3:32</v>
       </c>
       <c r="H160" t="str">
-        <v>Hunter Hayes</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/too-late/1866685875</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L160" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G161" t="str">
-        <v>2:50</v>
+        <v>3:20</v>
       </c>
       <c r="H161" t="str">
-        <v>i-dle</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L161" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Thank You Is Enough</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>1:55</v>
+        <v>2:48</v>
       </c>
       <c r="H162" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>Mýa</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L162" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>RIDIN</v>
+        <v>Once I Say</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>RIDIN - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G163" t="str">
-        <v>2:00</v>
+        <v>3:21</v>
       </c>
       <c r="H163" t="str">
-        <v>Tokischa</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L163" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>POSSESSION</v>
+        <v>believer</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>POSSESSION - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:07</v>
+        <v>2:57</v>
       </c>
       <c r="H164" t="str">
-        <v>Melanie Martinez</v>
+        <v>Yuna</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L164" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Poema</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Poema - Single</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:14</v>
+        <v>3:51</v>
       </c>
       <c r="H165" t="str">
-        <v>Óscar Maydon</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L165" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Live Without</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G166" t="str">
-        <v>2:55</v>
+        <v>3:13</v>
       </c>
       <c r="H166" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L166" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>FANÁTICO</v>
+        <v>Daysa</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:55</v>
+        <v>4:36</v>
       </c>
       <c r="H167" t="str">
-        <v>Blessd</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L167" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Frozen Lake</v>
+        <v>Fabulous</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:29</v>
+        <v>2:33</v>
       </c>
       <c r="H168" t="str">
-        <v>VOILÀ</v>
+        <v>MEEK</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L168" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:45</v>
+        <v>3:22</v>
       </c>
       <c r="H169" t="str">
-        <v>VEDO</v>
+        <v>RUBIO</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L169" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>brainchem</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:32</v>
+        <v>2:28</v>
       </c>
       <c r="H170" t="str">
-        <v>Chris Lorenzo</v>
+        <v>EMJAY</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L170" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>It’s Like That</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>A Pound of Feathers</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G171" t="str">
-        <v>3:20</v>
+        <v>2:48</v>
       </c>
       <c r="H171" t="str">
-        <v>The Black Crowes</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L171" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>A.S.A.P.</v>
+        <v>Giants</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:48</v>
+        <v>3:12</v>
       </c>
       <c r="H172" t="str">
-        <v>Mýa</v>
+        <v>Picture This</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L172" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Once I Say</v>
+        <v>Scooby</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>PASSION</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:21</v>
+        <v>3:41</v>
       </c>
       <c r="H173" t="str">
-        <v>Terrace Martin</v>
+        <v>corook</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L173" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>believer</v>
+        <v>La Racha</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>believer - Single</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:57</v>
+        <v>2:48</v>
       </c>
       <c r="H174" t="str">
-        <v>Yuna</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L174" t="str">
-        <v>believer - Yuna</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>I Envy The Wind</v>
+        <v>So Am I</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G175" t="str">
-        <v>3:51</v>
+        <v>2:50</v>
       </c>
       <c r="H175" t="str">
-        <v>Molly Parden</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L175" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>The Alchemist</v>
+        <v>best thing</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>The Alchemist</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:13</v>
+        <v>4:27</v>
       </c>
       <c r="H176" t="str">
-        <v>Bre Kennedy</v>
+        <v>WRABEL</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L176" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Daysa</v>
+        <v>Count It Back</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Daysa - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G177" t="str">
-        <v>4:36</v>
+        <v>2:52</v>
       </c>
       <c r="H177" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L177" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Fabulous</v>
+        <v>Good Girl</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Fabulous - Single</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:33</v>
+        <v>4:23</v>
       </c>
       <c r="H178" t="str">
-        <v>MEEK</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L178" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G179" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H179" t="str">
-        <v>RUBIO</v>
+        <v>MORGXN</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L179" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>brainchem</v>
+        <v>Run My Way</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>brainchem - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:28</v>
+        <v>2:44</v>
       </c>
       <c r="H180" t="str">
-        <v>EMJAY</v>
+        <v>December 10</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L180" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>Cold Night</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>With No Due Respect</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:48</v>
+        <v>3:12</v>
       </c>
       <c r="H181" t="str">
-        <v>Foggieraw</v>
+        <v>HANA</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L181" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Giants</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Giants - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:12</v>
+        <v>2:28</v>
       </c>
       <c r="H182" t="str">
-        <v>Picture This</v>
+        <v>LUNA</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L182" t="str">
-        <v>Giants - Picture This</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Scooby</v>
+        <v>Fragile</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Scooby - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:41</v>
+        <v>3:10</v>
       </c>
       <c r="H183" t="str">
-        <v>corook</v>
+        <v>Anajah</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L183" t="str">
-        <v>Scooby - corook</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>La Racha</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>La Racha - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:48</v>
+        <v>2:04</v>
       </c>
       <c r="H184" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L184" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>So Am I</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:50</v>
+        <v>3:04</v>
       </c>
       <c r="H185" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L185" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>best thing</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>best thing - Single</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:27</v>
+        <v>3:41</v>
       </c>
       <c r="H186" t="str">
-        <v>WRABEL</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L186" t="str">
-        <v>best thing - WRABEL</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Count It Back</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Magic Boy</v>
+        <v>ONE</v>
       </c>
       <c r="G187" t="str">
-        <v>2:52</v>
+        <v>3:46</v>
       </c>
       <c r="H187" t="str">
-        <v>Bartees Strange</v>
+        <v>Sevendust</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L187" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Good Girl</v>
+        <v>Hud</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Good Girl - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G188" t="str">
-        <v>4:23</v>
+        <v>4:46</v>
       </c>
       <c r="H188" t="str">
-        <v>Paris Paloma</v>
+        <v>MØL</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L188" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>MY REVIVAL</v>
+        <v>Ego Death</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:34</v>
+        <v>2:12</v>
       </c>
       <c r="H189" t="str">
-        <v>MORGXN</v>
+        <v>Atreyu</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L189" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Run My Way</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Run My Way - Single</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:44</v>
+        <v>4:05</v>
       </c>
       <c r="H190" t="str">
-        <v>December 10</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L190" t="str">
-        <v>Run My Way - December 10</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Cold Night</v>
+        <v>Disappear</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Cold Night - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G191" t="str">
-        <v>3:12</v>
+        <v>5:50</v>
       </c>
       <c r="H191" t="str">
-        <v>HANA</v>
+        <v>Lane 8</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L191" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Away With The Fairies</v>
+        <v>Misbehave</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:28</v>
+        <v>3:43</v>
       </c>
       <c r="H192" t="str">
-        <v>LUNA</v>
+        <v>Aluna</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L192" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Fragile</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Fragile - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:10</v>
+        <v>2:47</v>
       </c>
       <c r="H193" t="str">
-        <v>Anajah</v>
+        <v>Alok</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L193" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Slow Dancin'</v>
+        <v>Fly</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:04</v>
+        <v>3:04</v>
       </c>
       <c r="H194" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L194" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>ily anyway</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:04</v>
+        <v>3:05</v>
       </c>
       <c r="H195" t="str">
-        <v>Lily Meola</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L195" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>More Of What Matters</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G196" t="str">
-        <v>3:41</v>
+        <v>3:35</v>
       </c>
       <c r="H196" t="str">
-        <v>Jamey Johnson</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L196" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Is This The Real You</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>ONE</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G197" t="str">
-        <v>3:46</v>
+        <v>3:41</v>
       </c>
       <c r="H197" t="str">
-        <v>Sevendust</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L197" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Hud</v>
+        <v>praxis</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>DREAMCRUSH</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G198" t="str">
-        <v>4:46</v>
+        <v>3:28</v>
       </c>
       <c r="H198" t="str">
-        <v>MØL</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L198" t="str">
-        <v>Hud - MØL</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Ego Death</v>
+        <v>House</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Ego Death - Single</v>
+        <v>House - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:12</v>
+        <v>2:30</v>
       </c>
       <c r="H199" t="str">
-        <v>Atreyu</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L199" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G200" t="str">
-        <v>4:05</v>
+        <v>3:57</v>
       </c>
       <c r="H200" t="str">
-        <v>EJ Jones</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L200" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Disappear</v>
+        <v>Brincar</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Disappear</v>
+        <v>JET LAG - EP</v>
       </c>
       <c r="G201" t="str">
-        <v>5:50</v>
+        <v>3:06</v>
       </c>
       <c r="H201" t="str">
-        <v>Lane 8</v>
+        <v>J Castle</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
       </c>
       <c r="L201" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Brincar - J Castle</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Misbehave</v>
+        <v>Quién</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
       <c r="D202" t="str">
         <v>2026-02-01</v>
@@ -8051,410 +8051,30 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Misbehave - Single</v>
+        <v>Quién - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:43</v>
+        <v>4:19</v>
       </c>
       <c r="H202" t="str">
-        <v>Aluna</v>
+        <v>Daniela Darcourt</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
       <c r="L202" t="str">
-        <v>Misbehave - Aluna</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Club Bizarre</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Club Bizarre - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>2:47</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Alok</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Club Bizarre - Alok</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Fly</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Fly - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:04</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Stephen Stanley</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Fly - Stephen Stanley</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>ily anyway</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>ily anyway - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:05</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Strings &amp; Heart</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
-      </c>
-      <c r="L205" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>Nellene - EP</v>
-      </c>
-      <c r="G206" t="str">
-        <v>3:35</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Deloyd Elze</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
-      </c>
-      <c r="L206" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Kiss Big</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Kiss Big</v>
-      </c>
-      <c r="G207" t="str">
-        <v>3:41</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Ailbhe Reddy</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>praxis</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Whole World As Vigil</v>
-      </c>
-      <c r="G208" t="str">
-        <v>3:28</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Lauren Auder</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
-      </c>
-      <c r="L208" t="str">
-        <v>praxis - Lauren Auder</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>House</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>House - Single</v>
-      </c>
-      <c r="G209" t="str">
-        <v>2:30</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Connie Converse</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
-      </c>
-      <c r="L209" t="str">
-        <v>House - Connie Converse</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Cowboy Without a Clue</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>No Love Lost to Kindness</v>
-      </c>
-      <c r="G210" t="str">
-        <v>3:57</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Yumi Zouma</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
-      </c>
-      <c r="L210" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Brincar</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>JET LAG - EP</v>
-      </c>
-      <c r="G211" t="str">
-        <v>3:06</v>
-      </c>
-      <c r="H211" t="str">
-        <v>J Castle</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
-      </c>
-      <c r="L211" t="str">
-        <v>Brincar - J Castle</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Quién</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>Quién - Single</v>
-      </c>
-      <c r="G212" t="str">
-        <v>4:19</v>
-      </c>
-      <c r="H212" t="str">
-        <v>Daniela Darcourt</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
-      </c>
-      <c r="L212" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L212"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409444&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>4:58</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>The Warning</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
+        <v>פרחי ירושלים - סומלילנד</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409443&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>5:08</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>The Offspring</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
+        <v>פרחי ירושלים - סומלילנד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>מתנאל סבח - שדרות דוממת</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409442&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-01</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>4:38</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Roxette</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>מתנאל סבח - שדרות דוממת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409441&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-01</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:50</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Jessie Ware</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>אורי זר - חוזר לילדות</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-01</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409440&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-01</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3:10</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>אורי זר - חוזר לילדות</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-01</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:44</v>
+        <v>4:58</v>
       </c>
       <c r="H7" t="str">
-        <v>Dean Lewis</v>
+        <v>The Warning</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:57</v>
+        <v>5:08</v>
       </c>
       <c r="H8" t="str">
-        <v>Take That</v>
+        <v>The Offspring</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-01</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:39</v>
+        <v>4:38</v>
       </c>
       <c r="H9" t="str">
-        <v>The Cure</v>
+        <v>Roxette</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-01</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:07</v>
+        <v>3:50</v>
       </c>
       <c r="H10" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-01</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:47</v>
+        <v>3:10</v>
       </c>
       <c r="H11" t="str">
-        <v>Paris Paloma</v>
+        <v>Joseph</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-01</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:22</v>
+        <v>2:44</v>
       </c>
       <c r="H12" t="str">
-        <v>Zara Larsson</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-01</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:48</v>
+        <v>2:57</v>
       </c>
       <c r="H13" t="str">
-        <v>only the poets</v>
+        <v>Take That</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-01</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:52</v>
+        <v>2:39</v>
       </c>
       <c r="H14" t="str">
-        <v>Katelyn Tarver</v>
+        <v>The Cure</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-01</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:33</v>
+        <v>3:07</v>
       </c>
       <c r="H15" t="str">
-        <v>David Guetta</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-01</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:41</v>
+        <v>4:47</v>
       </c>
       <c r="H16" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-01</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:01</v>
+        <v>3:22</v>
       </c>
       <c r="H17" t="str">
-        <v>Ella Langley</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-01</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>2:48</v>
       </c>
       <c r="H18" t="str">
-        <v>Dogpark</v>
+        <v>only the poets</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-01</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:03</v>
+        <v>2:52</v>
       </c>
       <c r="H19" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-01</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:41</v>
+        <v>3:33</v>
       </c>
       <c r="H20" t="str">
-        <v>ERNEST</v>
+        <v>David Guetta</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:05</v>
+        <v>2:41</v>
       </c>
       <c r="H21" t="str">
-        <v>Labrinth</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:46</v>
+        <v>4:01</v>
       </c>
       <c r="H22" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:32</v>
+        <v>3:16</v>
       </c>
       <c r="H23" t="str">
-        <v>VOILÀ</v>
+        <v>Dogpark</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:42</v>
+        <v>3:03</v>
       </c>
       <c r="H24" t="str">
-        <v>Cannons</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:38</v>
+        <v>2:41</v>
       </c>
       <c r="H25" t="str">
-        <v>Kylie Morgan</v>
+        <v>ERNEST</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:10</v>
+        <v>3:05</v>
       </c>
       <c r="H26" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Labrinth</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:57</v>
+        <v>2:46</v>
       </c>
       <c r="H27" t="str">
-        <v>Willie Nelson</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:19</v>
+        <v>3:32</v>
       </c>
       <c r="H28" t="str">
-        <v>JeremyCampMusic</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:04</v>
+        <v>3:42</v>
       </c>
       <c r="H29" t="str">
-        <v>India Martínez</v>
+        <v>Cannons</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:16</v>
+        <v>2:38</v>
       </c>
       <c r="H30" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:58</v>
+        <v>3:10</v>
       </c>
       <c r="H31" t="str">
-        <v>TINI</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:26</v>
+        <v>3:57</v>
       </c>
       <c r="H32" t="str">
-        <v>Charley</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-01</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:05</v>
+        <v>2:19</v>
       </c>
       <c r="H33" t="str">
-        <v>Demi Lovato</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-01</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:16</v>
+        <v>4:04</v>
       </c>
       <c r="H34" t="str">
-        <v>Teddy Swims</v>
+        <v>India Martínez</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-01</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:14</v>
+        <v>2:16</v>
       </c>
       <c r="H35" t="str">
-        <v>Beck</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:57</v>
+        <v>5:58</v>
       </c>
       <c r="H36" t="str">
-        <v>The Offspring</v>
+        <v>TINI</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-01</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:10</v>
+        <v>3:26</v>
       </c>
       <c r="H37" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Charley</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-01</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:10</v>
+        <v>4:05</v>
       </c>
       <c r="H38" t="str">
-        <v>Jason Derulo</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:52</v>
+        <v>3:16</v>
       </c>
       <c r="H39" t="str">
-        <v>lights</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:50</v>
+        <v>3:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Telenova</v>
+        <v>Beck</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>I Explained "How Music Works" LIVE At My Concert</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-01</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:32</v>
+        <v>2:57</v>
       </c>
       <c r="H41" t="str">
-        <v>Marcin</v>
+        <v>The Offspring</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>I Explained "How Music Works" LIVE At My Concert - Marcin</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-01</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:27</v>
+        <v>4:10</v>
       </c>
       <c r="H42" t="str">
-        <v>We Three</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:01</v>
+        <v>2:10</v>
       </c>
       <c r="H43" t="str">
-        <v>Timebelle Official</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:20</v>
+        <v>3:52</v>
       </c>
       <c r="H44" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>lights</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:34</v>
+        <v>3:50</v>
       </c>
       <c r="H45" t="str">
-        <v>Clinton Kane</v>
+        <v>Telenova</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>I Explained "How Music Works" LIVE At My Concert</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:01</v>
+        <v>5:32</v>
       </c>
       <c r="H46" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Marcin</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>I Explained "How Music Works" LIVE At My Concert - Marcin</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:24</v>
+        <v>4:27</v>
       </c>
       <c r="H47" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>We Three</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>5:52</v>
+        <v>3:01</v>
       </c>
       <c r="H48" t="str">
-        <v>Harry Styles</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:01</v>
+        <v>3:20</v>
       </c>
       <c r="H49" t="str">
-        <v>Neal Francis</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:12</v>
+        <v>3:34</v>
       </c>
       <c r="H50" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-01</v>
@@ -2316,10 +2316,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:59</v>
+        <v>4:01</v>
       </c>
       <c r="H51" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B52" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-01</v>
@@ -2354,10 +2354,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:56</v>
+        <v>3:24</v>
       </c>
       <c r="H52" t="str">
-        <v>Cliff Richard</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B53" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-01</v>
@@ -2392,10 +2392,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:46</v>
+        <v>5:52</v>
       </c>
       <c r="H53" t="str">
-        <v>Jessie Ware</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B54" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-01</v>
@@ -2430,10 +2430,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:37</v>
+        <v>5:01</v>
       </c>
       <c r="H54" t="str">
-        <v>Bella White</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-01</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:06</v>
+        <v>4:12</v>
       </c>
       <c r="H55" t="str">
-        <v>Ryan Wright</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-01</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:54</v>
+        <v>3:59</v>
       </c>
       <c r="H56" t="str">
-        <v>Dove Cameron</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-01</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:10</v>
+        <v>2:56</v>
       </c>
       <c r="H57" t="str">
-        <v>Parker McCollum</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-01</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:26</v>
+        <v>3:46</v>
       </c>
       <c r="H58" t="str">
-        <v>Matt Hansen</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:56</v>
+        <v>4:37</v>
       </c>
       <c r="H59" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Bella White</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-01</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:56</v>
+        <v>4:06</v>
       </c>
       <c r="H60" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-01</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:01</v>
+        <v>3:54</v>
       </c>
       <c r="H61" t="str">
-        <v>Tauren Wells</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-01</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:05</v>
+        <v>4:10</v>
       </c>
       <c r="H62" t="str">
-        <v>Maiah Manser</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-01</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>3:26</v>
       </c>
       <c r="H63" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-01</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:34</v>
+        <v>2:56</v>
       </c>
       <c r="H64" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-01</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H65" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-01</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:13</v>
+        <v>4:01</v>
       </c>
       <c r="H66" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-01</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:08</v>
+        <v>3:05</v>
       </c>
       <c r="H67" t="str">
-        <v>CAIN</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-01</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:14</v>
+        <v>2:27</v>
       </c>
       <c r="H68" t="str">
-        <v>Harry Styles</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-01</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:59</v>
+        <v>2:34</v>
       </c>
       <c r="H69" t="str">
-        <v>Lana Lubany</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-01</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:21</v>
+        <v>3:13</v>
       </c>
       <c r="H70" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:09</v>
+        <v>3:13</v>
       </c>
       <c r="H71" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:34</v>
+        <v>3:08</v>
       </c>
       <c r="H72" t="str">
-        <v>Lauren Sanderson</v>
+        <v>CAIN</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:10</v>
+        <v>5:14</v>
       </c>
       <c r="H73" t="str">
-        <v>Olivia Dean</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-01</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:21</v>
+        <v>2:59</v>
       </c>
       <c r="H74" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:06</v>
+        <v>4:21</v>
       </c>
       <c r="H75" t="str">
-        <v>The Avett Brothers</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-01</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:21</v>
+        <v>4:09</v>
       </c>
       <c r="H76" t="str">
-        <v>Jordana Bryant</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-01</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>7:21</v>
+        <v>2:34</v>
       </c>
       <c r="H77" t="str">
-        <v>Katy Perry</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-01</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:17</v>
+        <v>3:10</v>
       </c>
       <c r="H78" t="str">
-        <v>Lauren Watkins</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:45</v>
+        <v>3:21</v>
       </c>
       <c r="H79" t="str">
-        <v>Tones And I</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:57</v>
+        <v>3:06</v>
       </c>
       <c r="H80" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-01</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H81" t="str">
-        <v>Charlie Puth</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-01</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:27</v>
+        <v>7:21</v>
       </c>
       <c r="H82" t="str">
-        <v>Chappell Roan</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-01</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:34</v>
+        <v>3:17</v>
       </c>
       <c r="H83" t="str">
-        <v>Armik</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-01</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:54</v>
+        <v>3:45</v>
       </c>
       <c r="H84" t="str">
-        <v>LØLØ</v>
+        <v>Tones And I</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-01</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:25</v>
+        <v>3:57</v>
       </c>
       <c r="H85" t="str">
-        <v>Tenille Townes</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-01</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:01</v>
+        <v>3:03</v>
       </c>
       <c r="H86" t="str">
-        <v>Alan Walker</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-01</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:25</v>
+        <v>4:27</v>
       </c>
       <c r="H87" t="str">
-        <v>Charli xcx</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-01</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>1:14</v>
+        <v>4:34</v>
       </c>
       <c r="H88" t="str">
-        <v>Labrinth</v>
+        <v>Armik</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-01</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:59</v>
+        <v>2:54</v>
       </c>
       <c r="H89" t="str">
-        <v>Charlie Puth</v>
+        <v>LØLØ</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-01</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:29</v>
+        <v>3:25</v>
       </c>
       <c r="H90" t="str">
-        <v>Girl Tones</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-01</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:34</v>
+        <v>2:01</v>
       </c>
       <c r="H91" t="str">
-        <v>Jagwar Twin</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-01</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:48</v>
+        <v>2:25</v>
       </c>
       <c r="H92" t="str">
-        <v>Caroline Jones</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-01</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:32</v>
+        <v>1:14</v>
       </c>
       <c r="H93" t="str">
-        <v>The Beaches</v>
+        <v>Labrinth</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-01</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:49</v>
+        <v>2:59</v>
       </c>
       <c r="H94" t="str">
-        <v>Dolly Parton</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-01</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:28</v>
+        <v>2:29</v>
       </c>
       <c r="H95" t="str">
-        <v>Madison Beer</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-01</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:37</v>
+        <v>2:34</v>
       </c>
       <c r="H96" t="str">
-        <v>Ty Myers</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-01</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:35</v>
+        <v>3:48</v>
       </c>
       <c r="H97" t="str">
-        <v>Megan Moroney</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-01</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:31</v>
+        <v>3:32</v>
       </c>
       <c r="H98" t="str">
-        <v>Julia Cole Music</v>
+        <v>The Beaches</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-01</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:21</v>
+        <v>3:49</v>
       </c>
       <c r="H99" t="str">
-        <v>Lily Allen</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-01</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:24</v>
+        <v>4:28</v>
       </c>
       <c r="H100" t="str">
-        <v>Nickless</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-01</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:11</v>
+        <v>3:37</v>
       </c>
       <c r="H101" t="str">
-        <v>Peach PRC</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Body</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/body/1871258331</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>OCTANE</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:35</v>
+        <v>3:35</v>
       </c>
       <c r="H102" t="str">
-        <v>Don Toliver</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/body/1871258329</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Body - Don Toliver</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dandelion</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Dandelion</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>4:00</v>
+        <v>2:31</v>
       </c>
       <c r="H103" t="str">
-        <v>Ella Langley</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Dandelion - Ella Langley</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>LIGHTS GO OUT</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>LIGHTS GO OUT - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>2:38</v>
+        <v>3:21</v>
       </c>
       <c r="H104" t="str">
-        <v>John Summit</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>LIGHTS GO OUT - John Summit</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Great Divide</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Great Divide</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>5:17</v>
+        <v>5:24</v>
       </c>
       <c r="H105" t="str">
-        <v>Noah Kahan</v>
+        <v>Nickless</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>The Great Divide - Noah Kahan</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>tristón</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>tristón - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:36</v>
+        <v>3:11</v>
       </c>
       <c r="H106" t="str">
-        <v>Fuerza Regida</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>tristón - Fuerza Regida</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Feed the Streets</v>
+        <v>Body</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
+        <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Feed the Streets - Single</v>
+        <v>OCTANE</v>
       </c>
       <c r="G107" t="str">
-        <v>2:58</v>
+        <v>2:35</v>
       </c>
       <c r="H107" t="str">
-        <v>Rod Wave</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
+        <v>https://music.apple.com/us/album/body/1871258329</v>
       </c>
       <c r="L107" t="str">
-        <v>Feed the Streets - Rod Wave</v>
+        <v>Body - Don Toliver</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Did This To Myself</v>
+        <v>Dandelion</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Distracted</v>
+        <v>Dandelion</v>
       </c>
       <c r="G108" t="str">
-        <v>2:30</v>
+        <v>4:00</v>
       </c>
       <c r="H108" t="str">
-        <v>Thundercat</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
       </c>
       <c r="L108" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>Dandelion - Ella Langley</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>For Hire</v>
+        <v>LIGHTS GO OUT</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>For Hire - Single</v>
+        <v>LIGHTS GO OUT - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:44</v>
+        <v>2:38</v>
       </c>
       <c r="H109" t="str">
-        <v>People I’ve Met</v>
+        <v>John Summit</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
       </c>
       <c r="L109" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>LIGHTS GO OUT - John Summit</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>McArthur</v>
+        <v>The Great Divide</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>McArthur - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G110" t="str">
-        <v>3:51</v>
+        <v>5:17</v>
       </c>
       <c r="H110" t="str">
-        <v>HARDY</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
       </c>
       <c r="L110" t="str">
-        <v>McArthur - HARDY</v>
+        <v>The Great Divide - Noah Kahan</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Debris</v>
+        <v>tristón</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>tristón - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:55</v>
+        <v>3:36</v>
       </c>
       <c r="H111" t="str">
-        <v>Labrinth</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
       </c>
       <c r="L111" t="str">
-        <v>Debris - Labrinth</v>
+        <v>tristón - Fuerza Regida</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Feed the Streets</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Feed the Streets - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:25</v>
+        <v>2:58</v>
       </c>
       <c r="H112" t="str">
-        <v>Militarie Gun</v>
+        <v>Rod Wave</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
       </c>
       <c r="L112" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>Feed the Streets - Rod Wave</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G113" t="str">
-        <v>4:38</v>
+        <v>2:30</v>
       </c>
       <c r="H113" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Thundercat</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>1+1</v>
+        <v>For Hire</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>1+1 - Single</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:06</v>
+        <v>3:44</v>
       </c>
       <c r="H114" t="str">
-        <v>Maluma</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L114" t="str">
-        <v>1+1 - Maluma</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>McArthur</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:08</v>
+        <v>3:51</v>
       </c>
       <c r="H115" t="str">
-        <v>MJ Cole</v>
+        <v>HARDY</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L115" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Two Car Garage</v>
+        <v>Debris</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G116" t="str">
-        <v>3:02</v>
+        <v>2:55</v>
       </c>
       <c r="H116" t="str">
-        <v>Jon Bellion</v>
+        <v>Labrinth</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L116" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>fml .</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G117" t="str">
-        <v>2:40</v>
+        <v>3:25</v>
       </c>
       <c r="H117" t="str">
-        <v>fakemink</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L117" t="str">
-        <v>fml . - fakemink</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Faked It All The Time</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:01</v>
+        <v>4:38</v>
       </c>
       <c r="H118" t="str">
-        <v>Allie Sherlock</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L118" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>House of the Rising Sun</v>
+        <v>1+1</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:08</v>
+        <v>3:06</v>
       </c>
       <c r="H119" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Maluma</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L119" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Lorelei</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Lorelei - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:35</v>
+        <v>3:08</v>
       </c>
       <c r="H120" t="str">
-        <v>ERNEST</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L120" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Free</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Free - Single</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:56</v>
+        <v>3:02</v>
       </c>
       <c r="H121" t="str">
-        <v>SLANDER</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L121" t="str">
-        <v>Free - SLANDER</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>professional heartbreaker</v>
+        <v>fml .</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G122" t="str">
-        <v>2:55</v>
+        <v>2:40</v>
       </c>
       <c r="H122" t="str">
-        <v>Artemas</v>
+        <v>fakemink</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L122" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>tell me what you want</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ACT II</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:56</v>
+        <v>3:01</v>
       </c>
       <c r="H123" t="str">
-        <v>Sasha Keable</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L123" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Aguas</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Aguas - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:52</v>
+        <v>3:08</v>
       </c>
       <c r="H124" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L124" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Ants In My Room</v>
+        <v>Lorelei</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:48</v>
+        <v>2:35</v>
       </c>
       <c r="H125" t="str">
-        <v>Carter Vail</v>
+        <v>ERNEST</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L125" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Baddie</v>
+        <v>Free</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Bohemio</v>
+        <v>Free - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:11</v>
+        <v>3:56</v>
       </c>
       <c r="H126" t="str">
-        <v>Nicky Jam</v>
+        <v>SLANDER</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L126" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H127" t="str">
-        <v>Tems</v>
+        <v>Artemas</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L127" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G128" t="str">
-        <v>3:16</v>
+        <v>3:56</v>
       </c>
       <c r="H128" t="str">
-        <v>Fred again..</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L128" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>Aguas</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:50</v>
+        <v>2:52</v>
       </c>
       <c r="H129" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:33</v>
+        <v>2:48</v>
       </c>
       <c r="H130" t="str">
-        <v>Tyler Ballgame</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L130" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Liars Tale</v>
+        <v>Baddie</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Liars Tale - Single</v>
+        <v>Bohemio</v>
       </c>
       <c r="G131" t="str">
-        <v>3:17</v>
+        <v>3:11</v>
       </c>
       <c r="H131" t="str">
-        <v>Kneecap</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L131" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:38</v>
+        <v>3:51</v>
       </c>
       <c r="H132" t="str">
-        <v>Motionless In White</v>
+        <v>Tems</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L132" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Wake Up Calling</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:49</v>
+        <v>3:16</v>
       </c>
       <c r="H133" t="str">
-        <v>Papa Roach</v>
+        <v>Fred again..</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L133" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>HIGH</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:23</v>
+        <v>3:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Magnolia Park</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L134" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Villain</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Reflections</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G135" t="str">
-        <v>3:53</v>
+        <v>3:33</v>
       </c>
       <c r="H135" t="str">
-        <v>From Ashes to New</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L135" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:00</v>
+        <v>3:17</v>
       </c>
       <c r="H136" t="str">
-        <v>Caleb Chan</v>
+        <v>Kneecap</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L136" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Residue</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:28</v>
+        <v>4:38</v>
       </c>
       <c r="H137" t="str">
-        <v>A. G. Cook</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L137" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:12</v>
+        <v>3:49</v>
       </c>
       <c r="H138" t="str">
-        <v>Joyce Manor</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L138" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Starlight</v>
+        <v>HIGH</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Everything Glows</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G139" t="str">
-        <v>3:21</v>
+        <v>3:23</v>
       </c>
       <c r="H139" t="str">
-        <v>Cannons</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L139" t="str">
-        <v>Starlight - Cannons</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Dandelion</v>
+        <v>Villain</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>Reflections</v>
       </c>
       <c r="G140" t="str">
-        <v>3:14</v>
+        <v>3:53</v>
       </c>
       <c r="H140" t="str">
-        <v>Dogpark</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L140" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>THEMSELVES</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BACKWARD</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G141" t="str">
-        <v>2:46</v>
+        <v>3:00</v>
       </c>
       <c r="H141" t="str">
-        <v>Jordan Ward</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L141" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>High Maintenance</v>
+        <v>Residue</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Miracle Mile</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G142" t="str">
-        <v>2:24</v>
+        <v>3:28</v>
       </c>
       <c r="H142" t="str">
-        <v>Paul Russell</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L142" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Trackhawk</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Da Realest</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G143" t="str">
-        <v>1:59</v>
+        <v>2:12</v>
       </c>
       <c r="H143" t="str">
-        <v>Babyfxce E</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L143" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Wheel Man</v>
+        <v>Starlight</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Xavier</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G144" t="str">
-        <v>3:05</v>
+        <v>3:21</v>
       </c>
       <c r="H144" t="str">
-        <v>xaviersobased</v>
+        <v>Cannons</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L144" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Natural Disaster</v>
+        <v>Dandelion</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G145" t="str">
-        <v>3:02</v>
+        <v>3:14</v>
       </c>
       <c r="H145" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Dogpark</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L145" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Prettier</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Prettier - Single</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G146" t="str">
-        <v>2:34</v>
+        <v>2:46</v>
       </c>
       <c r="H146" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L146" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Shotta Flow 8</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G147" t="str">
-        <v>3:21</v>
+        <v>2:24</v>
       </c>
       <c r="H147" t="str">
-        <v>NLE Choppa</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L147" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Die To Fall</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G148" t="str">
-        <v>3:20</v>
+        <v>1:59</v>
       </c>
       <c r="H148" t="str">
-        <v>The Maine</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L148" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Xavier</v>
       </c>
       <c r="G149" t="str">
-        <v>2:58</v>
+        <v>3:05</v>
       </c>
       <c r="H149" t="str">
-        <v>Steve Aoki</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Slow Burn</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Still There’s a Glow</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:14</v>
+        <v>3:02</v>
       </c>
       <c r="H150" t="str">
-        <v>Sweet Pill</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L150" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Prettier</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:50</v>
+        <v>2:34</v>
       </c>
       <c r="H151" t="str">
-        <v>i-dle</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L151" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>1:55</v>
+        <v>3:21</v>
       </c>
       <c r="H152" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L152" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>RIDIN</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>RIDIN - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:00</v>
+        <v>3:20</v>
       </c>
       <c r="H153" t="str">
-        <v>Tokischa</v>
+        <v>The Maine</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L153" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>POSSESSION</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>POSSESSION - Single</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:07</v>
+        <v>2:58</v>
       </c>
       <c r="H154" t="str">
-        <v>Melanie Martinez</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L154" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Poema</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Poema - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G155" t="str">
-        <v>3:14</v>
+        <v>2:14</v>
       </c>
       <c r="H155" t="str">
-        <v>Óscar Maydon</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L155" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Live Without</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:55</v>
+        <v>2:50</v>
       </c>
       <c r="H156" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>i-dle</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L156" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>FANÁTICO</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G157" t="str">
-        <v>3:55</v>
+        <v>1:55</v>
       </c>
       <c r="H157" t="str">
-        <v>Blessd</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L157" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Frozen Lake</v>
+        <v>RIDIN</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:29</v>
+        <v>2:00</v>
       </c>
       <c r="H158" t="str">
-        <v>VOILÀ</v>
+        <v>Tokischa</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L158" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:45</v>
+        <v>3:07</v>
       </c>
       <c r="H159" t="str">
-        <v>VEDO</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L159" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Poema</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:32</v>
+        <v>3:14</v>
       </c>
       <c r="H160" t="str">
-        <v>Chris Lorenzo</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L160" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>It’s Like That</v>
+        <v>Live Without</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>A Pound of Feathers</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G161" t="str">
-        <v>3:20</v>
+        <v>2:55</v>
       </c>
       <c r="H161" t="str">
-        <v>The Black Crowes</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L161" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>A.S.A.P.</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:48</v>
+        <v>3:55</v>
       </c>
       <c r="H162" t="str">
-        <v>Mýa</v>
+        <v>Blessd</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L162" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Once I Say</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>PASSION</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:21</v>
+        <v>3:29</v>
       </c>
       <c r="H163" t="str">
-        <v>Terrace Martin</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L163" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>believer</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>believer - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:57</v>
+        <v>2:45</v>
       </c>
       <c r="H164" t="str">
-        <v>Yuna</v>
+        <v>VEDO</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L164" t="str">
-        <v>believer - Yuna</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I Envy The Wind</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:51</v>
+        <v>3:32</v>
       </c>
       <c r="H165" t="str">
-        <v>Molly Parden</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L165" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>The Alchemist</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>The Alchemist</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G166" t="str">
-        <v>3:13</v>
+        <v>3:20</v>
       </c>
       <c r="H166" t="str">
-        <v>Bre Kennedy</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L166" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Daysa</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Daysa - Single</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:36</v>
+        <v>2:48</v>
       </c>
       <c r="H167" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Mýa</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L167" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fabulous</v>
+        <v>Once I Say</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Fabulous - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G168" t="str">
-        <v>2:33</v>
+        <v>3:21</v>
       </c>
       <c r="H168" t="str">
-        <v>MEEK</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L168" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>believer</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:22</v>
+        <v>2:57</v>
       </c>
       <c r="H169" t="str">
-        <v>RUBIO</v>
+        <v>Yuna</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L169" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>brainchem</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>brainchem - Single</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:28</v>
+        <v>3:51</v>
       </c>
       <c r="H170" t="str">
-        <v>EMJAY</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L170" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>With No Due Respect</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G171" t="str">
-        <v>2:48</v>
+        <v>3:13</v>
       </c>
       <c r="H171" t="str">
-        <v>Foggieraw</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L171" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Giants</v>
+        <v>Daysa</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Giants - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:12</v>
+        <v>4:36</v>
       </c>
       <c r="H172" t="str">
-        <v>Picture This</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L172" t="str">
-        <v>Giants - Picture This</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Scooby</v>
+        <v>Fabulous</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Scooby - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:41</v>
+        <v>2:33</v>
       </c>
       <c r="H173" t="str">
-        <v>corook</v>
+        <v>MEEK</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L173" t="str">
-        <v>Scooby - corook</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>La Racha</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>La Racha - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:48</v>
+        <v>3:22</v>
       </c>
       <c r="H174" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>RUBIO</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L174" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>So Am I</v>
+        <v>brainchem</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:50</v>
+        <v>2:28</v>
       </c>
       <c r="H175" t="str">
-        <v>Katelyn Tarver</v>
+        <v>EMJAY</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L175" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>best thing</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>best thing - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G176" t="str">
-        <v>4:27</v>
+        <v>2:48</v>
       </c>
       <c r="H176" t="str">
-        <v>WRABEL</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L176" t="str">
-        <v>best thing - WRABEL</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Count It Back</v>
+        <v>Giants</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Magic Boy</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:52</v>
+        <v>3:12</v>
       </c>
       <c r="H177" t="str">
-        <v>Bartees Strange</v>
+        <v>Picture This</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L177" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Good Girl</v>
+        <v>Scooby</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Good Girl - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:23</v>
+        <v>3:41</v>
       </c>
       <c r="H178" t="str">
-        <v>Paris Paloma</v>
+        <v>corook</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L178" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>MY REVIVAL</v>
+        <v>La Racha</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:34</v>
+        <v>2:48</v>
       </c>
       <c r="H179" t="str">
-        <v>MORGXN</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L179" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Run My Way</v>
+        <v>So Am I</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Run My Way - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G180" t="str">
-        <v>2:44</v>
+        <v>2:50</v>
       </c>
       <c r="H180" t="str">
-        <v>December 10</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L180" t="str">
-        <v>Run My Way - December 10</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Cold Night</v>
+        <v>best thing</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Cold Night - Single</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:12</v>
+        <v>4:27</v>
       </c>
       <c r="H181" t="str">
-        <v>HANA</v>
+        <v>WRABEL</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L181" t="str">
-        <v>Cold Night - HANA</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Away With The Fairies</v>
+        <v>Count It Back</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G182" t="str">
-        <v>2:28</v>
+        <v>2:52</v>
       </c>
       <c r="H182" t="str">
-        <v>LUNA</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L182" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fragile</v>
+        <v>Good Girl</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Fragile - Single</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:10</v>
+        <v>4:23</v>
       </c>
       <c r="H183" t="str">
-        <v>Anajah</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L183" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Slow Dancin'</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G184" t="str">
-        <v>2:04</v>
+        <v>3:34</v>
       </c>
       <c r="H184" t="str">
-        <v>STELLA LEFTY</v>
+        <v>MORGXN</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L184" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Run My Way</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:04</v>
+        <v>2:44</v>
       </c>
       <c r="H185" t="str">
-        <v>Lily Meola</v>
+        <v>December 10</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L185" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>More Of What Matters</v>
+        <v>Cold Night</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H186" t="str">
-        <v>Jamey Johnson</v>
+        <v>HANA</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L186" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Is This The Real You</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>ONE</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:46</v>
+        <v>2:28</v>
       </c>
       <c r="H187" t="str">
-        <v>Sevendust</v>
+        <v>LUNA</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L187" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Hud</v>
+        <v>Fragile</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>DREAMCRUSH</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:46</v>
+        <v>3:10</v>
       </c>
       <c r="H188" t="str">
-        <v>MØL</v>
+        <v>Anajah</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L188" t="str">
-        <v>Hud - MØL</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Ego Death</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Ego Death - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:12</v>
+        <v>2:04</v>
       </c>
       <c r="H189" t="str">
-        <v>Atreyu</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L189" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:05</v>
+        <v>3:04</v>
       </c>
       <c r="H190" t="str">
-        <v>EJ Jones</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L190" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Disappear</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Disappear</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>5:50</v>
+        <v>3:41</v>
       </c>
       <c r="H191" t="str">
-        <v>Lane 8</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L191" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Misbehave</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Misbehave - Single</v>
+        <v>ONE</v>
       </c>
       <c r="G192" t="str">
-        <v>3:43</v>
+        <v>3:46</v>
       </c>
       <c r="H192" t="str">
-        <v>Aluna</v>
+        <v>Sevendust</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L192" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Club Bizarre</v>
+        <v>Hud</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G193" t="str">
-        <v>2:47</v>
+        <v>4:46</v>
       </c>
       <c r="H193" t="str">
-        <v>Alok</v>
+        <v>MØL</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L193" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Fly</v>
+        <v>Ego Death</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Fly - Single</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:04</v>
+        <v>2:12</v>
       </c>
       <c r="H194" t="str">
-        <v>Stephen Stanley</v>
+        <v>Atreyu</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L194" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>ily anyway</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>ily anyway - Single</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:05</v>
+        <v>4:05</v>
       </c>
       <c r="H195" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L195" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>Disappear</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Nellene - EP</v>
+        <v>Disappear</v>
       </c>
       <c r="G196" t="str">
-        <v>3:35</v>
+        <v>5:50</v>
       </c>
       <c r="H196" t="str">
-        <v>Deloyd Elze</v>
+        <v>Lane 8</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L196" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Kiss Big</v>
+        <v>Misbehave</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Kiss Big</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:41</v>
+        <v>3:43</v>
       </c>
       <c r="H197" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Aluna</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L197" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>praxis</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:28</v>
+        <v>2:47</v>
       </c>
       <c r="H198" t="str">
-        <v>Lauren Auder</v>
+        <v>Alok</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L198" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>House</v>
+        <v>Fly</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>House - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:30</v>
+        <v>3:04</v>
       </c>
       <c r="H199" t="str">
-        <v>Connie Converse</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L199" t="str">
-        <v>House - Connie Converse</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>ily anyway</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:57</v>
+        <v>3:05</v>
       </c>
       <c r="H200" t="str">
-        <v>Yumi Zouma</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L200" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Brincar</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-01</v>
@@ -8013,68 +8013,258 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>JET LAG - EP</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G201" t="str">
-        <v>3:06</v>
+        <v>3:35</v>
       </c>
       <c r="H201" t="str">
-        <v>J Castle</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L201" t="str">
-        <v>Brincar - J Castle</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
+        <v>Kiss Big</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Kiss Big</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:41</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Ailbhe Reddy</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Kiss Big - Ailbhe Reddy</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>praxis</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Whole World As Vigil</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Lauren Auder</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+      </c>
+      <c r="L203" t="str">
+        <v>praxis - Lauren Auder</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>House</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/house/1866696487</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>House - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:30</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Connie Converse</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/house/1866696486</v>
+      </c>
+      <c r="L204" t="str">
+        <v>House - Connie Converse</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Cowboy Without a Clue</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>No Love Lost to Kindness</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:57</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Yumi Zouma</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G206" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H206" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
         <v>Quién</v>
       </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D202" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
+      <c r="D207" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G202" t="str">
+      <c r="G207" t="str">
         <v>4:19</v>
       </c>
-      <c r="H202" t="str">
+      <c r="H207" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K202" t="str">
+      <c r="K207" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L202" t="str">
+      <c r="L207" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week01/titles.xlsx
+++ b/data/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L207"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
+        <v>ששון שאולוב - חשבונות שמיים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409444&amp;sid=c5c30978038848a81687864b9fc464f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409446&amp;sid=27f51e4d97173c14aa9eadc22e457f7c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
+        <v>ששון שאולוב - חשבונות שמיים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>פרחי ירושלים - סומלילנד</v>
+        <v>רפאל שילוני - מחכה לך</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409443&amp;sid=c5c30978038848a81687864b9fc464f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409445&amp;sid=27f51e4d97173c14aa9eadc22e457f7c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>פרחי ירושלים - סומלילנד</v>
+        <v>רפאל שילוני - מחכה לך</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מתנאל סבח - שדרות דוממת</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409442&amp;sid=c5c30978038848a81687864b9fc464f8</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-01</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>4:58</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>The Warning</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מתנאל סבח - שדרות דוממת</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409441&amp;sid=c5c30978038848a81687864b9fc464f8</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-01</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>5:08</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>The Offspring</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אורי זר - חוזר לילדות</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409440&amp;sid=c5c30978038848a81687864b9fc464f8</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-01</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>4:38</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Roxette</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אורי זר - חוזר לילדות</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-01</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:58</v>
+        <v>3:50</v>
       </c>
       <c r="H7" t="str">
-        <v>The Warning</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>5:08</v>
+        <v>3:10</v>
       </c>
       <c r="H8" t="str">
-        <v>The Offspring</v>
+        <v>Joseph</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-01</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:38</v>
+        <v>2:44</v>
       </c>
       <c r="H9" t="str">
-        <v>Roxette</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-01</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:50</v>
+        <v>2:57</v>
       </c>
       <c r="H10" t="str">
-        <v>Jessie Ware</v>
+        <v>Take That</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-01</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:10</v>
+        <v>2:39</v>
       </c>
       <c r="H11" t="str">
-        <v>Joseph</v>
+        <v>The Cure</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-01</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:44</v>
+        <v>3:07</v>
       </c>
       <c r="H12" t="str">
-        <v>Dean Lewis</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-01</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:57</v>
+        <v>4:47</v>
       </c>
       <c r="H13" t="str">
-        <v>Take That</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-01</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:39</v>
+        <v>3:22</v>
       </c>
       <c r="H14" t="str">
-        <v>The Cure</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-01</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:07</v>
+        <v>2:48</v>
       </c>
       <c r="H15" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>only the poets</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-01</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:47</v>
+        <v>2:52</v>
       </c>
       <c r="H16" t="str">
-        <v>Paris Paloma</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-01</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:22</v>
+        <v>3:33</v>
       </c>
       <c r="H17" t="str">
-        <v>Zara Larsson</v>
+        <v>David Guetta</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-01</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:48</v>
+        <v>2:41</v>
       </c>
       <c r="H18" t="str">
-        <v>only the poets</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-01</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:52</v>
+        <v>4:01</v>
       </c>
       <c r="H19" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-01</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:33</v>
+        <v>3:16</v>
       </c>
       <c r="H20" t="str">
-        <v>David Guetta</v>
+        <v>Dogpark</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:41</v>
+        <v>3:03</v>
       </c>
       <c r="H21" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:01</v>
+        <v>2:41</v>
       </c>
       <c r="H22" t="str">
-        <v>Ella Langley</v>
+        <v>ERNEST</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:16</v>
+        <v>3:05</v>
       </c>
       <c r="H23" t="str">
-        <v>Dogpark</v>
+        <v>Labrinth</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:03</v>
+        <v>2:46</v>
       </c>
       <c r="H24" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:41</v>
+        <v>3:32</v>
       </c>
       <c r="H25" t="str">
-        <v>ERNEST</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:05</v>
+        <v>3:42</v>
       </c>
       <c r="H26" t="str">
-        <v>Labrinth</v>
+        <v>Cannons</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:46</v>
+        <v>2:38</v>
       </c>
       <c r="H27" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:32</v>
+        <v>3:10</v>
       </c>
       <c r="H28" t="str">
-        <v>VOILÀ</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:42</v>
+        <v>3:57</v>
       </c>
       <c r="H29" t="str">
-        <v>Cannons</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:38</v>
+        <v>2:19</v>
       </c>
       <c r="H30" t="str">
-        <v>Kylie Morgan</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:10</v>
+        <v>4:04</v>
       </c>
       <c r="H31" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>India Martínez</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:57</v>
+        <v>2:16</v>
       </c>
       <c r="H32" t="str">
-        <v>Willie Nelson</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-01</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:19</v>
+        <v>5:58</v>
       </c>
       <c r="H33" t="str">
-        <v>JeremyCampMusic</v>
+        <v>TINI</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-01</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:04</v>
+        <v>3:26</v>
       </c>
       <c r="H34" t="str">
-        <v>India Martínez</v>
+        <v>Charley</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-01</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:16</v>
+        <v>4:05</v>
       </c>
       <c r="H35" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-01</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>5:58</v>
+        <v>3:16</v>
       </c>
       <c r="H36" t="str">
-        <v>TINI</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-01</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:26</v>
+        <v>3:14</v>
       </c>
       <c r="H37" t="str">
-        <v>Charley</v>
+        <v>Beck</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-01</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:05</v>
+        <v>2:57</v>
       </c>
       <c r="H38" t="str">
-        <v>Demi Lovato</v>
+        <v>The Offspring</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:16</v>
+        <v>4:10</v>
       </c>
       <c r="H39" t="str">
-        <v>Teddy Swims</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:14</v>
+        <v>2:10</v>
       </c>
       <c r="H40" t="str">
-        <v>Beck</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-01</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:57</v>
+        <v>3:52</v>
       </c>
       <c r="H41" t="str">
-        <v>The Offspring</v>
+        <v>lights</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-01</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:10</v>
+        <v>3:50</v>
       </c>
       <c r="H42" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Telenova</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>I Explained How Music Works LIVE At My Concert</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-01</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:10</v>
+        <v>5:32</v>
       </c>
       <c r="H43" t="str">
-        <v>Jason Derulo</v>
+        <v>Marcin</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>I Explained How Music Works LIVE At My Concert - Marcin</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-01</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:52</v>
+        <v>4:27</v>
       </c>
       <c r="H44" t="str">
-        <v>lights</v>
+        <v>We Three</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:50</v>
+        <v>3:01</v>
       </c>
       <c r="H45" t="str">
-        <v>Telenova</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>I Explained "How Music Works" LIVE At My Concert</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>5:32</v>
+        <v>3:20</v>
       </c>
       <c r="H46" t="str">
-        <v>Marcin</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>I Explained "How Music Works" LIVE At My Concert - Marcin</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:27</v>
+        <v>3:34</v>
       </c>
       <c r="H47" t="str">
-        <v>We Three</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:01</v>
+        <v>4:01</v>
       </c>
       <c r="H48" t="str">
-        <v>Timebelle Official</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B49" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:20</v>
+        <v>3:24</v>
       </c>
       <c r="H49" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:34</v>
+        <v>5:52</v>
       </c>
       <c r="H50" t="str">
-        <v>Clinton Kane</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B51" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-01</v>
@@ -2316,10 +2316,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:01</v>
+        <v>5:01</v>
       </c>
       <c r="H51" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B52" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-01</v>
@@ -2354,10 +2354,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:24</v>
+        <v>4:12</v>
       </c>
       <c r="H52" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B53" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-01</v>
@@ -2392,10 +2392,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>5:52</v>
+        <v>3:59</v>
       </c>
       <c r="H53" t="str">
-        <v>Harry Styles</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B54" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-01</v>
@@ -2430,10 +2430,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>5:01</v>
+        <v>2:56</v>
       </c>
       <c r="H54" t="str">
-        <v>Neal Francis</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-01</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:12</v>
+        <v>3:46</v>
       </c>
       <c r="H55" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-01</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:59</v>
+        <v>4:37</v>
       </c>
       <c r="H56" t="str">
-        <v>Holly Humberstone</v>
+        <v>Bella White</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-01</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:56</v>
+        <v>4:06</v>
       </c>
       <c r="H57" t="str">
-        <v>Cliff Richard</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-01</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:46</v>
+        <v>3:54</v>
       </c>
       <c r="H58" t="str">
-        <v>Jessie Ware</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-01</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:37</v>
+        <v>4:10</v>
       </c>
       <c r="H59" t="str">
-        <v>Bella White</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-01</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:06</v>
+        <v>3:26</v>
       </c>
       <c r="H60" t="str">
-        <v>Ryan Wright</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-01</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:54</v>
+        <v>2:56</v>
       </c>
       <c r="H61" t="str">
-        <v>Dove Cameron</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-01</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:10</v>
+        <v>2:56</v>
       </c>
       <c r="H62" t="str">
-        <v>Parker McCollum</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-01</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:26</v>
+        <v>4:01</v>
       </c>
       <c r="H63" t="str">
-        <v>Matt Hansen</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-01</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:56</v>
+        <v>3:05</v>
       </c>
       <c r="H64" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-01</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:56</v>
+        <v>2:27</v>
       </c>
       <c r="H65" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-01</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:01</v>
+        <v>2:34</v>
       </c>
       <c r="H66" t="str">
-        <v>Tauren Wells</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-01</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:05</v>
+        <v>3:13</v>
       </c>
       <c r="H67" t="str">
-        <v>Maiah Manser</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-01</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:27</v>
+        <v>3:13</v>
       </c>
       <c r="H68" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-01</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:34</v>
+        <v>3:08</v>
       </c>
       <c r="H69" t="str">
-        <v>Chelsea Cutler</v>
+        <v>CAIN</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-01</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:13</v>
+        <v>5:14</v>
       </c>
       <c r="H70" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:13</v>
+        <v>2:59</v>
       </c>
       <c r="H71" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:08</v>
+        <v>4:21</v>
       </c>
       <c r="H72" t="str">
-        <v>CAIN</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>5:14</v>
+        <v>4:09</v>
       </c>
       <c r="H73" t="str">
-        <v>Harry Styles</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-01</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:59</v>
+        <v>2:34</v>
       </c>
       <c r="H74" t="str">
-        <v>Lana Lubany</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:21</v>
+        <v>3:10</v>
       </c>
       <c r="H75" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-01</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:09</v>
+        <v>3:21</v>
       </c>
       <c r="H76" t="str">
-        <v>Dermot Kennedy</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-01</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:34</v>
+        <v>3:06</v>
       </c>
       <c r="H77" t="str">
-        <v>Lauren Sanderson</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-01</v>
@@ -3342,10 +3342,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H78" t="str">
-        <v>Olivia Dean</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B79" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-01</v>
@@ -3380,10 +3380,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:21</v>
+        <v>7:21</v>
       </c>
       <c r="H79" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H80" t="str">
-        <v>The Avett Brothers</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-01</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:21</v>
+        <v>3:45</v>
       </c>
       <c r="H81" t="str">
-        <v>Jordana Bryant</v>
+        <v>Tones And I</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-01</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>7:21</v>
+        <v>3:57</v>
       </c>
       <c r="H82" t="str">
-        <v>Katy Perry</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-01</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:17</v>
+        <v>3:03</v>
       </c>
       <c r="H83" t="str">
-        <v>Lauren Watkins</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-01</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:45</v>
+        <v>4:27</v>
       </c>
       <c r="H84" t="str">
-        <v>Tones And I</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-01</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:57</v>
+        <v>4:34</v>
       </c>
       <c r="H85" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Armik</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-01</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:03</v>
+        <v>2:54</v>
       </c>
       <c r="H86" t="str">
-        <v>Charlie Puth</v>
+        <v>LØLØ</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-01</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:27</v>
+        <v>3:25</v>
       </c>
       <c r="H87" t="str">
-        <v>Chappell Roan</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-01</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:34</v>
+        <v>2:01</v>
       </c>
       <c r="H88" t="str">
-        <v>Armik</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-01</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:54</v>
+        <v>2:25</v>
       </c>
       <c r="H89" t="str">
-        <v>LØLØ</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-01</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:25</v>
+        <v>1:14</v>
       </c>
       <c r="H90" t="str">
-        <v>Tenille Townes</v>
+        <v>Labrinth</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-01</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:01</v>
+        <v>2:59</v>
       </c>
       <c r="H91" t="str">
-        <v>Alan Walker</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-01</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:25</v>
+        <v>2:29</v>
       </c>
       <c r="H92" t="str">
-        <v>Charli xcx</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-01</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>1:14</v>
+        <v>2:34</v>
       </c>
       <c r="H93" t="str">
-        <v>Labrinth</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-01</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:59</v>
+        <v>3:48</v>
       </c>
       <c r="H94" t="str">
-        <v>Charlie Puth</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-01</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:29</v>
+        <v>3:32</v>
       </c>
       <c r="H95" t="str">
-        <v>Girl Tones</v>
+        <v>The Beaches</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-01</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:34</v>
+        <v>3:49</v>
       </c>
       <c r="H96" t="str">
-        <v>Jagwar Twin</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-01</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:48</v>
+        <v>4:28</v>
       </c>
       <c r="H97" t="str">
-        <v>Caroline Jones</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-01</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:32</v>
+        <v>3:37</v>
       </c>
       <c r="H98" t="str">
-        <v>The Beaches</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-01</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:49</v>
+        <v>3:35</v>
       </c>
       <c r="H99" t="str">
-        <v>Dolly Parton</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-01</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:28</v>
+        <v>2:31</v>
       </c>
       <c r="H100" t="str">
-        <v>Madison Beer</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-01</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:37</v>
+        <v>3:21</v>
       </c>
       <c r="H101" t="str">
-        <v>Ty Myers</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B102" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-01</v>
@@ -4254,10 +4254,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:35</v>
+        <v>5:24</v>
       </c>
       <c r="H102" t="str">
-        <v>Megan Moroney</v>
+        <v>Nickless</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B103" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-01</v>
@@ -4292,10 +4292,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>2:31</v>
+        <v>3:11</v>
       </c>
       <c r="H103" t="str">
-        <v>Julia Cole Music</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Body</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>OCTANE</v>
       </c>
       <c r="G104" t="str">
-        <v>3:21</v>
+        <v>2:35</v>
       </c>
       <c r="H104" t="str">
-        <v>Lily Allen</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/body/1871258329</v>
       </c>
       <c r="L104" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Body - Don Toliver</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Dandelion</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>Dandelion</v>
       </c>
       <c r="G105" t="str">
-        <v>5:24</v>
+        <v>4:00</v>
       </c>
       <c r="H105" t="str">
-        <v>Nickless</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
       </c>
       <c r="L105" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Dandelion - Ella Langley</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>LIGHTS GO OUT</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>LIGHTS GO OUT - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:11</v>
+        <v>2:38</v>
       </c>
       <c r="H106" t="str">
-        <v>Peach PRC</v>
+        <v>John Summit</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
       </c>
       <c r="L106" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>LIGHTS GO OUT - John Summit</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Body</v>
+        <v>The Great Divide</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/body/1871258331</v>
+        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>OCTANE</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G107" t="str">
-        <v>2:35</v>
+        <v>5:17</v>
       </c>
       <c r="H107" t="str">
-        <v>Don Toliver</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/body/1871258329</v>
+        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
       </c>
       <c r="L107" t="str">
-        <v>Body - Don Toliver</v>
+        <v>The Great Divide - Noah Kahan</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Dandelion</v>
+        <v>tristón</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
+        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Dandelion</v>
+        <v>tristón - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>4:00</v>
+        <v>3:36</v>
       </c>
       <c r="H108" t="str">
-        <v>Ella Langley</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
+        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
       </c>
       <c r="L108" t="str">
-        <v>Dandelion - Ella Langley</v>
+        <v>tristón - Fuerza Regida</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>LIGHTS GO OUT</v>
+        <v>Feed the Streets</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
+        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>LIGHTS GO OUT - Single</v>
+        <v>Feed the Streets - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:38</v>
+        <v>2:58</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>Rod Wave</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
+        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
       </c>
       <c r="L109" t="str">
-        <v>LIGHTS GO OUT - John Summit</v>
+        <v>Feed the Streets - Rod Wave</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>The Great Divide</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>The Great Divide</v>
+        <v>Distracted</v>
       </c>
       <c r="G110" t="str">
-        <v>5:17</v>
+        <v>2:30</v>
       </c>
       <c r="H110" t="str">
-        <v>Noah Kahan</v>
+        <v>Thundercat</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L110" t="str">
-        <v>The Great Divide - Noah Kahan</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>tristón</v>
+        <v>For Hire</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>tristón - Single</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:36</v>
+        <v>3:44</v>
       </c>
       <c r="H111" t="str">
-        <v>Fuerza Regida</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L111" t="str">
-        <v>tristón - Fuerza Regida</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Feed the Streets</v>
+        <v>McArthur</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Feed the Streets - Single</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:58</v>
+        <v>3:51</v>
       </c>
       <c r="H112" t="str">
-        <v>Rod Wave</v>
+        <v>HARDY</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L112" t="str">
-        <v>Feed the Streets - Rod Wave</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>I Did This To Myself</v>
+        <v>Debris</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Distracted</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G113" t="str">
-        <v>2:30</v>
+        <v>2:55</v>
       </c>
       <c r="H113" t="str">
-        <v>Thundercat</v>
+        <v>Labrinth</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L113" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>For Hire</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>For Hire - Single</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G114" t="str">
-        <v>3:44</v>
+        <v>3:25</v>
       </c>
       <c r="H114" t="str">
-        <v>People I’ve Met</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L114" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>McArthur</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>McArthur - Single</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:51</v>
+        <v>4:38</v>
       </c>
       <c r="H115" t="str">
-        <v>HARDY</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L115" t="str">
-        <v>McArthur - HARDY</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Debris</v>
+        <v>1+1</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:55</v>
+        <v>3:06</v>
       </c>
       <c r="H116" t="str">
-        <v>Labrinth</v>
+        <v>Maluma</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L116" t="str">
-        <v>Debris - Labrinth</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:25</v>
+        <v>3:08</v>
       </c>
       <c r="H117" t="str">
-        <v>Militarie Gun</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L117" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>4:38</v>
+        <v>3:02</v>
       </c>
       <c r="H118" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L118" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>1+1</v>
+        <v>fml .</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>1+1 - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G119" t="str">
-        <v>3:06</v>
+        <v>2:40</v>
       </c>
       <c r="H119" t="str">
-        <v>Maluma</v>
+        <v>fakemink</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L119" t="str">
-        <v>1+1 - Maluma</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:08</v>
+        <v>3:01</v>
       </c>
       <c r="H120" t="str">
-        <v>MJ Cole</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L120" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Two Car Garage</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:02</v>
+        <v>3:08</v>
       </c>
       <c r="H121" t="str">
-        <v>Jon Bellion</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L121" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>fml .</v>
+        <v>Lorelei</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:40</v>
+        <v>2:35</v>
       </c>
       <c r="H122" t="str">
-        <v>fakemink</v>
+        <v>ERNEST</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L122" t="str">
-        <v>fml . - fakemink</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Faked It All The Time</v>
+        <v>Free</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:01</v>
+        <v>3:56</v>
       </c>
       <c r="H123" t="str">
-        <v>Allie Sherlock</v>
+        <v>SLANDER</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L123" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>House of the Rising Sun</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:08</v>
+        <v>2:55</v>
       </c>
       <c r="H124" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Artemas</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L124" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Lorelei</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Lorelei - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G125" t="str">
-        <v>2:35</v>
+        <v>3:56</v>
       </c>
       <c r="H125" t="str">
-        <v>ERNEST</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L125" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Free</v>
+        <v>Aguas</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Free - Single</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:56</v>
+        <v>2:52</v>
       </c>
       <c r="H126" t="str">
-        <v>SLANDER</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L126" t="str">
-        <v>Free - SLANDER</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>professional heartbreaker</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:55</v>
+        <v>2:48</v>
       </c>
       <c r="H127" t="str">
-        <v>Artemas</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L127" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>tell me what you want</v>
+        <v>Baddie</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>ACT II</v>
+        <v>Bohemio</v>
       </c>
       <c r="G128" t="str">
-        <v>3:56</v>
+        <v>3:11</v>
       </c>
       <c r="H128" t="str">
-        <v>Sasha Keable</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L128" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Aguas</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Aguas - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:52</v>
+        <v>3:51</v>
       </c>
       <c r="H129" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Tems</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L129" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Ants In My Room</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:48</v>
+        <v>3:16</v>
       </c>
       <c r="H130" t="str">
-        <v>Carter Vail</v>
+        <v>Fred again..</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L130" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Baddie</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Bohemio</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:11</v>
+        <v>3:50</v>
       </c>
       <c r="H131" t="str">
-        <v>Nicky Jam</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L131" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G132" t="str">
-        <v>3:51</v>
+        <v>3:33</v>
       </c>
       <c r="H132" t="str">
-        <v>Tems</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L132" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:16</v>
+        <v>3:17</v>
       </c>
       <c r="H133" t="str">
-        <v>Fred again..</v>
+        <v>Kneecap</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L133" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:50</v>
+        <v>4:38</v>
       </c>
       <c r="H134" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L134" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>For The First Time, Again</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>For The First Time, Again</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:33</v>
+        <v>3:49</v>
       </c>
       <c r="H135" t="str">
-        <v>Tyler Ballgame</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L135" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Liars Tale</v>
+        <v>HIGH</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Liars Tale - Single</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G136" t="str">
-        <v>3:17</v>
+        <v>3:23</v>
       </c>
       <c r="H136" t="str">
-        <v>Kneecap</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L136" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>Villain</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G137" t="str">
-        <v>4:38</v>
+        <v>3:53</v>
       </c>
       <c r="H137" t="str">
-        <v>Motionless In White</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L137" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Wake Up Calling</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G138" t="str">
-        <v>3:49</v>
+        <v>3:00</v>
       </c>
       <c r="H138" t="str">
-        <v>Papa Roach</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L138" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>HIGH</v>
+        <v>Residue</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G139" t="str">
-        <v>3:23</v>
+        <v>3:28</v>
       </c>
       <c r="H139" t="str">
-        <v>Magnolia Park</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L139" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Villain</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Reflections</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G140" t="str">
-        <v>3:53</v>
+        <v>2:12</v>
       </c>
       <c r="H140" t="str">
-        <v>From Ashes to New</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L140" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Starlight</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G141" t="str">
-        <v>3:00</v>
+        <v>3:21</v>
       </c>
       <c r="H141" t="str">
-        <v>Caleb Chan</v>
+        <v>Cannons</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L141" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Residue</v>
+        <v>Dandelion</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G142" t="str">
-        <v>3:28</v>
+        <v>3:14</v>
       </c>
       <c r="H142" t="str">
-        <v>A. G. Cook</v>
+        <v>Dogpark</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L142" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G143" t="str">
-        <v>2:12</v>
+        <v>2:46</v>
       </c>
       <c r="H143" t="str">
-        <v>Joyce Manor</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L143" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Starlight</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Everything Glows</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G144" t="str">
-        <v>3:21</v>
+        <v>2:24</v>
       </c>
       <c r="H144" t="str">
-        <v>Cannons</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L144" t="str">
-        <v>Starlight - Cannons</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Dandelion</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>Da Realest</v>
       </c>
       <c r="G145" t="str">
-        <v>3:14</v>
+        <v>1:59</v>
       </c>
       <c r="H145" t="str">
-        <v>Dogpark</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L145" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>THEMSELVES</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>BACKWARD</v>
+        <v>Xavier</v>
       </c>
       <c r="G146" t="str">
-        <v>2:46</v>
+        <v>3:05</v>
       </c>
       <c r="H146" t="str">
-        <v>Jordan Ward</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L146" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>High Maintenance</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Miracle Mile</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:24</v>
+        <v>3:02</v>
       </c>
       <c r="H147" t="str">
-        <v>Paul Russell</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L147" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Trackhawk</v>
+        <v>Prettier</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Da Realest</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>1:59</v>
+        <v>2:34</v>
       </c>
       <c r="H148" t="str">
-        <v>Babyfxce E</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L148" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Wheel Man</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Xavier</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:05</v>
+        <v>3:21</v>
       </c>
       <c r="H149" t="str">
-        <v>xaviersobased</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L149" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Natural Disaster</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:02</v>
+        <v>3:20</v>
       </c>
       <c r="H150" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Maine</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L150" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Prettier</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Prettier - Single</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:34</v>
+        <v>2:58</v>
       </c>
       <c r="H151" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L151" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G152" t="str">
-        <v>3:21</v>
+        <v>2:14</v>
       </c>
       <c r="H152" t="str">
-        <v>NLE Choppa</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L152" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Die To Fall</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:20</v>
+        <v>2:50</v>
       </c>
       <c r="H153" t="str">
-        <v>The Maine</v>
+        <v>i-dle</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L153" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G154" t="str">
-        <v>2:58</v>
+        <v>1:55</v>
       </c>
       <c r="H154" t="str">
-        <v>Steve Aoki</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L154" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Slow Burn</v>
+        <v>RIDIN</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Still There’s a Glow</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:14</v>
+        <v>2:00</v>
       </c>
       <c r="H155" t="str">
-        <v>Sweet Pill</v>
+        <v>Tokischa</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L155" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:50</v>
+        <v>3:07</v>
       </c>
       <c r="H156" t="str">
-        <v>i-dle</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L156" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Poema</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>1:55</v>
+        <v>3:14</v>
       </c>
       <c r="H157" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L157" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>RIDIN</v>
+        <v>Live Without</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>RIDIN - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G158" t="str">
-        <v>2:00</v>
+        <v>2:55</v>
       </c>
       <c r="H158" t="str">
-        <v>Tokischa</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L158" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>POSSESSION</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>POSSESSION - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:07</v>
+        <v>3:55</v>
       </c>
       <c r="H159" t="str">
-        <v>Melanie Martinez</v>
+        <v>Blessd</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L159" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Poema</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Poema - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H160" t="str">
-        <v>Óscar Maydon</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L160" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Live Without</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:55</v>
+        <v>2:45</v>
       </c>
       <c r="H161" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>VEDO</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L161" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>FANÁTICO</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:55</v>
+        <v>3:32</v>
       </c>
       <c r="H162" t="str">
-        <v>Blessd</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L162" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Frozen Lake</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G163" t="str">
-        <v>3:29</v>
+        <v>3:20</v>
       </c>
       <c r="H163" t="str">
-        <v>VOILÀ</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L163" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:45</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>VEDO</v>
+        <v>Mýa</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L164" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Once I Say</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G165" t="str">
-        <v>3:32</v>
+        <v>3:21</v>
       </c>
       <c r="H165" t="str">
-        <v>Chris Lorenzo</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L165" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>It’s Like That</v>
+        <v>believer</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>A Pound of Feathers</v>
+        <v>believer - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:20</v>
+        <v>2:57</v>
       </c>
       <c r="H166" t="str">
-        <v>The Black Crowes</v>
+        <v>Yuna</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L166" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>A.S.A.P.</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:48</v>
+        <v>3:51</v>
       </c>
       <c r="H167" t="str">
-        <v>Mýa</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L167" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Once I Say</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>PASSION</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G168" t="str">
-        <v>3:21</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>Terrace Martin</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L168" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>believer</v>
+        <v>Daysa</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>believer - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:57</v>
+        <v>4:36</v>
       </c>
       <c r="H169" t="str">
-        <v>Yuna</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L169" t="str">
-        <v>believer - Yuna</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>I Envy The Wind</v>
+        <v>Fabulous</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:51</v>
+        <v>2:33</v>
       </c>
       <c r="H170" t="str">
-        <v>Molly Parden</v>
+        <v>MEEK</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L170" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>The Alchemist</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Alchemist</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:13</v>
+        <v>3:22</v>
       </c>
       <c r="H171" t="str">
-        <v>Bre Kennedy</v>
+        <v>RUBIO</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L171" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Daysa</v>
+        <v>brainchem</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Daysa - Single</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:36</v>
+        <v>2:28</v>
       </c>
       <c r="H172" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>EMJAY</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L172" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Fabulous</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Fabulous - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G173" t="str">
-        <v>2:33</v>
+        <v>2:48</v>
       </c>
       <c r="H173" t="str">
-        <v>MEEK</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L173" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Giants</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:22</v>
+        <v>3:12</v>
       </c>
       <c r="H174" t="str">
-        <v>RUBIO</v>
+        <v>Picture This</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L174" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>brainchem</v>
+        <v>Scooby</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v